--- a/Specialty Claims 2026-S1/2026-05 May - Specialty Claims.xlsx
+++ b/Specialty Claims 2026-S1/2026-05 May - Specialty Claims.xlsx
@@ -77,7 +77,7 @@
             <family val="2"/>
             <scheme val="minor"/>
           </rPr>
-          <t>The master workbook matches on this column to pull Claim Status, Notes, Processed Date and Date Worked 1 back from this file with INDEX/MATCH, so you can freely sort or filter these rows without breaking the link. Do not edit it.</t>
+          <t>The master workbook matches on this column to pull Claim Status, Notes, Processed Date and Latest Date Worked back from this file with INDEX/MATCH, so you can freely sort or filter these rows without breaking the link. Do not edit it.</t>
         </r>
       </text>
     </comment>
@@ -283,7 +283,7 @@
             <family val="2"/>
             <scheme val="minor"/>
           </rPr>
-          <t>The master workbook matches on this column to pull Claim Status, Notes, Processed Date and Date Worked 1 back from this file with INDEX/MATCH, so you can freely sort or filter these rows without breaking the link. Do not edit it.</t>
+          <t>The master workbook matches on this column to pull Claim Status, Notes, Processed Date and Latest Date Worked back from this file with INDEX/MATCH, so you can freely sort or filter these rows without breaking the link. Do not edit it.</t>
         </r>
       </text>
     </comment>
@@ -489,7 +489,7 @@
             <family val="2"/>
             <scheme val="minor"/>
           </rPr>
-          <t>The master workbook matches on this column to pull Claim Status, Notes, Processed Date and Date Worked 1 back from this file with INDEX/MATCH, so you can freely sort or filter these rows without breaking the link. Do not edit it.</t>
+          <t>The master workbook matches on this column to pull Claim Status, Notes, Processed Date and Latest Date Worked back from this file with INDEX/MATCH, so you can freely sort or filter these rows without breaking the link. Do not edit it.</t>
         </r>
       </text>
     </comment>
@@ -695,7 +695,7 @@
             <family val="2"/>
             <scheme val="minor"/>
           </rPr>
-          <t>The master workbook matches on this column to pull Claim Status, Notes, Processed Date and Date Worked 1 back from this file with INDEX/MATCH, so you can freely sort or filter these rows without breaking the link. Do not edit it.</t>
+          <t>The master workbook matches on this column to pull Claim Status, Notes, Processed Date and Latest Date Worked back from this file with INDEX/MATCH, so you can freely sort or filter these rows without breaking the link. Do not edit it.</t>
         </r>
       </text>
     </comment>
@@ -901,7 +901,7 @@
             <family val="2"/>
             <scheme val="minor"/>
           </rPr>
-          <t>The master workbook matches on this column to pull Claim Status, Notes, Processed Date and Date Worked 1 back from this file with INDEX/MATCH, so you can freely sort or filter these rows without breaking the link. Do not edit it.</t>
+          <t>The master workbook matches on this column to pull Claim Status, Notes, Processed Date and Latest Date Worked back from this file with INDEX/MATCH, so you can freely sort or filter these rows without breaking the link. Do not edit it.</t>
         </r>
       </text>
     </comment>
@@ -1704,7 +1704,7 @@
     <t>1029</t>
   </si>
   <si>
-    <t>Date Worked 1</t>
+    <t>Latest Date Worked</t>
   </si>
   <si>
     <t>Remove CPT A6219, and resubmitted</t>
@@ -3045,19 +3045,19 @@
     <t>Cells you edit</t>
   </si>
   <si>
-    <t>Four columns are shaded pale yellow and are the ones meant to be edited here: Claim Status (A), Notes (B), Processed Date (C) and Date Worked 1 (K). Claim Status has a drop-down of the statuses already in use - it is a suggestion, not a restriction, so you can type anything.</t>
+    <t>Four columns are shaded pale yellow and are the ones meant to be edited here: Claim Status (A), Notes (B), Processed Date (C) and Latest Date Worked (K). Claim Status has a drop-down of the statuses already in use - it is a suggestion, not a restriction, so you can type anything.</t>
   </si>
   <si>
     <t>Statuses currently in use: Denied, Finalized, PAID, Pending, Received, Rejected.</t>
   </si>
   <si>
-    <t>Example of the expected format - Claim Status: "Denied";  Notes: "Corrected service line 1 - resubmitted";  Processed Date: "06/25/2026";  Date Worked 1: "08/12/2026".</t>
-  </si>
-  <si>
-    <t>Processed Date and Date Worked 1</t>
-  </si>
-  <si>
-    <t>Both are real dates displayed MM/DD/YYYY, the same order as every other date column in these files and as the source data. Date Worked 1 starts empty.</t>
+    <t>Example of the expected format - Claim Status: "Denied";  Notes: "Corrected service line 1 - resubmitted";  Processed Date: "06/25/2026";  Latest Date Worked: "08/12/2026".</t>
+  </si>
+  <si>
+    <t>Processed Date and Latest Date Worked</t>
+  </si>
+  <si>
+    <t>Both are real dates displayed MM/DD/YYYY, the same order as every other date column in these files and as the source data. Latest Date Worked starts empty.</t>
   </si>
   <si>
     <t>Processed Date is filled in wherever the row had something to fill it with: the date written into the Notes where there was one, otherwise the Insurance Check Date. A date from the Notes is never overwritten by a check date. Where the row has neither, it is blank for you to fill in.</t>

--- a/Specialty Claims 2026-S1/2026-05 May - Specialty Claims.xlsx
+++ b/Specialty Claims 2026-S1/2026-05 May - Specialty Claims.xlsx
@@ -21,13 +21,13 @@
     <sheet name="Read Me" sheetId="6" r:id="rId6"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">BH!$A$1:$AO$33</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">BH!$A$1:$AO$31</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">DME!$A$1:$AO$35</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">GAE!$A$1:$AO$7</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">ORTHO!$A$1:$AO$24</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">US!$A$1:$AO$19</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">ORTHO!$A$1:$AO$23</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">US!$A$1:$AO$16</definedName>
   </definedNames>
-  <calcPr calcId="191028"/>
+  <calcPr calcId="191028" fullCalcOnLoad="1"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -4528,7 +4528,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:AO33"/>
+  <dimension ref="A1:AO31"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="14" customWidth="1"/>
@@ -4727,7 +4727,7 @@
         <v>46244</v>
       </c>
       <c r="L2" s="12">
-        <f t="shared" ref="L2:L33" ca="1" si="0">IF($O2="","",$O2-TODAY())</f>
+        <f ca="1">IF($O2="","",$O2-TODAY())</f>
         <v>-36</v>
       </c>
       <c r="M2" s="12" t="str">
@@ -4837,7 +4837,7 @@
         <v>46244</v>
       </c>
       <c r="L3" s="12">
-        <f t="shared" ca="1" si="0"/>
+        <f ca="1">IF($O3="","",$O3-TODAY())</f>
         <v>-36</v>
       </c>
       <c r="M3" s="12" t="str">
@@ -4947,7 +4947,7 @@
         <v>46245</v>
       </c>
       <c r="L4" s="12">
-        <f t="shared" ca="1" si="0"/>
+        <f ca="1">IF($O4="","",$O4-TODAY())</f>
         <v>-34</v>
       </c>
       <c r="M4" s="12" t="str">
@@ -5059,7 +5059,7 @@
         <v>46245</v>
       </c>
       <c r="L5" s="12">
-        <f t="shared" ca="1" si="0"/>
+        <f ca="1">IF($O5="","",$O5-TODAY())</f>
         <v>-30</v>
       </c>
       <c r="M5" s="12">
@@ -5067,7 +5067,7 @@
         <v>87</v>
       </c>
       <c r="N5" s="12">
-        <f t="shared" ref="N5:N10" ca="1" si="1">IF($C5="","",$C5+365-TODAY())</f>
+        <f ca="1">IF($C5="","",$C5+365-TODAY())</f>
         <v>272</v>
       </c>
       <c r="O5" s="6">
@@ -5175,7 +5175,7 @@
         <v>46245</v>
       </c>
       <c r="L6" s="12">
-        <f t="shared" ca="1" si="0"/>
+        <f ca="1">IF($O6="","",$O6-TODAY())</f>
         <v>-30</v>
       </c>
       <c r="M6" s="12">
@@ -5183,7 +5183,7 @@
         <v>81</v>
       </c>
       <c r="N6" s="12">
-        <f t="shared" ca="1" si="1"/>
+        <f ca="1">IF($C6="","",$C6+365-TODAY())</f>
         <v>266</v>
       </c>
       <c r="O6" s="6">
@@ -5289,7 +5289,7 @@
         <v>46245</v>
       </c>
       <c r="L7" s="12">
-        <f t="shared" ca="1" si="0"/>
+        <f ca="1">IF($O7="","",$O7-TODAY())</f>
         <v>-28</v>
       </c>
       <c r="M7" s="12" t="str">
@@ -5297,7 +5297,7 @@
         <v/>
       </c>
       <c r="N7" s="12" t="str">
-        <f t="shared" ca="1" si="1"/>
+        <f ca="1">IF($C7="","",$C7+365-TODAY())</f>
         <v/>
       </c>
       <c r="O7" s="6">
@@ -5401,7 +5401,7 @@
         <v>46245</v>
       </c>
       <c r="L8" s="12">
-        <f t="shared" ca="1" si="0"/>
+        <f ca="1">IF($O8="","",$O8-TODAY())</f>
         <v>-28</v>
       </c>
       <c r="M8" s="12">
@@ -5409,7 +5409,7 @@
         <v>81</v>
       </c>
       <c r="N8" s="12">
-        <f t="shared" ca="1" si="1"/>
+        <f ca="1">IF($C8="","",$C8+365-TODAY())</f>
         <v>266</v>
       </c>
       <c r="O8" s="6">
@@ -5517,7 +5517,7 @@
         <v>46245</v>
       </c>
       <c r="L9" s="12">
-        <f t="shared" ca="1" si="0"/>
+        <f ca="1">IF($O9="","",$O9-TODAY())</f>
         <v>-21</v>
       </c>
       <c r="M9" s="12">
@@ -5525,7 +5525,7 @@
         <v>274</v>
       </c>
       <c r="N9" s="12">
-        <f t="shared" ca="1" si="1"/>
+        <f ca="1">IF($C9="","",$C9+365-TODAY())</f>
         <v>274</v>
       </c>
       <c r="O9" s="6">
@@ -5629,7 +5629,7 @@
         <v>46248</v>
       </c>
       <c r="L10" s="12">
-        <f t="shared" ca="1" si="0"/>
+        <f ca="1">IF($O10="","",$O10-TODAY())</f>
         <v>6</v>
       </c>
       <c r="M10" s="12" t="str">
@@ -5637,7 +5637,7 @@
         <v/>
       </c>
       <c r="N10" s="12" t="str">
-        <f t="shared" ca="1" si="1"/>
+        <f ca="1">IF($C10="","",$C10+365-TODAY())</f>
         <v/>
       </c>
       <c r="O10" s="6">
@@ -5739,7 +5739,7 @@
       </c>
       <c r="K11" s="3"/>
       <c r="L11" s="12">
-        <f t="shared" ca="1" si="0"/>
+        <f ca="1">IF($O11="","",$O11-TODAY())</f>
         <v>7</v>
       </c>
       <c r="M11" s="12">
@@ -5853,7 +5853,7 @@
         <v>46276</v>
       </c>
       <c r="L12" s="12">
-        <f t="shared" ca="1" si="0"/>
+        <f ca="1">IF($O12="","",$O12-TODAY())</f>
         <v>7</v>
       </c>
       <c r="M12" s="12">
@@ -5942,65 +5942,65 @@
       <c r="A13" s="2" t="s">
         <v>129</v>
       </c>
-      <c r="B13" s="2" t="s">
-        <v>130</v>
+      <c r="B13" s="15" t="s">
+        <v>673</v>
       </c>
       <c r="C13" s="3">
-        <v>46203</v>
+        <v>46266</v>
       </c>
       <c r="D13" s="4">
-        <v>560694862</v>
+        <v>563732700</v>
       </c>
       <c r="E13" s="5" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="F13" s="6">
-        <v>46169</v>
+        <v>46143</v>
       </c>
       <c r="G13" s="5" t="s">
-        <v>114</v>
+        <v>134</v>
       </c>
       <c r="H13" s="5" t="s">
-        <v>114</v>
+        <v>134</v>
       </c>
       <c r="I13" s="5" t="s">
-        <v>45</v>
+        <v>135</v>
       </c>
       <c r="J13" s="5" t="s">
-        <v>98</v>
+        <v>136</v>
       </c>
       <c r="K13" s="3">
-        <v>46251</v>
+        <v>46276</v>
       </c>
       <c r="L13" s="12">
-        <f t="shared" ca="1" si="0"/>
-        <v>7</v>
+        <f ca="1">IF($O13="","",$O13-TODAY())</f>
+        <v>226</v>
       </c>
       <c r="M13" s="12">
-        <f ca="1">IF($C13="","",$C13+180-TODAY())</f>
-        <v>101</v>
+        <f ca="1">IF($C13="","",$C13+365-TODAY())</f>
+        <v>349</v>
       </c>
       <c r="N13" s="12">
-        <f ca="1">IF($C13="","",$C13+180-TODAY())</f>
-        <v>101</v>
+        <f ca="1">IF($C13="","",$C13+120-TODAY())</f>
+        <v>104</v>
       </c>
       <c r="O13" s="6">
-        <v>46289</v>
+        <v>46508</v>
       </c>
       <c r="P13" s="5" t="s">
-        <v>115</v>
+        <v>51</v>
       </c>
       <c r="Q13" s="5" t="s">
-        <v>116</v>
+        <v>137</v>
       </c>
       <c r="R13" s="5" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="S13" s="5" t="s">
         <v>50</v>
       </c>
       <c r="T13" s="5" t="s">
-        <v>49</v>
+        <v>115</v>
       </c>
       <c r="U13" s="5" t="s">
         <v>50</v>
@@ -6012,7 +6012,7 @@
         <v>52</v>
       </c>
       <c r="Z13" s="7">
-        <v>1372.91</v>
+        <v>1426.25</v>
       </c>
       <c r="AA13" s="7">
         <v>0</v>
@@ -6022,20 +6022,20 @@
       </c>
       <c r="AC13" s="6"/>
       <c r="AD13" s="7">
-        <v>1372.91</v>
+        <v>1426.25</v>
       </c>
       <c r="AE13" s="4">
-        <v>73</v>
+        <v>99</v>
       </c>
       <c r="AF13" s="5" t="s">
-        <v>85</v>
+        <v>90</v>
       </c>
       <c r="AG13" s="5"/>
       <c r="AH13" s="5"/>
       <c r="AI13" s="5"/>
       <c r="AJ13" s="4"/>
       <c r="AK13" s="5" t="s">
-        <v>70</v>
+        <v>138</v>
       </c>
       <c r="AL13" s="5" t="s">
         <v>92</v>
@@ -6047,27 +6047,27 @@
         <v>56</v>
       </c>
       <c r="AO13" s="5" t="s">
-        <v>132</v>
+        <v>139</v>
       </c>
     </row>
     <row r="14" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A14" s="2" t="s">
-        <v>129</v>
-      </c>
-      <c r="B14" s="15" t="s">
-        <v>673</v>
+        <v>94</v>
+      </c>
+      <c r="B14" s="2" t="s">
+        <v>140</v>
       </c>
       <c r="C14" s="3">
-        <v>46266</v>
+        <v>46190</v>
       </c>
       <c r="D14" s="4">
-        <v>563732700</v>
+        <v>558264075</v>
       </c>
       <c r="E14" s="5" t="s">
-        <v>133</v>
+        <v>141</v>
       </c>
       <c r="F14" s="6">
-        <v>46143</v>
+        <v>46146</v>
       </c>
       <c r="G14" s="5" t="s">
         <v>134</v>
@@ -6076,28 +6076,28 @@
         <v>134</v>
       </c>
       <c r="I14" s="5" t="s">
-        <v>135</v>
+        <v>142</v>
       </c>
       <c r="J14" s="5" t="s">
-        <v>136</v>
+        <v>143</v>
       </c>
       <c r="K14" s="3">
-        <v>46276</v>
+        <v>46252</v>
       </c>
       <c r="L14" s="12">
-        <f t="shared" ca="1" si="0"/>
-        <v>226</v>
+        <f ca="1">IF($O14="","",$O14-TODAY())</f>
+        <v>229</v>
       </c>
       <c r="M14" s="12">
-        <f t="shared" ref="M14:M22" ca="1" si="2">IF($C14="","",$C14+365-TODAY())</f>
-        <v>349</v>
+        <f ca="1">IF($C14="","",$C14+365-TODAY())</f>
+        <v>273</v>
       </c>
       <c r="N14" s="12">
-        <f t="shared" ref="N14:N22" ca="1" si="3">IF($C14="","",$C14+120-TODAY())</f>
-        <v>104</v>
+        <f ca="1">IF($C14="","",$C14+120-TODAY())</f>
+        <v>28</v>
       </c>
       <c r="O14" s="6">
-        <v>46508</v>
+        <v>46511</v>
       </c>
       <c r="P14" s="5" t="s">
         <v>51</v>
@@ -6121,10 +6121,10 @@
       <c r="W14" s="5"/>
       <c r="X14" s="5"/>
       <c r="Y14" s="5" t="s">
-        <v>52</v>
+        <v>144</v>
       </c>
       <c r="Z14" s="7">
-        <v>1426.25</v>
+        <v>1822.52</v>
       </c>
       <c r="AA14" s="7">
         <v>0</v>
@@ -6132,25 +6132,27 @@
       <c r="AB14" s="7">
         <v>0</v>
       </c>
-      <c r="AC14" s="6"/>
+      <c r="AC14" s="6">
+        <v>46190</v>
+      </c>
       <c r="AD14" s="7">
-        <v>1426.25</v>
+        <v>1822.52</v>
       </c>
       <c r="AE14" s="4">
-        <v>99</v>
+        <v>96</v>
       </c>
       <c r="AF14" s="5" t="s">
-        <v>90</v>
+        <v>145</v>
       </c>
       <c r="AG14" s="5"/>
       <c r="AH14" s="5"/>
       <c r="AI14" s="5"/>
       <c r="AJ14" s="4"/>
       <c r="AK14" s="5" t="s">
-        <v>138</v>
+        <v>70</v>
       </c>
       <c r="AL14" s="5" t="s">
-        <v>92</v>
+        <v>71</v>
       </c>
       <c r="AM14" s="6">
         <v>46182</v>
@@ -6159,57 +6161,57 @@
         <v>56</v>
       </c>
       <c r="AO14" s="5" t="s">
-        <v>139</v>
+        <v>146</v>
       </c>
     </row>
     <row r="15" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A15" s="2" t="s">
-        <v>94</v>
+        <v>41</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>140</v>
+        <v>147</v>
       </c>
       <c r="C15" s="3">
-        <v>46190</v>
+        <v>46196</v>
       </c>
       <c r="D15" s="4">
-        <v>558264075</v>
+        <v>558264882</v>
       </c>
       <c r="E15" s="5" t="s">
-        <v>141</v>
+        <v>148</v>
       </c>
       <c r="F15" s="6">
-        <v>46146</v>
+        <v>46147</v>
       </c>
       <c r="G15" s="5" t="s">
-        <v>134</v>
+        <v>149</v>
       </c>
       <c r="H15" s="5" t="s">
         <v>134</v>
       </c>
       <c r="I15" s="5" t="s">
-        <v>142</v>
+        <v>149</v>
       </c>
       <c r="J15" s="5" t="s">
-        <v>143</v>
+        <v>136</v>
       </c>
       <c r="K15" s="3">
-        <v>46252</v>
+        <v>46227</v>
       </c>
       <c r="L15" s="12">
-        <f t="shared" ca="1" si="0"/>
-        <v>229</v>
+        <f ca="1">IF($O15="","",$O15-TODAY())</f>
+        <v>230</v>
       </c>
       <c r="M15" s="12">
-        <f t="shared" ca="1" si="2"/>
-        <v>273</v>
+        <f ca="1">IF($C15="","",$C15+365-TODAY())</f>
+        <v>279</v>
       </c>
       <c r="N15" s="12">
-        <f t="shared" ca="1" si="3"/>
-        <v>28</v>
+        <f ca="1">IF($C15="","",$C15+120-TODAY())</f>
+        <v>34</v>
       </c>
       <c r="O15" s="6">
-        <v>46511</v>
+        <v>46512</v>
       </c>
       <c r="P15" s="5" t="s">
         <v>51</v>
@@ -6233,33 +6235,35 @@
       <c r="W15" s="5"/>
       <c r="X15" s="5"/>
       <c r="Y15" s="5" t="s">
-        <v>144</v>
+        <v>52</v>
       </c>
       <c r="Z15" s="7">
-        <v>1822.52</v>
+        <v>1426.25</v>
       </c>
       <c r="AA15" s="7">
-        <v>0</v>
+        <v>1212.77</v>
       </c>
       <c r="AB15" s="7">
-        <v>0</v>
+        <v>170.09</v>
       </c>
       <c r="AC15" s="6">
-        <v>46190</v>
+        <v>46196</v>
       </c>
       <c r="AD15" s="7">
-        <v>1822.52</v>
+        <v>43.39</v>
       </c>
       <c r="AE15" s="4">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="AF15" s="5" t="s">
-        <v>145</v>
+        <v>61</v>
       </c>
       <c r="AG15" s="5"/>
       <c r="AH15" s="5"/>
       <c r="AI15" s="5"/>
-      <c r="AJ15" s="4"/>
+      <c r="AJ15" s="4">
+        <v>564131166</v>
+      </c>
       <c r="AK15" s="5" t="s">
         <v>70</v>
       </c>
@@ -6273,27 +6277,27 @@
         <v>56</v>
       </c>
       <c r="AO15" s="5" t="s">
-        <v>146</v>
+        <v>150</v>
       </c>
     </row>
     <row r="16" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A16" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="B16" s="2" t="s">
-        <v>147</v>
+        <v>129</v>
+      </c>
+      <c r="B16" s="15" t="s">
+        <v>672</v>
       </c>
       <c r="C16" s="3">
         <v>46196</v>
       </c>
       <c r="D16" s="4">
-        <v>558264882</v>
+        <v>558645693</v>
       </c>
       <c r="E16" s="5" t="s">
-        <v>148</v>
+        <v>151</v>
       </c>
       <c r="F16" s="6">
-        <v>46147</v>
+        <v>46149</v>
       </c>
       <c r="G16" s="5" t="s">
         <v>149</v>
@@ -6308,22 +6312,22 @@
         <v>136</v>
       </c>
       <c r="K16" s="3">
-        <v>46227</v>
+        <v>46252</v>
       </c>
       <c r="L16" s="12">
-        <f t="shared" ca="1" si="0"/>
-        <v>230</v>
+        <f ca="1">IF($O16="","",$O16-TODAY())</f>
+        <v>232</v>
       </c>
       <c r="M16" s="12">
-        <f t="shared" ca="1" si="2"/>
+        <f ca="1">IF($C16="","",$C16+365-TODAY())</f>
         <v>279</v>
       </c>
       <c r="N16" s="12">
-        <f t="shared" ca="1" si="3"/>
+        <f ca="1">IF($C16="","",$C16+120-TODAY())</f>
         <v>34</v>
       </c>
       <c r="O16" s="6">
-        <v>46512</v>
+        <v>46514</v>
       </c>
       <c r="P16" s="5" t="s">
         <v>51</v>
@@ -6365,7 +6369,7 @@
         <v>43.39</v>
       </c>
       <c r="AE16" s="4">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="AF16" s="5" t="s">
         <v>61</v>
@@ -6374,72 +6378,72 @@
       <c r="AH16" s="5"/>
       <c r="AI16" s="5"/>
       <c r="AJ16" s="4">
-        <v>564131166</v>
+        <v>564131691</v>
       </c>
       <c r="AK16" s="5" t="s">
-        <v>70</v>
+        <v>54</v>
       </c>
       <c r="AL16" s="5" t="s">
-        <v>71</v>
+        <v>55</v>
       </c>
       <c r="AM16" s="6">
-        <v>46182</v>
+        <v>46181</v>
       </c>
       <c r="AN16" s="5" t="s">
         <v>56</v>
       </c>
       <c r="AO16" s="5" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
     </row>
     <row r="17" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A17" s="2" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="B17" s="15" t="s">
-        <v>672</v>
+        <v>671</v>
       </c>
       <c r="C17" s="3">
-        <v>46196</v>
+        <v>46190</v>
       </c>
       <c r="D17" s="4">
-        <v>558645693</v>
+        <v>558588714</v>
       </c>
       <c r="E17" s="5" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="F17" s="6">
-        <v>46149</v>
+        <v>46150</v>
       </c>
       <c r="G17" s="5" t="s">
-        <v>149</v>
+        <v>134</v>
       </c>
       <c r="H17" s="5" t="s">
         <v>134</v>
       </c>
       <c r="I17" s="5" t="s">
-        <v>149</v>
+        <v>154</v>
       </c>
       <c r="J17" s="5" t="s">
-        <v>136</v>
+        <v>98</v>
       </c>
       <c r="K17" s="3">
         <v>46252</v>
       </c>
       <c r="L17" s="12">
-        <f t="shared" ca="1" si="0"/>
-        <v>232</v>
+        <f ca="1">IF($O17="","",$O17-TODAY())</f>
+        <v>233</v>
       </c>
       <c r="M17" s="12">
-        <f t="shared" ca="1" si="2"/>
-        <v>279</v>
+        <f ca="1">IF($C17="","",$C17+365-TODAY())</f>
+        <v>273</v>
       </c>
       <c r="N17" s="12">
-        <f t="shared" ca="1" si="3"/>
-        <v>34</v>
+        <f ca="1">IF($C17="","",$C17+120-TODAY())</f>
+        <v>28</v>
       </c>
       <c r="O17" s="6">
-        <v>46514</v>
+        <v>46515</v>
       </c>
       <c r="P17" s="5" t="s">
         <v>51</v>
@@ -6466,75 +6470,73 @@
         <v>52</v>
       </c>
       <c r="Z17" s="7">
-        <v>1426.25</v>
+        <v>1372.91</v>
       </c>
       <c r="AA17" s="7">
-        <v>1212.77</v>
+        <v>0</v>
       </c>
       <c r="AB17" s="7">
-        <v>170.09</v>
+        <v>0</v>
       </c>
       <c r="AC17" s="6">
-        <v>46196</v>
+        <v>46190</v>
       </c>
       <c r="AD17" s="7">
-        <v>43.39</v>
+        <v>1372.91</v>
       </c>
       <c r="AE17" s="4">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="AF17" s="5" t="s">
-        <v>61</v>
+        <v>99</v>
       </c>
       <c r="AG17" s="5"/>
       <c r="AH17" s="5"/>
       <c r="AI17" s="5"/>
-      <c r="AJ17" s="4">
-        <v>564131691</v>
-      </c>
+      <c r="AJ17" s="4"/>
       <c r="AK17" s="5" t="s">
-        <v>54</v>
+        <v>105</v>
       </c>
       <c r="AL17" s="5" t="s">
-        <v>55</v>
+        <v>92</v>
       </c>
       <c r="AM17" s="6">
-        <v>46181</v>
+        <v>46182</v>
       </c>
       <c r="AN17" s="5" t="s">
         <v>56</v>
       </c>
       <c r="AO17" s="5" t="s">
-        <v>152</v>
+        <v>155</v>
       </c>
     </row>
     <row r="18" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A18" s="2" t="s">
-        <v>130</v>
-      </c>
-      <c r="B18" s="15" t="s">
-        <v>671</v>
+        <v>129</v>
+      </c>
+      <c r="B18" s="2" t="s">
+        <v>156</v>
       </c>
       <c r="C18" s="3">
-        <v>46190</v>
+        <v>46196</v>
       </c>
       <c r="D18" s="4">
-        <v>558588714</v>
+        <v>558777279</v>
       </c>
       <c r="E18" s="5" t="s">
-        <v>153</v>
+        <v>157</v>
       </c>
       <c r="F18" s="6">
         <v>46150</v>
       </c>
       <c r="G18" s="5" t="s">
-        <v>134</v>
+        <v>149</v>
       </c>
       <c r="H18" s="5" t="s">
         <v>134</v>
       </c>
       <c r="I18" s="5" t="s">
-        <v>154</v>
+        <v>149</v>
       </c>
       <c r="J18" s="5" t="s">
         <v>98</v>
@@ -6543,16 +6545,16 @@
         <v>46252</v>
       </c>
       <c r="L18" s="12">
-        <f t="shared" ca="1" si="0"/>
+        <f ca="1">IF($O18="","",$O18-TODAY())</f>
         <v>233</v>
       </c>
       <c r="M18" s="12">
-        <f t="shared" ca="1" si="2"/>
-        <v>273</v>
+        <f ca="1">IF($C18="","",$C18+365-TODAY())</f>
+        <v>279</v>
       </c>
       <c r="N18" s="12">
-        <f t="shared" ca="1" si="3"/>
-        <v>28</v>
+        <f ca="1">IF($C18="","",$C18+120-TODAY())</f>
+        <v>34</v>
       </c>
       <c r="O18" s="6">
         <v>46515</v>
@@ -6585,32 +6587,34 @@
         <v>1372.91</v>
       </c>
       <c r="AA18" s="7">
-        <v>0</v>
+        <v>1173.9000000000001</v>
       </c>
       <c r="AB18" s="7">
-        <v>0</v>
+        <v>158.56</v>
       </c>
       <c r="AC18" s="6">
-        <v>46190</v>
+        <v>46196</v>
       </c>
       <c r="AD18" s="7">
-        <v>1372.91</v>
+        <v>40.450000000000003</v>
       </c>
       <c r="AE18" s="4">
         <v>92</v>
       </c>
       <c r="AF18" s="5" t="s">
-        <v>99</v>
+        <v>61</v>
       </c>
       <c r="AG18" s="5"/>
       <c r="AH18" s="5"/>
       <c r="AI18" s="5"/>
-      <c r="AJ18" s="4"/>
+      <c r="AJ18" s="4">
+        <v>564131697</v>
+      </c>
       <c r="AK18" s="5" t="s">
-        <v>105</v>
+        <v>70</v>
       </c>
       <c r="AL18" s="5" t="s">
-        <v>92</v>
+        <v>55</v>
       </c>
       <c r="AM18" s="6">
         <v>46182</v>
@@ -6619,27 +6623,27 @@
         <v>56</v>
       </c>
       <c r="AO18" s="5" t="s">
-        <v>155</v>
+        <v>158</v>
       </c>
     </row>
     <row r="19" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A19" s="2" t="s">
-        <v>129</v>
+        <v>41</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>156</v>
+        <v>147</v>
       </c>
       <c r="C19" s="3">
         <v>46196</v>
       </c>
       <c r="D19" s="4">
-        <v>558777279</v>
+        <v>559107561</v>
       </c>
       <c r="E19" s="5" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="F19" s="6">
-        <v>46150</v>
+        <v>46155</v>
       </c>
       <c r="G19" s="5" t="s">
         <v>149</v>
@@ -6651,25 +6655,25 @@
         <v>149</v>
       </c>
       <c r="J19" s="5" t="s">
-        <v>98</v>
+        <v>60</v>
       </c>
       <c r="K19" s="3">
-        <v>46252</v>
+        <v>46227</v>
       </c>
       <c r="L19" s="12">
-        <f t="shared" ca="1" si="0"/>
-        <v>233</v>
+        <f ca="1">IF($O19="","",$O19-TODAY())</f>
+        <v>238</v>
       </c>
       <c r="M19" s="12">
-        <f t="shared" ca="1" si="2"/>
+        <f ca="1">IF($C19="","",$C19+365-TODAY())</f>
         <v>279</v>
       </c>
       <c r="N19" s="12">
-        <f t="shared" ca="1" si="3"/>
+        <f ca="1">IF($C19="","",$C19+120-TODAY())</f>
         <v>34</v>
       </c>
       <c r="O19" s="6">
-        <v>46515</v>
+        <v>46520</v>
       </c>
       <c r="P19" s="5" t="s">
         <v>51</v>
@@ -6696,37 +6700,37 @@
         <v>52</v>
       </c>
       <c r="Z19" s="7">
-        <v>1372.91</v>
+        <v>1426.25</v>
       </c>
       <c r="AA19" s="7">
-        <v>1173.9000000000001</v>
+        <v>1228.08</v>
       </c>
       <c r="AB19" s="7">
-        <v>158.56</v>
+        <v>154.78</v>
       </c>
       <c r="AC19" s="6">
         <v>46196</v>
       </c>
       <c r="AD19" s="7">
-        <v>40.450000000000003</v>
+        <v>43.39</v>
       </c>
       <c r="AE19" s="4">
-        <v>92</v>
+        <v>87</v>
       </c>
       <c r="AF19" s="5" t="s">
-        <v>61</v>
+        <v>85</v>
       </c>
       <c r="AG19" s="5"/>
       <c r="AH19" s="5"/>
       <c r="AI19" s="5"/>
       <c r="AJ19" s="4">
-        <v>564131697</v>
+        <v>564131742</v>
       </c>
       <c r="AK19" s="5" t="s">
-        <v>70</v>
+        <v>105</v>
       </c>
       <c r="AL19" s="5" t="s">
-        <v>55</v>
+        <v>92</v>
       </c>
       <c r="AM19" s="6">
         <v>46182</v>
@@ -6735,7 +6739,7 @@
         <v>56</v>
       </c>
       <c r="AO19" s="5" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
     </row>
     <row r="20" spans="1:41" x14ac:dyDescent="0.25">
@@ -6749,13 +6753,13 @@
         <v>46196</v>
       </c>
       <c r="D20" s="4">
-        <v>559107561</v>
+        <v>559368713</v>
       </c>
       <c r="E20" s="5" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="F20" s="6">
-        <v>46155</v>
+        <v>46157</v>
       </c>
       <c r="G20" s="5" t="s">
         <v>149</v>
@@ -6773,19 +6777,19 @@
         <v>46227</v>
       </c>
       <c r="L20" s="12">
-        <f t="shared" ca="1" si="0"/>
-        <v>238</v>
+        <f ca="1">IF($O20="","",$O20-TODAY())</f>
+        <v>240</v>
       </c>
       <c r="M20" s="12">
-        <f t="shared" ca="1" si="2"/>
+        <f ca="1">IF($C20="","",$C20+365-TODAY())</f>
         <v>279</v>
       </c>
       <c r="N20" s="12">
-        <f t="shared" ca="1" si="3"/>
+        <f ca="1">IF($C20="","",$C20+120-TODAY())</f>
         <v>34</v>
       </c>
       <c r="O20" s="6">
-        <v>46520</v>
+        <v>46522</v>
       </c>
       <c r="P20" s="5" t="s">
         <v>51</v>
@@ -6827,16 +6831,16 @@
         <v>43.39</v>
       </c>
       <c r="AE20" s="4">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="AF20" s="5" t="s">
-        <v>85</v>
+        <v>90</v>
       </c>
       <c r="AG20" s="5"/>
       <c r="AH20" s="5"/>
       <c r="AI20" s="5"/>
       <c r="AJ20" s="4">
-        <v>564131742</v>
+        <v>564132159</v>
       </c>
       <c r="AK20" s="5" t="s">
         <v>105</v>
@@ -6851,7 +6855,7 @@
         <v>56</v>
       </c>
       <c r="AO20" s="5" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
     </row>
     <row r="21" spans="1:41" x14ac:dyDescent="0.25">
@@ -6865,13 +6869,13 @@
         <v>46196</v>
       </c>
       <c r="D21" s="4">
-        <v>559368713</v>
+        <v>560682170</v>
       </c>
       <c r="E21" s="5" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="F21" s="6">
-        <v>46157</v>
+        <v>46170</v>
       </c>
       <c r="G21" s="5" t="s">
         <v>149</v>
@@ -6883,25 +6887,25 @@
         <v>149</v>
       </c>
       <c r="J21" s="5" t="s">
-        <v>60</v>
+        <v>67</v>
       </c>
       <c r="K21" s="3">
         <v>46227</v>
       </c>
       <c r="L21" s="12">
-        <f t="shared" ca="1" si="0"/>
-        <v>240</v>
+        <f ca="1">IF($O21="","",$O21-TODAY())</f>
+        <v>253</v>
       </c>
       <c r="M21" s="12">
-        <f t="shared" ca="1" si="2"/>
+        <f ca="1">IF($C21="","",$C21+365-TODAY())</f>
         <v>279</v>
       </c>
       <c r="N21" s="12">
-        <f t="shared" ca="1" si="3"/>
+        <f ca="1">IF($C21="","",$C21+120-TODAY())</f>
         <v>34</v>
       </c>
       <c r="O21" s="6">
-        <v>46522</v>
+        <v>46535</v>
       </c>
       <c r="P21" s="5" t="s">
         <v>51</v>
@@ -6928,37 +6932,37 @@
         <v>52</v>
       </c>
       <c r="Z21" s="7">
-        <v>1426.25</v>
+        <v>976.64</v>
       </c>
       <c r="AA21" s="7">
-        <v>1228.08</v>
+        <v>844.25</v>
       </c>
       <c r="AB21" s="7">
-        <v>154.78</v>
+        <v>103.98</v>
       </c>
       <c r="AC21" s="6">
         <v>46196</v>
       </c>
       <c r="AD21" s="7">
-        <v>43.39</v>
+        <v>28.41</v>
       </c>
       <c r="AE21" s="4">
-        <v>85</v>
+        <v>72</v>
       </c>
       <c r="AF21" s="5" t="s">
-        <v>90</v>
+        <v>61</v>
       </c>
       <c r="AG21" s="5"/>
       <c r="AH21" s="5"/>
       <c r="AI21" s="5"/>
       <c r="AJ21" s="4">
-        <v>564132159</v>
+        <v>564133893</v>
       </c>
       <c r="AK21" s="5" t="s">
-        <v>105</v>
+        <v>164</v>
       </c>
       <c r="AL21" s="5" t="s">
-        <v>92</v>
+        <v>55</v>
       </c>
       <c r="AM21" s="6">
         <v>46182</v>
@@ -6967,7 +6971,7 @@
         <v>56</v>
       </c>
       <c r="AO21" s="5" t="s">
-        <v>162</v>
+        <v>165</v>
       </c>
     </row>
     <row r="22" spans="1:41" x14ac:dyDescent="0.25">
@@ -6975,64 +6979,56 @@
         <v>41</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>147</v>
-      </c>
-      <c r="C22" s="3">
-        <v>46196</v>
-      </c>
+        <v>166</v>
+      </c>
+      <c r="C22" s="3"/>
       <c r="D22" s="4">
-        <v>560682170</v>
+        <v>568553454</v>
       </c>
       <c r="E22" s="5" t="s">
-        <v>163</v>
+        <v>167</v>
       </c>
       <c r="F22" s="6">
-        <v>46170</v>
+        <v>46149</v>
       </c>
       <c r="G22" s="5" t="s">
-        <v>149</v>
+        <v>168</v>
       </c>
       <c r="H22" s="5" t="s">
-        <v>134</v>
+        <v>45</v>
       </c>
       <c r="I22" s="5" t="s">
-        <v>149</v>
+        <v>45</v>
       </c>
       <c r="J22" s="5" t="s">
-        <v>67</v>
+        <v>60</v>
       </c>
       <c r="K22" s="3">
-        <v>46227</v>
+        <v>46247</v>
       </c>
       <c r="L22" s="12">
-        <f t="shared" ca="1" si="0"/>
-        <v>253</v>
-      </c>
-      <c r="M22" s="12">
-        <f t="shared" ca="1" si="2"/>
-        <v>279</v>
-      </c>
-      <c r="N22" s="12">
-        <f t="shared" ca="1" si="3"/>
-        <v>34</v>
-      </c>
+        <f ca="1">IF($O22="","",$O22-TODAY())</f>
+        <v>-73</v>
+      </c>
+      <c r="M22" s="12"/>
+      <c r="N22" s="12"/>
       <c r="O22" s="6">
-        <v>46535</v>
+        <v>46209</v>
       </c>
       <c r="P22" s="5" t="s">
-        <v>51</v>
+        <v>169</v>
       </c>
       <c r="Q22" s="5" t="s">
-        <v>137</v>
+        <v>170</v>
       </c>
       <c r="R22" s="5" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="S22" s="5" t="s">
         <v>50</v>
       </c>
       <c r="T22" s="5" t="s">
-        <v>115</v>
+        <v>51</v>
       </c>
       <c r="U22" s="5" t="s">
         <v>50</v>
@@ -7044,22 +7040,20 @@
         <v>52</v>
       </c>
       <c r="Z22" s="7">
-        <v>976.64</v>
+        <v>1426.25</v>
       </c>
       <c r="AA22" s="7">
-        <v>844.25</v>
+        <v>0</v>
       </c>
       <c r="AB22" s="7">
-        <v>103.98</v>
-      </c>
-      <c r="AC22" s="6">
-        <v>46196</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="AC22" s="6"/>
       <c r="AD22" s="7">
-        <v>28.41</v>
+        <v>1426.25</v>
       </c>
       <c r="AE22" s="4">
-        <v>72</v>
+        <v>93</v>
       </c>
       <c r="AF22" s="5" t="s">
         <v>61</v>
@@ -7067,11 +7061,9 @@
       <c r="AG22" s="5"/>
       <c r="AH22" s="5"/>
       <c r="AI22" s="5"/>
-      <c r="AJ22" s="4">
-        <v>564133893</v>
-      </c>
+      <c r="AJ22" s="4"/>
       <c r="AK22" s="5" t="s">
-        <v>164</v>
+        <v>86</v>
       </c>
       <c r="AL22" s="5" t="s">
         <v>55</v>
@@ -7083,7 +7075,7 @@
         <v>56</v>
       </c>
       <c r="AO22" s="5" t="s">
-        <v>165</v>
+        <v>171</v>
       </c>
     </row>
     <row r="23" spans="1:41" x14ac:dyDescent="0.25">
@@ -7091,23 +7083,25 @@
         <v>41</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>166</v>
-      </c>
-      <c r="C23" s="3"/>
+        <v>172</v>
+      </c>
+      <c r="C23" s="3">
+        <v>46217</v>
+      </c>
       <c r="D23" s="4">
-        <v>568553454</v>
+        <v>559861642</v>
       </c>
       <c r="E23" s="5" t="s">
-        <v>167</v>
+        <v>173</v>
       </c>
       <c r="F23" s="6">
-        <v>46149</v>
+        <v>46161</v>
       </c>
       <c r="G23" s="5" t="s">
-        <v>168</v>
+        <v>174</v>
       </c>
       <c r="H23" s="5" t="s">
-        <v>45</v>
+        <v>174</v>
       </c>
       <c r="I23" s="5" t="s">
         <v>45</v>
@@ -7119,22 +7113,28 @@
         <v>46247</v>
       </c>
       <c r="L23" s="12">
-        <f t="shared" ca="1" si="0"/>
-        <v>-73</v>
-      </c>
-      <c r="M23" s="12"/>
-      <c r="N23" s="12"/>
+        <f ca="1">IF($O23="","",$O23-TODAY())</f>
+        <v>-61</v>
+      </c>
+      <c r="M23" s="12">
+        <f ca="1">IF($C23="","",$C23+365-TODAY())</f>
+        <v>300</v>
+      </c>
+      <c r="N23" s="12">
+        <f ca="1">IF($C23="","",$C23+365-TODAY())</f>
+        <v>300</v>
+      </c>
       <c r="O23" s="6">
-        <v>46209</v>
+        <v>46221</v>
       </c>
       <c r="P23" s="5" t="s">
         <v>169</v>
       </c>
       <c r="Q23" s="5" t="s">
-        <v>170</v>
+        <v>175</v>
       </c>
       <c r="R23" s="5" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="S23" s="5" t="s">
         <v>50</v>
@@ -7160,12 +7160,14 @@
       <c r="AB23" s="7">
         <v>0</v>
       </c>
-      <c r="AC23" s="6"/>
+      <c r="AC23" s="6">
+        <v>46217</v>
+      </c>
       <c r="AD23" s="7">
         <v>1426.25</v>
       </c>
       <c r="AE23" s="4">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="AF23" s="5" t="s">
         <v>61</v>
@@ -7175,45 +7177,45 @@
       <c r="AI23" s="5"/>
       <c r="AJ23" s="4"/>
       <c r="AK23" s="5" t="s">
-        <v>86</v>
+        <v>70</v>
       </c>
       <c r="AL23" s="5" t="s">
-        <v>55</v>
+        <v>71</v>
       </c>
       <c r="AM23" s="6">
-        <v>46182</v>
+        <v>46181</v>
       </c>
       <c r="AN23" s="5" t="s">
         <v>56</v>
       </c>
       <c r="AO23" s="5" t="s">
-        <v>171</v>
+        <v>176</v>
       </c>
     </row>
     <row r="24" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A24" s="2" t="s">
-        <v>41</v>
+        <v>129</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>172</v>
+        <v>180</v>
       </c>
       <c r="C24" s="3">
-        <v>46217</v>
+        <v>46216</v>
       </c>
       <c r="D24" s="4">
-        <v>559861642</v>
+        <v>559340053</v>
       </c>
       <c r="E24" s="5" t="s">
-        <v>173</v>
+        <v>181</v>
       </c>
       <c r="F24" s="6">
-        <v>46161</v>
+        <v>46154</v>
       </c>
       <c r="G24" s="5" t="s">
-        <v>174</v>
+        <v>149</v>
       </c>
       <c r="H24" s="5" t="s">
-        <v>174</v>
+        <v>149</v>
       </c>
       <c r="I24" s="5" t="s">
         <v>45</v>
@@ -7222,28 +7224,28 @@
         <v>60</v>
       </c>
       <c r="K24" s="3">
-        <v>46247</v>
+        <v>46245</v>
       </c>
       <c r="L24" s="12">
-        <f t="shared" ca="1" si="0"/>
-        <v>-61</v>
+        <f ca="1">IF($O24="","",$O24-TODAY())</f>
+        <v>-38</v>
       </c>
       <c r="M24" s="12">
         <f ca="1">IF($C24="","",$C24+365-TODAY())</f>
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="N24" s="12">
         <f ca="1">IF($C24="","",$C24+365-TODAY())</f>
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="O24" s="6">
-        <v>46221</v>
+        <v>46244</v>
       </c>
       <c r="P24" s="5" t="s">
-        <v>169</v>
+        <v>47</v>
       </c>
       <c r="Q24" s="5" t="s">
-        <v>175</v>
+        <v>182</v>
       </c>
       <c r="R24" s="5" t="s">
         <v>51</v>
@@ -7273,13 +7275,13 @@
         <v>0</v>
       </c>
       <c r="AC24" s="6">
-        <v>46217</v>
+        <v>46216</v>
       </c>
       <c r="AD24" s="7">
-        <v>1426.25</v>
+        <v>1144.3</v>
       </c>
       <c r="AE24" s="4">
-        <v>81</v>
+        <v>88</v>
       </c>
       <c r="AF24" s="5" t="s">
         <v>61</v>
@@ -7295,82 +7297,64 @@
         <v>71</v>
       </c>
       <c r="AM24" s="6">
-        <v>46181</v>
+        <v>46180</v>
       </c>
       <c r="AN24" s="5" t="s">
         <v>56</v>
       </c>
       <c r="AO24" s="5" t="s">
-        <v>176</v>
+        <v>183</v>
       </c>
     </row>
     <row r="25" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A25" s="2" t="s">
-        <v>129</v>
+        <v>94</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>130</v>
+        <v>184</v>
       </c>
       <c r="C25" s="3">
-        <v>46233</v>
+        <v>46191</v>
       </c>
       <c r="D25" s="4">
-        <v>558482837</v>
+        <v>558331839</v>
       </c>
       <c r="E25" s="5" t="s">
-        <v>177</v>
+        <v>185</v>
       </c>
       <c r="F25" s="6">
         <v>46148</v>
       </c>
       <c r="G25" s="5" t="s">
-        <v>75</v>
+        <v>186</v>
       </c>
       <c r="H25" s="5" t="s">
-        <v>75</v>
+        <v>186</v>
       </c>
       <c r="I25" s="5" t="s">
         <v>45</v>
       </c>
       <c r="J25" s="5" t="s">
-        <v>136</v>
+        <v>60</v>
       </c>
       <c r="K25" s="3">
-        <v>46246</v>
-      </c>
-      <c r="L25" s="12">
-        <f t="shared" ca="1" si="0"/>
-        <v>-44</v>
-      </c>
-      <c r="M25" s="12">
-        <f ca="1">IF($C25="","",$C25+180-TODAY())</f>
-        <v>131</v>
-      </c>
-      <c r="N25" s="12">
-        <f ca="1">IF($C25="","",$C25+365-TODAY())</f>
-        <v>316</v>
-      </c>
-      <c r="O25" s="6">
-        <v>46238</v>
-      </c>
-      <c r="P25" s="5" t="s">
-        <v>47</v>
-      </c>
+        <v>46252</v>
+      </c>
+      <c r="L25" s="4" t="str">
+        <f ca="1">IF($O25="","",$O25-TODAY())</f>
+        <v/>
+      </c>
+      <c r="M25" s="4"/>
+      <c r="N25" s="4"/>
+      <c r="O25" s="6"/>
+      <c r="P25" s="5"/>
       <c r="Q25" s="5" t="s">
-        <v>77</v>
-      </c>
-      <c r="R25" s="5" t="s">
-        <v>49</v>
-      </c>
-      <c r="S25" s="5" t="s">
-        <v>50</v>
-      </c>
-      <c r="T25" s="5" t="s">
-        <v>51</v>
-      </c>
-      <c r="U25" s="5" t="s">
-        <v>50</v>
-      </c>
+        <v>187</v>
+      </c>
+      <c r="R25" s="5"/>
+      <c r="S25" s="5"/>
+      <c r="T25" s="5"/>
+      <c r="U25" s="5"/>
       <c r="V25" s="5"/>
       <c r="W25" s="5"/>
       <c r="X25" s="5"/>
@@ -7386,7 +7370,9 @@
       <c r="AB25" s="7">
         <v>0</v>
       </c>
-      <c r="AC25" s="6"/>
+      <c r="AC25" s="6">
+        <v>46191</v>
+      </c>
       <c r="AD25" s="7">
         <v>1426.25</v>
       </c>
@@ -7394,95 +7380,73 @@
         <v>94</v>
       </c>
       <c r="AF25" s="5" t="s">
-        <v>178</v>
+        <v>85</v>
       </c>
       <c r="AG25" s="5"/>
       <c r="AH25" s="5"/>
       <c r="AI25" s="5"/>
       <c r="AJ25" s="4"/>
       <c r="AK25" s="5" t="s">
-        <v>91</v>
+        <v>188</v>
       </c>
       <c r="AL25" s="5" t="s">
-        <v>55</v>
+        <v>92</v>
       </c>
       <c r="AM25" s="6">
-        <v>46217</v>
+        <v>46182</v>
       </c>
       <c r="AN25" s="5" t="s">
         <v>56</v>
       </c>
       <c r="AO25" s="5" t="s">
-        <v>179</v>
+        <v>189</v>
       </c>
     </row>
     <row r="26" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A26" s="2" t="s">
-        <v>129</v>
+        <v>190</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>180</v>
-      </c>
-      <c r="C26" s="3">
-        <v>46216</v>
-      </c>
+        <v>191</v>
+      </c>
+      <c r="C26" s="3"/>
       <c r="D26" s="4">
-        <v>559340053</v>
+        <v>558642005</v>
       </c>
       <c r="E26" s="5" t="s">
-        <v>181</v>
+        <v>192</v>
       </c>
       <c r="F26" s="6">
-        <v>46154</v>
+        <v>46150</v>
       </c>
       <c r="G26" s="5" t="s">
-        <v>149</v>
+        <v>193</v>
       </c>
       <c r="H26" s="5" t="s">
-        <v>149</v>
+        <v>193</v>
       </c>
       <c r="I26" s="5" t="s">
         <v>45</v>
       </c>
       <c r="J26" s="5" t="s">
-        <v>60</v>
-      </c>
-      <c r="K26" s="3">
-        <v>46245</v>
-      </c>
-      <c r="L26" s="12">
-        <f t="shared" ca="1" si="0"/>
-        <v>-38</v>
-      </c>
-      <c r="M26" s="12">
-        <f ca="1">IF($C26="","",$C26+365-TODAY())</f>
-        <v>299</v>
-      </c>
-      <c r="N26" s="12">
-        <f ca="1">IF($C26="","",$C26+365-TODAY())</f>
-        <v>299</v>
-      </c>
-      <c r="O26" s="6">
-        <v>46244</v>
-      </c>
-      <c r="P26" s="5" t="s">
-        <v>47</v>
-      </c>
+        <v>194</v>
+      </c>
+      <c r="K26" s="3"/>
+      <c r="L26" s="4" t="str">
+        <f ca="1">IF($O26="","",$O26-TODAY())</f>
+        <v/>
+      </c>
+      <c r="M26" s="4"/>
+      <c r="N26" s="4"/>
+      <c r="O26" s="6"/>
+      <c r="P26" s="5"/>
       <c r="Q26" s="5" t="s">
-        <v>182</v>
-      </c>
-      <c r="R26" s="5" t="s">
-        <v>51</v>
-      </c>
-      <c r="S26" s="5" t="s">
-        <v>50</v>
-      </c>
-      <c r="T26" s="5" t="s">
-        <v>51</v>
-      </c>
-      <c r="U26" s="5" t="s">
-        <v>50</v>
-      </c>
+        <v>187</v>
+      </c>
+      <c r="R26" s="5"/>
+      <c r="S26" s="5"/>
+      <c r="T26" s="5"/>
+      <c r="U26" s="5"/>
       <c r="V26" s="5"/>
       <c r="W26" s="5"/>
       <c r="X26" s="5"/>
@@ -7490,7 +7454,7 @@
         <v>52</v>
       </c>
       <c r="Z26" s="7">
-        <v>1426.25</v>
+        <v>1029.98</v>
       </c>
       <c r="AA26" s="7">
         <v>0</v>
@@ -7498,36 +7462,34 @@
       <c r="AB26" s="7">
         <v>0</v>
       </c>
-      <c r="AC26" s="6">
-        <v>46216</v>
-      </c>
+      <c r="AC26" s="6"/>
       <c r="AD26" s="7">
-        <v>1144.3</v>
+        <v>1029.98</v>
       </c>
       <c r="AE26" s="4">
-        <v>88</v>
+        <v>92</v>
       </c>
       <c r="AF26" s="5" t="s">
-        <v>61</v>
+        <v>85</v>
       </c>
       <c r="AG26" s="5"/>
       <c r="AH26" s="5"/>
       <c r="AI26" s="5"/>
       <c r="AJ26" s="4"/>
       <c r="AK26" s="5" t="s">
-        <v>70</v>
+        <v>188</v>
       </c>
       <c r="AL26" s="5" t="s">
-        <v>71</v>
+        <v>92</v>
       </c>
       <c r="AM26" s="6">
-        <v>46180</v>
+        <v>46188</v>
       </c>
       <c r="AN26" s="5" t="s">
         <v>56</v>
       </c>
       <c r="AO26" s="5" t="s">
-        <v>183</v>
+        <v>195</v>
       </c>
     </row>
     <row r="27" spans="1:41" x14ac:dyDescent="0.25">
@@ -7541,13 +7503,13 @@
         <v>46191</v>
       </c>
       <c r="D27" s="4">
-        <v>558331839</v>
+        <v>559338687</v>
       </c>
       <c r="E27" s="5" t="s">
-        <v>185</v>
+        <v>196</v>
       </c>
       <c r="F27" s="6">
-        <v>46148</v>
+        <v>46157</v>
       </c>
       <c r="G27" s="5" t="s">
         <v>186</v>
@@ -7559,13 +7521,13 @@
         <v>45</v>
       </c>
       <c r="J27" s="5" t="s">
-        <v>60</v>
+        <v>136</v>
       </c>
       <c r="K27" s="3">
         <v>46252</v>
       </c>
       <c r="L27" s="4" t="str">
-        <f t="shared" ca="1" si="0"/>
+        <f ca="1">IF($O27="","",$O27-TODAY())</f>
         <v/>
       </c>
       <c r="M27" s="4"/>
@@ -7601,63 +7563,67 @@
         <v>1426.25</v>
       </c>
       <c r="AE27" s="4">
-        <v>94</v>
+        <v>85</v>
       </c>
       <c r="AF27" s="5" t="s">
-        <v>85</v>
+        <v>61</v>
       </c>
       <c r="AG27" s="5"/>
       <c r="AH27" s="5"/>
       <c r="AI27" s="5"/>
       <c r="AJ27" s="4"/>
       <c r="AK27" s="5" t="s">
-        <v>188</v>
+        <v>197</v>
       </c>
       <c r="AL27" s="5" t="s">
-        <v>92</v>
+        <v>55</v>
       </c>
       <c r="AM27" s="6">
-        <v>46182</v>
+        <v>46181</v>
       </c>
       <c r="AN27" s="5" t="s">
         <v>56</v>
       </c>
       <c r="AO27" s="5" t="s">
-        <v>189</v>
+        <v>198</v>
       </c>
     </row>
     <row r="28" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A28" s="2" t="s">
-        <v>190</v>
+        <v>94</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>191</v>
-      </c>
-      <c r="C28" s="3"/>
+        <v>184</v>
+      </c>
+      <c r="C28" s="3">
+        <v>46191</v>
+      </c>
       <c r="D28" s="4">
-        <v>558642005</v>
+        <v>560178907</v>
       </c>
       <c r="E28" s="5" t="s">
-        <v>192</v>
+        <v>199</v>
       </c>
       <c r="F28" s="6">
-        <v>46150</v>
+        <v>46164</v>
       </c>
       <c r="G28" s="5" t="s">
-        <v>193</v>
+        <v>186</v>
       </c>
       <c r="H28" s="5" t="s">
-        <v>193</v>
+        <v>186</v>
       </c>
       <c r="I28" s="5" t="s">
         <v>45</v>
       </c>
       <c r="J28" s="5" t="s">
-        <v>194</v>
-      </c>
-      <c r="K28" s="3"/>
+        <v>60</v>
+      </c>
+      <c r="K28" s="3">
+        <v>46252</v>
+      </c>
       <c r="L28" s="4" t="str">
-        <f t="shared" ca="1" si="0"/>
+        <f ca="1">IF($O28="","",$O28-TODAY())</f>
         <v/>
       </c>
       <c r="M28" s="4"/>
@@ -7678,7 +7644,7 @@
         <v>52</v>
       </c>
       <c r="Z28" s="7">
-        <v>1029.98</v>
+        <v>1426.25</v>
       </c>
       <c r="AA28" s="7">
         <v>0</v>
@@ -7686,34 +7652,38 @@
       <c r="AB28" s="7">
         <v>0</v>
       </c>
-      <c r="AC28" s="6"/>
+      <c r="AC28" s="6">
+        <v>46191</v>
+      </c>
       <c r="AD28" s="7">
-        <v>1029.98</v>
+        <v>1426.25</v>
       </c>
       <c r="AE28" s="4">
-        <v>92</v>
+        <v>78</v>
       </c>
       <c r="AF28" s="5" t="s">
-        <v>85</v>
-      </c>
-      <c r="AG28" s="5"/>
+        <v>78</v>
+      </c>
+      <c r="AG28" s="5" t="s">
+        <v>79</v>
+      </c>
       <c r="AH28" s="5"/>
       <c r="AI28" s="5"/>
       <c r="AJ28" s="4"/>
       <c r="AK28" s="5" t="s">
-        <v>188</v>
+        <v>91</v>
       </c>
       <c r="AL28" s="5" t="s">
-        <v>92</v>
+        <v>55</v>
       </c>
       <c r="AM28" s="6">
-        <v>46188</v>
+        <v>46182</v>
       </c>
       <c r="AN28" s="5" t="s">
         <v>56</v>
       </c>
       <c r="AO28" s="5" t="s">
-        <v>195</v>
+        <v>200</v>
       </c>
     </row>
     <row r="29" spans="1:41" x14ac:dyDescent="0.25">
@@ -7727,13 +7697,13 @@
         <v>46191</v>
       </c>
       <c r="D29" s="4">
-        <v>559338687</v>
-      </c>
-      <c r="E29" s="5" t="s">
-        <v>196</v>
+        <v>560590155</v>
+      </c>
+      <c r="E29" s="16" t="s">
+        <v>201</v>
       </c>
       <c r="F29" s="6">
-        <v>46157</v>
+        <v>46170</v>
       </c>
       <c r="G29" s="5" t="s">
         <v>186</v>
@@ -7751,7 +7721,7 @@
         <v>46252</v>
       </c>
       <c r="L29" s="4" t="str">
-        <f t="shared" ca="1" si="0"/>
+        <f ca="1">IF($O29="","",$O29-TODAY())</f>
         <v/>
       </c>
       <c r="M29" s="4"/>
@@ -7787,7 +7757,7 @@
         <v>1426.25</v>
       </c>
       <c r="AE29" s="4">
-        <v>85</v>
+        <v>72</v>
       </c>
       <c r="AF29" s="5" t="s">
         <v>61</v>
@@ -7803,51 +7773,51 @@
         <v>55</v>
       </c>
       <c r="AM29" s="6">
-        <v>46181</v>
+        <v>46182</v>
       </c>
       <c r="AN29" s="5" t="s">
         <v>56</v>
       </c>
       <c r="AO29" s="5" t="s">
-        <v>198</v>
+        <v>202</v>
       </c>
     </row>
     <row r="30" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A30" s="2" t="s">
-        <v>94</v>
-      </c>
-      <c r="B30" s="2" t="s">
-        <v>184</v>
+        <v>129</v>
+      </c>
+      <c r="B30" s="15" t="s">
+        <v>670</v>
       </c>
       <c r="C30" s="3">
-        <v>46191</v>
+        <v>46253</v>
       </c>
       <c r="D30" s="4">
-        <v>560178907</v>
+        <v>567670697</v>
       </c>
       <c r="E30" s="5" t="s">
-        <v>199</v>
+        <v>203</v>
       </c>
       <c r="F30" s="6">
-        <v>46164</v>
+        <v>46170</v>
       </c>
       <c r="G30" s="5" t="s">
-        <v>186</v>
+        <v>204</v>
       </c>
       <c r="H30" s="5" t="s">
-        <v>186</v>
+        <v>204</v>
       </c>
       <c r="I30" s="5" t="s">
         <v>45</v>
       </c>
       <c r="J30" s="5" t="s">
-        <v>60</v>
+        <v>136</v>
       </c>
       <c r="K30" s="3">
-        <v>46252</v>
+        <v>46262</v>
       </c>
       <c r="L30" s="4" t="str">
-        <f t="shared" ca="1" si="0"/>
+        <f ca="1">IF($O30="","",$O30-TODAY())</f>
         <v/>
       </c>
       <c r="M30" s="4"/>
@@ -7876,76 +7846,68 @@
       <c r="AB30" s="7">
         <v>0</v>
       </c>
-      <c r="AC30" s="6">
-        <v>46191</v>
-      </c>
+      <c r="AC30" s="6"/>
       <c r="AD30" s="7">
         <v>1426.25</v>
       </c>
       <c r="AE30" s="4">
-        <v>78</v>
+        <v>72</v>
       </c>
       <c r="AF30" s="5" t="s">
-        <v>78</v>
-      </c>
-      <c r="AG30" s="5" t="s">
-        <v>79</v>
-      </c>
+        <v>61</v>
+      </c>
+      <c r="AG30" s="5"/>
       <c r="AH30" s="5"/>
       <c r="AI30" s="5"/>
       <c r="AJ30" s="4"/>
       <c r="AK30" s="5" t="s">
-        <v>91</v>
+        <v>54</v>
       </c>
       <c r="AL30" s="5" t="s">
         <v>55</v>
       </c>
       <c r="AM30" s="6">
-        <v>46182</v>
+        <v>46180</v>
       </c>
       <c r="AN30" s="5" t="s">
         <v>56</v>
       </c>
       <c r="AO30" s="5" t="s">
-        <v>200</v>
+        <v>205</v>
       </c>
     </row>
     <row r="31" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A31" s="2" t="s">
-        <v>94</v>
+        <v>190</v>
       </c>
       <c r="B31" s="2" t="s">
-        <v>184</v>
-      </c>
-      <c r="C31" s="3">
-        <v>46191</v>
-      </c>
+        <v>191</v>
+      </c>
+      <c r="C31" s="3"/>
       <c r="D31" s="4">
-        <v>560590155</v>
-      </c>
-      <c r="E31" s="16" t="s">
-        <v>201</v>
+        <v>560692149</v>
+      </c>
+      <c r="E31" s="5" t="s">
+        <v>206</v>
       </c>
       <c r="F31" s="6">
-        <v>46170</v>
+        <v>46171</v>
       </c>
       <c r="G31" s="5" t="s">
-        <v>186</v>
+        <v>193</v>
       </c>
       <c r="H31" s="5" t="s">
-        <v>186</v>
+        <v>193</v>
       </c>
       <c r="I31" s="5" t="s">
         <v>45</v>
       </c>
       <c r="J31" s="5" t="s">
-        <v>136</v>
-      </c>
-      <c r="K31" s="3">
-        <v>46252</v>
-      </c>
+        <v>194</v>
+      </c>
+      <c r="K31" s="3"/>
       <c r="L31" s="4" t="str">
-        <f t="shared" ca="1" si="0"/>
+        <f ca="1">IF($O31="","",$O31-TODAY())</f>
         <v/>
       </c>
       <c r="M31" s="4"/>
@@ -7966,7 +7928,7 @@
         <v>52</v>
       </c>
       <c r="Z31" s="7">
-        <v>1426.25</v>
+        <v>1029.98</v>
       </c>
       <c r="AA31" s="7">
         <v>0</v>
@@ -7974,27 +7936,25 @@
       <c r="AB31" s="7">
         <v>0</v>
       </c>
-      <c r="AC31" s="6">
-        <v>46191</v>
-      </c>
+      <c r="AC31" s="6"/>
       <c r="AD31" s="7">
-        <v>1426.25</v>
+        <v>1029.98</v>
       </c>
       <c r="AE31" s="4">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="AF31" s="5" t="s">
-        <v>61</v>
+        <v>85</v>
       </c>
       <c r="AG31" s="5"/>
       <c r="AH31" s="5"/>
       <c r="AI31" s="5"/>
       <c r="AJ31" s="4"/>
       <c r="AK31" s="5" t="s">
-        <v>197</v>
+        <v>105</v>
       </c>
       <c r="AL31" s="5" t="s">
-        <v>55</v>
+        <v>92</v>
       </c>
       <c r="AM31" s="6">
         <v>46182</v>
@@ -8003,196 +7963,12 @@
         <v>56</v>
       </c>
       <c r="AO31" s="5" t="s">
-        <v>202</v>
-      </c>
-    </row>
-    <row r="32" spans="1:41" x14ac:dyDescent="0.25">
-      <c r="A32" s="2" t="s">
-        <v>129</v>
-      </c>
-      <c r="B32" s="15" t="s">
-        <v>670</v>
-      </c>
-      <c r="C32" s="3">
-        <v>46253</v>
-      </c>
-      <c r="D32" s="4">
-        <v>567670697</v>
-      </c>
-      <c r="E32" s="5" t="s">
-        <v>203</v>
-      </c>
-      <c r="F32" s="6">
-        <v>46170</v>
-      </c>
-      <c r="G32" s="5" t="s">
-        <v>204</v>
-      </c>
-      <c r="H32" s="5" t="s">
-        <v>204</v>
-      </c>
-      <c r="I32" s="5" t="s">
-        <v>45</v>
-      </c>
-      <c r="J32" s="5" t="s">
-        <v>136</v>
-      </c>
-      <c r="K32" s="3">
-        <v>46262</v>
-      </c>
-      <c r="L32" s="4" t="str">
-        <f t="shared" ca="1" si="0"/>
-        <v/>
-      </c>
-      <c r="M32" s="4"/>
-      <c r="N32" s="4"/>
-      <c r="O32" s="6"/>
-      <c r="P32" s="5"/>
-      <c r="Q32" s="5" t="s">
-        <v>187</v>
-      </c>
-      <c r="R32" s="5"/>
-      <c r="S32" s="5"/>
-      <c r="T32" s="5"/>
-      <c r="U32" s="5"/>
-      <c r="V32" s="5"/>
-      <c r="W32" s="5"/>
-      <c r="X32" s="5"/>
-      <c r="Y32" s="5" t="s">
-        <v>52</v>
-      </c>
-      <c r="Z32" s="7">
-        <v>1426.25</v>
-      </c>
-      <c r="AA32" s="7">
-        <v>0</v>
-      </c>
-      <c r="AB32" s="7">
-        <v>0</v>
-      </c>
-      <c r="AC32" s="6"/>
-      <c r="AD32" s="7">
-        <v>1426.25</v>
-      </c>
-      <c r="AE32" s="4">
-        <v>72</v>
-      </c>
-      <c r="AF32" s="5" t="s">
-        <v>61</v>
-      </c>
-      <c r="AG32" s="5"/>
-      <c r="AH32" s="5"/>
-      <c r="AI32" s="5"/>
-      <c r="AJ32" s="4"/>
-      <c r="AK32" s="5" t="s">
-        <v>54</v>
-      </c>
-      <c r="AL32" s="5" t="s">
-        <v>55</v>
-      </c>
-      <c r="AM32" s="6">
-        <v>46180</v>
-      </c>
-      <c r="AN32" s="5" t="s">
-        <v>56</v>
-      </c>
-      <c r="AO32" s="5" t="s">
-        <v>205</v>
-      </c>
-    </row>
-    <row r="33" spans="1:41" x14ac:dyDescent="0.25">
-      <c r="A33" s="2" t="s">
-        <v>190</v>
-      </c>
-      <c r="B33" s="2" t="s">
-        <v>191</v>
-      </c>
-      <c r="C33" s="3"/>
-      <c r="D33" s="4">
-        <v>560692149</v>
-      </c>
-      <c r="E33" s="5" t="s">
-        <v>206</v>
-      </c>
-      <c r="F33" s="6">
-        <v>46171</v>
-      </c>
-      <c r="G33" s="5" t="s">
-        <v>193</v>
-      </c>
-      <c r="H33" s="5" t="s">
-        <v>193</v>
-      </c>
-      <c r="I33" s="5" t="s">
-        <v>45</v>
-      </c>
-      <c r="J33" s="5" t="s">
-        <v>194</v>
-      </c>
-      <c r="K33" s="3"/>
-      <c r="L33" s="4" t="str">
-        <f t="shared" ca="1" si="0"/>
-        <v/>
-      </c>
-      <c r="M33" s="4"/>
-      <c r="N33" s="4"/>
-      <c r="O33" s="6"/>
-      <c r="P33" s="5"/>
-      <c r="Q33" s="5" t="s">
-        <v>187</v>
-      </c>
-      <c r="R33" s="5"/>
-      <c r="S33" s="5"/>
-      <c r="T33" s="5"/>
-      <c r="U33" s="5"/>
-      <c r="V33" s="5"/>
-      <c r="W33" s="5"/>
-      <c r="X33" s="5"/>
-      <c r="Y33" s="5" t="s">
-        <v>52</v>
-      </c>
-      <c r="Z33" s="7">
-        <v>1029.98</v>
-      </c>
-      <c r="AA33" s="7">
-        <v>0</v>
-      </c>
-      <c r="AB33" s="7">
-        <v>0</v>
-      </c>
-      <c r="AC33" s="6"/>
-      <c r="AD33" s="7">
-        <v>1029.98</v>
-      </c>
-      <c r="AE33" s="4">
-        <v>71</v>
-      </c>
-      <c r="AF33" s="5" t="s">
-        <v>85</v>
-      </c>
-      <c r="AG33" s="5"/>
-      <c r="AH33" s="5"/>
-      <c r="AI33" s="5"/>
-      <c r="AJ33" s="4"/>
-      <c r="AK33" s="5" t="s">
-        <v>105</v>
-      </c>
-      <c r="AL33" s="5" t="s">
-        <v>92</v>
-      </c>
-      <c r="AM33" s="6">
-        <v>46182</v>
-      </c>
-      <c r="AN33" s="5" t="s">
-        <v>56</v>
-      </c>
-      <c r="AO33" s="5" t="s">
         <v>207</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AO33" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
-  <conditionalFormatting sqref="L2:L33 O2:U33">
+  <autoFilter ref="A1:AO31" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
+  <conditionalFormatting sqref="L2:L31 O2:U31">
     <cfRule type="expression" dxfId="94" priority="1">
       <formula>AND($L2&lt;&gt;"", $L2&gt;=0, $L2&lt;=5)</formula>
     </cfRule>
@@ -8209,7 +7985,7 @@
       <formula>$L2=""</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="M2:M33">
+  <conditionalFormatting sqref="M2:M31">
     <cfRule type="expression" dxfId="89" priority="6">
       <formula>AND($M2&lt;&gt;"", $M2&gt;=0, $M2&lt;=5)</formula>
     </cfRule>
@@ -8226,7 +8002,7 @@
       <formula>$M2=""</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="N2:N33">
+  <conditionalFormatting sqref="N2:N31">
     <cfRule type="expression" dxfId="84" priority="11">
       <formula>AND($N2&lt;&gt;"", $N2&gt;=0, $N2&lt;=5)</formula>
     </cfRule>
@@ -8244,7 +8020,7 @@
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" promptTitle="Claim Status" prompt="Pick a status, or type a new one." sqref="A2:A33" xr:uid="{00000000-0002-0000-0000-000000000000}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" promptTitle="Claim Status" prompt="Pick a status, or type a new one." sqref="A2:A31" xr:uid="{00000000-0002-0000-0000-000000000000}">
       <formula1>"Denied,Finalized,PAID,Pending,Received,Rejected"</formula1>
     </dataValidation>
   </dataValidations>
@@ -13436,7 +13212,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
-  <dimension ref="A1:AO24"/>
+  <dimension ref="A1:AO23"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="14" customWidth="1"/>
@@ -13637,7 +13413,7 @@
         <v>46247</v>
       </c>
       <c r="L2" s="12">
-        <f t="shared" ref="L2:L24" ca="1" si="0">IF($O2="","",$O2-TODAY())</f>
+        <f ca="1">IF($O2="","",$O2-TODAY())</f>
         <v>-36</v>
       </c>
       <c r="M2" s="12">
@@ -13751,7 +13527,7 @@
         <v>46252</v>
       </c>
       <c r="L3" s="12">
-        <f t="shared" ca="1" si="0"/>
+        <f ca="1">IF($O3="","",$O3-TODAY())</f>
         <v>-32</v>
       </c>
       <c r="M3" s="12">
@@ -13867,7 +13643,7 @@
         <v>46245</v>
       </c>
       <c r="L4" s="12">
-        <f t="shared" ca="1" si="0"/>
+        <f ca="1">IF($O4="","",$O4-TODAY())</f>
         <v>-30</v>
       </c>
       <c r="M4" s="12">
@@ -13985,7 +13761,7 @@
         <v>46245</v>
       </c>
       <c r="L5" s="12">
-        <f t="shared" ca="1" si="0"/>
+        <f ca="1">IF($O5="","",$O5-TODAY())</f>
         <v>-29</v>
       </c>
       <c r="M5" s="12">
@@ -14105,7 +13881,7 @@
         <v>46245</v>
       </c>
       <c r="L6" s="12">
-        <f t="shared" ca="1" si="0"/>
+        <f ca="1">IF($O6="","",$O6-TODAY())</f>
         <v>-24</v>
       </c>
       <c r="M6" s="12">
@@ -14219,7 +13995,7 @@
         <v>46250</v>
       </c>
       <c r="L7" s="12">
-        <f t="shared" ca="1" si="0"/>
+        <f ca="1">IF($O7="","",$O7-TODAY())</f>
         <v>-23</v>
       </c>
       <c r="M7" s="12">
@@ -14339,7 +14115,7 @@
         <v>46250</v>
       </c>
       <c r="L8" s="12">
-        <f t="shared" ca="1" si="0"/>
+        <f ca="1">IF($O8="","",$O8-TODAY())</f>
         <v>-19</v>
       </c>
       <c r="M8" s="12">
@@ -14455,7 +14231,7 @@
         <v>46250</v>
       </c>
       <c r="L9" s="12">
-        <f t="shared" ca="1" si="0"/>
+        <f ca="1">IF($O9="","",$O9-TODAY())</f>
         <v>-9</v>
       </c>
       <c r="M9" s="12">
@@ -14577,7 +14353,7 @@
         <v>46250</v>
       </c>
       <c r="L10" s="12">
-        <f t="shared" ca="1" si="0"/>
+        <f ca="1">IF($O10="","",$O10-TODAY())</f>
         <v>-6</v>
       </c>
       <c r="M10" s="12">
@@ -14693,7 +14469,7 @@
         <v>46250</v>
       </c>
       <c r="L11" s="12">
-        <f t="shared" ca="1" si="0"/>
+        <f ca="1">IF($O11="","",$O11-TODAY())</f>
         <v>-6</v>
       </c>
       <c r="M11" s="12">
@@ -14807,7 +14583,7 @@
         <v>46252</v>
       </c>
       <c r="L12" s="12">
-        <f t="shared" ca="1" si="0"/>
+        <f ca="1">IF($O12="","",$O12-TODAY())</f>
         <v>54</v>
       </c>
       <c r="M12" s="12">
@@ -14921,15 +14697,15 @@
         <v>46246</v>
       </c>
       <c r="L13" s="12">
-        <f t="shared" ca="1" si="0"/>
+        <f ca="1">IF($O13="","",$O13-TODAY())</f>
         <v>226</v>
       </c>
       <c r="M13" s="12">
-        <f t="shared" ref="M13:M19" ca="1" si="1">IF($C13="","",$C13+365-TODAY())</f>
+        <f ca="1">IF($C13="","",$C13+365-TODAY())</f>
         <v>240</v>
       </c>
       <c r="N13" s="12">
-        <f t="shared" ref="N13:N18" ca="1" si="2">IF($C13="","",$C13+120-TODAY())</f>
+        <f ca="1">IF($C13="","",$C13+120-TODAY())</f>
         <v>-5</v>
       </c>
       <c r="O13" s="6">
@@ -15037,15 +14813,15 @@
         <v>46254</v>
       </c>
       <c r="L14" s="12">
-        <f t="shared" ca="1" si="0"/>
+        <f ca="1">IF($O14="","",$O14-TODAY())</f>
         <v>229</v>
       </c>
       <c r="M14" s="12">
-        <f t="shared" ca="1" si="1"/>
+        <f ca="1">IF($C14="","",$C14+365-TODAY())</f>
         <v>244</v>
       </c>
       <c r="N14" s="12">
-        <f t="shared" ca="1" si="2"/>
+        <f ca="1">IF($C14="","",$C14+120-TODAY())</f>
         <v>-1</v>
       </c>
       <c r="O14" s="6">
@@ -15157,15 +14933,15 @@
         <v>46259</v>
       </c>
       <c r="L15" s="12">
-        <f t="shared" ca="1" si="0"/>
+        <f ca="1">IF($O15="","",$O15-TODAY())</f>
         <v>236</v>
       </c>
       <c r="M15" s="12">
-        <f t="shared" ca="1" si="1"/>
+        <f ca="1">IF($C15="","",$C15+365-TODAY())</f>
         <v>328</v>
       </c>
       <c r="N15" s="12">
-        <f t="shared" ca="1" si="2"/>
+        <f ca="1">IF($C15="","",$C15+120-TODAY())</f>
         <v>83</v>
       </c>
       <c r="O15" s="6">
@@ -15271,15 +15047,15 @@
         <v>46259</v>
       </c>
       <c r="L16" s="12">
-        <f t="shared" ca="1" si="0"/>
+        <f ca="1">IF($O16="","",$O16-TODAY())</f>
         <v>238</v>
       </c>
       <c r="M16" s="12">
-        <f t="shared" ca="1" si="1"/>
+        <f ca="1">IF($C16="","",$C16+365-TODAY())</f>
         <v>251</v>
       </c>
       <c r="N16" s="12">
-        <f t="shared" ca="1" si="2"/>
+        <f ca="1">IF($C16="","",$C16+120-TODAY())</f>
         <v>6</v>
       </c>
       <c r="O16" s="6">
@@ -15387,15 +15163,15 @@
         <v>46259</v>
       </c>
       <c r="L17" s="12">
-        <f t="shared" ca="1" si="0"/>
+        <f ca="1">IF($O17="","",$O17-TODAY())</f>
         <v>240</v>
       </c>
       <c r="M17" s="12">
-        <f t="shared" ca="1" si="1"/>
+        <f ca="1">IF($C17="","",$C17+365-TODAY())</f>
         <v>251</v>
       </c>
       <c r="N17" s="12">
-        <f t="shared" ca="1" si="2"/>
+        <f ca="1">IF($C17="","",$C17+120-TODAY())</f>
         <v>6</v>
       </c>
       <c r="O17" s="6">
@@ -15505,15 +15281,15 @@
         <v>46256</v>
       </c>
       <c r="L18" s="12">
-        <f t="shared" ca="1" si="0"/>
+        <f ca="1">IF($O18="","",$O18-TODAY())</f>
         <v>254</v>
       </c>
       <c r="M18" s="12">
-        <f t="shared" ca="1" si="1"/>
+        <f ca="1">IF($C18="","",$C18+365-TODAY())</f>
         <v>272</v>
       </c>
       <c r="N18" s="12">
-        <f t="shared" ca="1" si="2"/>
+        <f ca="1">IF($C18="","",$C18+120-TODAY())</f>
         <v>27</v>
       </c>
       <c r="O18" s="6">
@@ -15621,11 +15397,11 @@
       </c>
       <c r="K19" s="3"/>
       <c r="L19" s="12">
-        <f t="shared" ca="1" si="0"/>
+        <f ca="1">IF($O19="","",$O19-TODAY())</f>
         <v>-74</v>
       </c>
       <c r="M19" s="12">
-        <f t="shared" ca="1" si="1"/>
+        <f ca="1">IF($C19="","",$C19+365-TODAY())</f>
         <v>245</v>
       </c>
       <c r="N19" s="12">
@@ -15737,7 +15513,7 @@
         <v>46256</v>
       </c>
       <c r="L20" s="12">
-        <f t="shared" ca="1" si="0"/>
+        <f ca="1">IF($O20="","",$O20-TODAY())</f>
         <v>-46</v>
       </c>
       <c r="M20" s="12">
@@ -15818,22 +15594,22 @@
     </row>
     <row r="21" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A21" s="2" t="s">
-        <v>129</v>
+        <v>94</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>130</v>
+        <v>549</v>
       </c>
       <c r="C21" s="3">
-        <v>46169</v>
+        <v>46197</v>
       </c>
       <c r="D21" s="4">
-        <v>559112699</v>
+        <v>558351506</v>
       </c>
       <c r="E21" s="5" t="s">
-        <v>544</v>
+        <v>411</v>
       </c>
       <c r="F21" s="6">
-        <v>46146</v>
+        <v>46148</v>
       </c>
       <c r="G21" s="5" t="s">
         <v>149</v>
@@ -15845,25 +15621,25 @@
         <v>45</v>
       </c>
       <c r="J21" s="5" t="s">
-        <v>545</v>
+        <v>476</v>
       </c>
       <c r="K21" s="3">
-        <v>46255</v>
+        <v>46177</v>
       </c>
       <c r="L21" s="12">
-        <f t="shared" ca="1" si="0"/>
-        <v>-46</v>
+        <f ca="1">IF($O21="","",$O21-TODAY())</f>
+        <v>-44</v>
       </c>
       <c r="M21" s="12">
         <f ca="1">IF($C21="","",$C21+365-TODAY())</f>
-        <v>252</v>
+        <v>280</v>
       </c>
       <c r="N21" s="12">
         <f ca="1">IF($C21="","",$C21+365-TODAY())</f>
-        <v>252</v>
+        <v>280</v>
       </c>
       <c r="O21" s="6">
-        <v>46236</v>
+        <v>46238</v>
       </c>
       <c r="P21" s="5" t="s">
         <v>47</v>
@@ -15890,7 +15666,7 @@
         <v>52</v>
       </c>
       <c r="Z21" s="7">
-        <v>3471.16</v>
+        <v>2493.33</v>
       </c>
       <c r="AA21" s="7">
         <v>0</v>
@@ -15898,36 +15674,38 @@
       <c r="AB21" s="7">
         <v>0</v>
       </c>
-      <c r="AC21" s="6"/>
+      <c r="AC21" s="6">
+        <v>46197</v>
+      </c>
       <c r="AD21" s="7">
-        <v>3471.16</v>
+        <v>2493.33</v>
       </c>
       <c r="AE21" s="4">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="AF21" s="5" t="s">
-        <v>546</v>
+        <v>273</v>
       </c>
       <c r="AG21" s="5" t="s">
-        <v>547</v>
+        <v>342</v>
       </c>
       <c r="AH21" s="5"/>
       <c r="AI21" s="5"/>
       <c r="AJ21" s="4"/>
       <c r="AK21" s="5" t="s">
-        <v>105</v>
+        <v>86</v>
       </c>
       <c r="AL21" s="5" t="s">
-        <v>427</v>
+        <v>436</v>
       </c>
       <c r="AM21" s="6">
-        <v>46157</v>
+        <v>46149</v>
       </c>
       <c r="AN21" s="5" t="s">
         <v>466</v>
       </c>
       <c r="AO21" s="5" t="s">
-        <v>548</v>
+        <v>550</v>
       </c>
     </row>
     <row r="22" spans="1:41" x14ac:dyDescent="0.25">
@@ -15935,55 +15713,55 @@
         <v>94</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>549</v>
+        <v>551</v>
       </c>
       <c r="C22" s="3">
-        <v>46197</v>
+        <v>46262</v>
       </c>
       <c r="D22" s="4">
-        <v>558351506</v>
+        <v>559605223</v>
       </c>
       <c r="E22" s="5" t="s">
-        <v>411</v>
+        <v>210</v>
       </c>
       <c r="F22" s="6">
-        <v>46148</v>
+        <v>46155</v>
       </c>
       <c r="G22" s="5" t="s">
-        <v>149</v>
+        <v>103</v>
       </c>
       <c r="H22" s="5" t="s">
-        <v>149</v>
+        <v>103</v>
       </c>
       <c r="I22" s="5" t="s">
         <v>45</v>
       </c>
       <c r="J22" s="5" t="s">
-        <v>476</v>
+        <v>552</v>
       </c>
       <c r="K22" s="3">
-        <v>46177</v>
+        <v>46244</v>
       </c>
       <c r="L22" s="12">
-        <f t="shared" ca="1" si="0"/>
-        <v>-44</v>
+        <f ca="1">IF($O22="","",$O22-TODAY())</f>
+        <v>-37</v>
       </c>
       <c r="M22" s="12">
         <f ca="1">IF($C22="","",$C22+365-TODAY())</f>
-        <v>280</v>
+        <v>345</v>
       </c>
       <c r="N22" s="12">
         <f ca="1">IF($C22="","",$C22+365-TODAY())</f>
-        <v>280</v>
+        <v>345</v>
       </c>
       <c r="O22" s="6">
-        <v>46238</v>
+        <v>46245</v>
       </c>
       <c r="P22" s="5" t="s">
         <v>47</v>
       </c>
       <c r="Q22" s="5" t="s">
-        <v>182</v>
+        <v>104</v>
       </c>
       <c r="R22" s="5" t="s">
         <v>51</v>
@@ -15997,14 +15775,16 @@
       <c r="U22" s="5" t="s">
         <v>50</v>
       </c>
-      <c r="V22" s="5"/>
+      <c r="V22" s="5" t="s">
+        <v>422</v>
+      </c>
       <c r="W22" s="5"/>
       <c r="X22" s="5"/>
       <c r="Y22" s="5" t="s">
         <v>52</v>
       </c>
       <c r="Z22" s="7">
-        <v>2493.33</v>
+        <v>20158.46</v>
       </c>
       <c r="AA22" s="7">
         <v>0</v>
@@ -16012,109 +15792,91 @@
       <c r="AB22" s="7">
         <v>0</v>
       </c>
-      <c r="AC22" s="6">
-        <v>46197</v>
-      </c>
+      <c r="AC22" s="6"/>
       <c r="AD22" s="7">
-        <v>2493.33</v>
+        <v>20158.46</v>
       </c>
       <c r="AE22" s="4">
-        <v>94</v>
+        <v>87</v>
       </c>
       <c r="AF22" s="5" t="s">
-        <v>273</v>
+        <v>553</v>
       </c>
       <c r="AG22" s="5" t="s">
-        <v>342</v>
-      </c>
-      <c r="AH22" s="5"/>
-      <c r="AI22" s="5"/>
+        <v>554</v>
+      </c>
+      <c r="AH22" s="5" t="s">
+        <v>555</v>
+      </c>
+      <c r="AI22" s="5" t="s">
+        <v>556</v>
+      </c>
       <c r="AJ22" s="4"/>
       <c r="AK22" s="5" t="s">
-        <v>86</v>
+        <v>164</v>
       </c>
       <c r="AL22" s="5" t="s">
         <v>436</v>
       </c>
       <c r="AM22" s="6">
-        <v>46149</v>
+        <v>46161</v>
       </c>
       <c r="AN22" s="5" t="s">
         <v>466</v>
       </c>
       <c r="AO22" s="5" t="s">
-        <v>550</v>
+        <v>557</v>
       </c>
     </row>
     <row r="23" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A23" s="2" t="s">
-        <v>94</v>
+        <v>130</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>551</v>
+        <v>558</v>
       </c>
       <c r="C23" s="3">
-        <v>46262</v>
+        <v>46168</v>
       </c>
       <c r="D23" s="4">
-        <v>559605223</v>
+        <v>558845008</v>
       </c>
       <c r="E23" s="5" t="s">
-        <v>210</v>
+        <v>416</v>
       </c>
       <c r="F23" s="6">
-        <v>46155</v>
+        <v>46146</v>
       </c>
       <c r="G23" s="5" t="s">
-        <v>103</v>
+        <v>186</v>
       </c>
       <c r="H23" s="5" t="s">
-        <v>103</v>
+        <v>186</v>
       </c>
       <c r="I23" s="5" t="s">
         <v>45</v>
       </c>
       <c r="J23" s="5" t="s">
-        <v>552</v>
-      </c>
-      <c r="K23" s="3">
-        <v>46244</v>
-      </c>
-      <c r="L23" s="12">
-        <f t="shared" ca="1" si="0"/>
-        <v>-37</v>
-      </c>
-      <c r="M23" s="12">
-        <f ca="1">IF($C23="","",$C23+365-TODAY())</f>
-        <v>345</v>
-      </c>
-      <c r="N23" s="12">
-        <f ca="1">IF($C23="","",$C23+365-TODAY())</f>
-        <v>345</v>
-      </c>
-      <c r="O23" s="6">
-        <v>46245</v>
-      </c>
-      <c r="P23" s="5" t="s">
-        <v>47</v>
-      </c>
+        <v>528</v>
+      </c>
+      <c r="K23" s="3"/>
+      <c r="L23" s="12" t="str">
+        <f ca="1">IF($O23="","",$O23-TODAY())</f>
+        <v/>
+      </c>
+      <c r="M23" s="12"/>
+      <c r="N23" s="12"/>
+      <c r="O23" s="6"/>
+      <c r="P23" s="5"/>
       <c r="Q23" s="5" t="s">
-        <v>104</v>
-      </c>
-      <c r="R23" s="5" t="s">
-        <v>51</v>
-      </c>
-      <c r="S23" s="5" t="s">
-        <v>50</v>
-      </c>
-      <c r="T23" s="5" t="s">
-        <v>51</v>
-      </c>
-      <c r="U23" s="5" t="s">
-        <v>50</v>
-      </c>
+        <v>187</v>
+      </c>
+      <c r="R23" s="5"/>
+      <c r="S23" s="5"/>
+      <c r="T23" s="5"/>
+      <c r="U23" s="5"/>
       <c r="V23" s="5" t="s">
-        <v>422</v>
+        <v>389</v>
       </c>
       <c r="W23" s="5"/>
       <c r="X23" s="5"/>
@@ -16122,7 +15884,7 @@
         <v>52</v>
       </c>
       <c r="Z23" s="7">
-        <v>20158.46</v>
+        <v>5614.63</v>
       </c>
       <c r="AA23" s="7">
         <v>0</v>
@@ -16132,137 +15894,37 @@
       </c>
       <c r="AC23" s="6"/>
       <c r="AD23" s="7">
-        <v>20158.46</v>
+        <v>5614.63</v>
       </c>
       <c r="AE23" s="4">
-        <v>87</v>
+        <v>96</v>
       </c>
       <c r="AF23" s="5" t="s">
-        <v>553</v>
-      </c>
-      <c r="AG23" s="5" t="s">
-        <v>554</v>
-      </c>
-      <c r="AH23" s="5" t="s">
-        <v>555</v>
-      </c>
-      <c r="AI23" s="5" t="s">
-        <v>556</v>
-      </c>
+        <v>251</v>
+      </c>
+      <c r="AG23" s="5"/>
+      <c r="AH23" s="5"/>
+      <c r="AI23" s="5"/>
       <c r="AJ23" s="4"/>
       <c r="AK23" s="5" t="s">
-        <v>164</v>
+        <v>252</v>
       </c>
       <c r="AL23" s="5" t="s">
-        <v>436</v>
+        <v>427</v>
       </c>
       <c r="AM23" s="6">
-        <v>46161</v>
+        <v>46155</v>
       </c>
       <c r="AN23" s="5" t="s">
         <v>466</v>
       </c>
       <c r="AO23" s="5" t="s">
-        <v>557</v>
-      </c>
-    </row>
-    <row r="24" spans="1:41" x14ac:dyDescent="0.25">
-      <c r="A24" s="2" t="s">
-        <v>130</v>
-      </c>
-      <c r="B24" s="2" t="s">
-        <v>558</v>
-      </c>
-      <c r="C24" s="3">
-        <v>46168</v>
-      </c>
-      <c r="D24" s="4">
-        <v>558845008</v>
-      </c>
-      <c r="E24" s="5" t="s">
-        <v>416</v>
-      </c>
-      <c r="F24" s="6">
-        <v>46146</v>
-      </c>
-      <c r="G24" s="5" t="s">
-        <v>186</v>
-      </c>
-      <c r="H24" s="5" t="s">
-        <v>186</v>
-      </c>
-      <c r="I24" s="5" t="s">
-        <v>45</v>
-      </c>
-      <c r="J24" s="5" t="s">
-        <v>528</v>
-      </c>
-      <c r="K24" s="3"/>
-      <c r="L24" s="12" t="str">
-        <f t="shared" ca="1" si="0"/>
-        <v/>
-      </c>
-      <c r="M24" s="12"/>
-      <c r="N24" s="12"/>
-      <c r="O24" s="6"/>
-      <c r="P24" s="5"/>
-      <c r="Q24" s="5" t="s">
-        <v>187</v>
-      </c>
-      <c r="R24" s="5"/>
-      <c r="S24" s="5"/>
-      <c r="T24" s="5"/>
-      <c r="U24" s="5"/>
-      <c r="V24" s="5" t="s">
-        <v>389</v>
-      </c>
-      <c r="W24" s="5"/>
-      <c r="X24" s="5"/>
-      <c r="Y24" s="5" t="s">
-        <v>52</v>
-      </c>
-      <c r="Z24" s="7">
-        <v>5614.63</v>
-      </c>
-      <c r="AA24" s="7">
-        <v>0</v>
-      </c>
-      <c r="AB24" s="7">
-        <v>0</v>
-      </c>
-      <c r="AC24" s="6"/>
-      <c r="AD24" s="7">
-        <v>5614.63</v>
-      </c>
-      <c r="AE24" s="4">
-        <v>96</v>
-      </c>
-      <c r="AF24" s="5" t="s">
-        <v>251</v>
-      </c>
-      <c r="AG24" s="5"/>
-      <c r="AH24" s="5"/>
-      <c r="AI24" s="5"/>
-      <c r="AJ24" s="4"/>
-      <c r="AK24" s="5" t="s">
-        <v>252</v>
-      </c>
-      <c r="AL24" s="5" t="s">
-        <v>427</v>
-      </c>
-      <c r="AM24" s="6">
-        <v>46155</v>
-      </c>
-      <c r="AN24" s="5" t="s">
-        <v>466</v>
-      </c>
-      <c r="AO24" s="5" t="s">
         <v>559</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AO24" xr:uid="{00000000-0009-0000-0000-000003000000}"/>
-  <conditionalFormatting sqref="L2:L24">
+  <autoFilter ref="A1:AO23" xr:uid="{00000000-0009-0000-0000-000003000000}"/>
+  <conditionalFormatting sqref="L2:L23">
     <cfRule type="expression" dxfId="39" priority="1">
       <formula>AND($L2&lt;&gt;"", $L2&gt;=0, $L2&lt;=5)</formula>
     </cfRule>
@@ -16279,7 +15941,7 @@
       <formula>$L2=""</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="M2:M24">
+  <conditionalFormatting sqref="M2:M23">
     <cfRule type="expression" dxfId="34" priority="6">
       <formula>AND($M2&lt;&gt;"", $M2&gt;=0, $M2&lt;=5)</formula>
     </cfRule>
@@ -16296,7 +15958,7 @@
       <formula>$M2=""</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="N2:N24">
+  <conditionalFormatting sqref="N2:N23">
     <cfRule type="expression" dxfId="29" priority="11">
       <formula>AND($N2&lt;&gt;"", $N2&gt;=0, $N2&lt;=5)</formula>
     </cfRule>
@@ -16313,7 +15975,7 @@
       <formula>$N2=""</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="O2:U24">
+  <conditionalFormatting sqref="O2:U23">
     <cfRule type="expression" dxfId="24" priority="16">
       <formula>AND($L2&lt;&gt;"", $L2&gt;=0, $L2&lt;=5)</formula>
     </cfRule>
@@ -16331,7 +15993,7 @@
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" promptTitle="Claim Status" prompt="Pick a status, or type a new one." sqref="A2:A24" xr:uid="{00000000-0002-0000-0300-000000000000}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" promptTitle="Claim Status" prompt="Pick a status, or type a new one." sqref="A2:A23" xr:uid="{00000000-0002-0000-0300-000000000000}">
       <formula1>"Denied,Finalized,PAID,Pending,Received,Rejected"</formula1>
     </dataValidation>
   </dataValidations>
@@ -16342,7 +16004,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
-  <dimension ref="A1:AO19"/>
+  <dimension ref="A1:AO16"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="14" customWidth="1"/>
@@ -16543,7 +16205,7 @@
         <v>46246</v>
       </c>
       <c r="L2" s="12">
-        <f t="shared" ref="L2:L19" ca="1" si="0">IF($O2="","",$O2-TODAY())</f>
+        <f ca="1">IF($O2="","",$O2-TODAY())</f>
         <v>-29</v>
       </c>
       <c r="M2" s="12">
@@ -16657,7 +16319,7 @@
         <v>46246</v>
       </c>
       <c r="L3" s="12">
-        <f t="shared" ca="1" si="0"/>
+        <f ca="1">IF($O3="","",$O3-TODAY())</f>
         <v>-29</v>
       </c>
       <c r="M3" s="12">
@@ -16739,64 +16401,64 @@
         <v>129</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>130</v>
+        <v>577</v>
       </c>
       <c r="C4" s="3">
-        <v>46244</v>
+        <v>46175</v>
       </c>
       <c r="D4" s="4">
-        <v>566566596</v>
+        <v>560711027</v>
       </c>
       <c r="E4" s="5" t="s">
-        <v>572</v>
+        <v>578</v>
       </c>
       <c r="F4" s="6">
-        <v>46163</v>
+        <v>46168</v>
       </c>
       <c r="G4" s="5" t="s">
-        <v>75</v>
+        <v>447</v>
       </c>
       <c r="H4" s="5" t="s">
-        <v>75</v>
+        <v>447</v>
       </c>
       <c r="I4" s="5" t="s">
         <v>45</v>
       </c>
       <c r="J4" s="5" t="s">
-        <v>573</v>
+        <v>579</v>
       </c>
       <c r="K4" s="3">
-        <v>46259</v>
+        <v>46251</v>
       </c>
       <c r="L4" s="12">
-        <f t="shared" ca="1" si="0"/>
-        <v>-29</v>
+        <f ca="1">IF($O4="","",$O4-TODAY())</f>
+        <v>-24</v>
       </c>
       <c r="M4" s="12">
-        <f ca="1">IF($C4="","",$C4+180-TODAY())</f>
-        <v>142</v>
+        <f ca="1">IF($F4="","",$F4+90-TODAY())</f>
+        <v>-24</v>
       </c>
       <c r="N4" s="12">
-        <f ca="1">IF($C4="","",$C4+365-TODAY())</f>
-        <v>327</v>
+        <f ca="1">IF($C4="","",$C4+60-TODAY())</f>
+        <v>-47</v>
       </c>
       <c r="O4" s="6">
-        <v>46253</v>
+        <v>46258</v>
       </c>
       <c r="P4" s="5" t="s">
         <v>47</v>
       </c>
       <c r="Q4" s="5" t="s">
-        <v>77</v>
+        <v>449</v>
       </c>
       <c r="R4" s="5" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="S4" s="5" t="s">
-        <v>50</v>
+        <v>234</v>
       </c>
       <c r="T4" s="5" t="s">
-        <v>51</v>
+        <v>169</v>
       </c>
       <c r="U4" s="5" t="s">
         <v>50</v>
@@ -16808,7 +16470,7 @@
         <v>52</v>
       </c>
       <c r="Z4" s="7">
-        <v>3822.49</v>
+        <v>1294.23</v>
       </c>
       <c r="AA4" s="7">
         <v>0</v>
@@ -16816,29 +16478,29 @@
       <c r="AB4" s="7">
         <v>0</v>
       </c>
-      <c r="AC4" s="6">
-        <v>46182</v>
-      </c>
+      <c r="AC4" s="6"/>
       <c r="AD4" s="7">
-        <v>3822.49</v>
+        <v>1294.23</v>
       </c>
       <c r="AE4" s="4">
-        <v>79</v>
+        <v>74</v>
       </c>
       <c r="AF4" s="5" t="s">
+        <v>580</v>
+      </c>
+      <c r="AG4" s="5" t="s">
         <v>574</v>
       </c>
-      <c r="AG4" s="5" t="s">
-        <v>575</v>
-      </c>
-      <c r="AH4" s="5"/>
+      <c r="AH4" s="5" t="s">
+        <v>258</v>
+      </c>
       <c r="AI4" s="5"/>
       <c r="AJ4" s="4"/>
       <c r="AK4" s="5" t="s">
-        <v>86</v>
+        <v>105</v>
       </c>
       <c r="AL4" s="5" t="s">
-        <v>564</v>
+        <v>92</v>
       </c>
       <c r="AM4" s="6">
         <v>46171</v>
@@ -16847,33 +16509,33 @@
         <v>565</v>
       </c>
       <c r="AO4" s="5" t="s">
-        <v>576</v>
+        <v>581</v>
       </c>
     </row>
     <row r="5" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
-        <v>129</v>
+        <v>94</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>577</v>
+        <v>582</v>
       </c>
       <c r="C5" s="3">
-        <v>46175</v>
+        <v>46181</v>
       </c>
       <c r="D5" s="4">
-        <v>560711027</v>
+        <v>560711490</v>
       </c>
       <c r="E5" s="5" t="s">
-        <v>578</v>
+        <v>583</v>
       </c>
       <c r="F5" s="6">
         <v>46168</v>
       </c>
       <c r="G5" s="5" t="s">
-        <v>447</v>
+        <v>394</v>
       </c>
       <c r="H5" s="5" t="s">
-        <v>447</v>
+        <v>394</v>
       </c>
       <c r="I5" s="5" t="s">
         <v>45</v>
@@ -16882,10 +16544,10 @@
         <v>579</v>
       </c>
       <c r="K5" s="3">
-        <v>46251</v>
+        <v>46250</v>
       </c>
       <c r="L5" s="12">
-        <f t="shared" ca="1" si="0"/>
+        <f ca="1">IF($O5="","",$O5-TODAY())</f>
         <v>-24</v>
       </c>
       <c r="M5" s="12">
@@ -16893,8 +16555,8 @@
         <v>-24</v>
       </c>
       <c r="N5" s="12">
-        <f ca="1">IF($C5="","",$C5+60-TODAY())</f>
-        <v>-47</v>
+        <f ca="1">IF($C5="","",$C5+180-TODAY())</f>
+        <v>79</v>
       </c>
       <c r="O5" s="6">
         <v>46258</v>
@@ -16903,7 +16565,7 @@
         <v>47</v>
       </c>
       <c r="Q5" s="5" t="s">
-        <v>449</v>
+        <v>396</v>
       </c>
       <c r="R5" s="5" t="s">
         <v>47</v>
@@ -16912,7 +16574,7 @@
         <v>234</v>
       </c>
       <c r="T5" s="5" t="s">
-        <v>169</v>
+        <v>49</v>
       </c>
       <c r="U5" s="5" t="s">
         <v>50</v>
@@ -16932,7 +16594,9 @@
       <c r="AB5" s="7">
         <v>0</v>
       </c>
-      <c r="AC5" s="6"/>
+      <c r="AC5" s="6">
+        <v>46181</v>
+      </c>
       <c r="AD5" s="7">
         <v>1294.23</v>
       </c>
@@ -16940,13 +16604,13 @@
         <v>74</v>
       </c>
       <c r="AF5" s="5" t="s">
-        <v>580</v>
+        <v>575</v>
       </c>
       <c r="AG5" s="5" t="s">
-        <v>574</v>
+        <v>584</v>
       </c>
       <c r="AH5" s="5" t="s">
-        <v>258</v>
+        <v>585</v>
       </c>
       <c r="AI5" s="5"/>
       <c r="AJ5" s="4"/>
@@ -16963,7 +16627,7 @@
         <v>565</v>
       </c>
       <c r="AO5" s="5" t="s">
-        <v>581</v>
+        <v>586</v>
       </c>
     </row>
     <row r="6" spans="1:41" x14ac:dyDescent="0.25">
@@ -16971,19 +16635,19 @@
         <v>94</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>582</v>
+        <v>587</v>
       </c>
       <c r="C6" s="3">
-        <v>46181</v>
+        <v>46177</v>
       </c>
       <c r="D6" s="4">
-        <v>560711490</v>
+        <v>560713422</v>
       </c>
       <c r="E6" s="5" t="s">
-        <v>583</v>
+        <v>588</v>
       </c>
       <c r="F6" s="6">
-        <v>46168</v>
+        <v>46169</v>
       </c>
       <c r="G6" s="5" t="s">
         <v>394</v>
@@ -16995,25 +16659,25 @@
         <v>45</v>
       </c>
       <c r="J6" s="5" t="s">
-        <v>579</v>
+        <v>589</v>
       </c>
       <c r="K6" s="3">
-        <v>46250</v>
+        <v>46251</v>
       </c>
       <c r="L6" s="12">
-        <f t="shared" ca="1" si="0"/>
-        <v>-24</v>
+        <f ca="1">IF($O6="","",$O6-TODAY())</f>
+        <v>-23</v>
       </c>
       <c r="M6" s="12">
         <f ca="1">IF($F6="","",$F6+90-TODAY())</f>
-        <v>-24</v>
+        <v>-23</v>
       </c>
       <c r="N6" s="12">
         <f ca="1">IF($C6="","",$C6+180-TODAY())</f>
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="O6" s="6">
-        <v>46258</v>
+        <v>46259</v>
       </c>
       <c r="P6" s="5" t="s">
         <v>47</v>
@@ -17040,7 +16704,7 @@
         <v>52</v>
       </c>
       <c r="Z6" s="7">
-        <v>1294.23</v>
+        <v>2173.29</v>
       </c>
       <c r="AA6" s="7">
         <v>0</v>
@@ -17049,30 +16713,32 @@
         <v>0</v>
       </c>
       <c r="AC6" s="6">
-        <v>46181</v>
+        <v>46177</v>
       </c>
       <c r="AD6" s="7">
-        <v>1294.23</v>
+        <v>2173.29</v>
       </c>
       <c r="AE6" s="4">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="AF6" s="5" t="s">
-        <v>575</v>
+        <v>590</v>
       </c>
       <c r="AG6" s="5" t="s">
-        <v>584</v>
+        <v>591</v>
       </c>
       <c r="AH6" s="5" t="s">
-        <v>585</v>
-      </c>
-      <c r="AI6" s="5"/>
+        <v>257</v>
+      </c>
+      <c r="AI6" s="5" t="s">
+        <v>592</v>
+      </c>
       <c r="AJ6" s="4"/>
       <c r="AK6" s="5" t="s">
-        <v>105</v>
+        <v>164</v>
       </c>
       <c r="AL6" s="5" t="s">
-        <v>92</v>
+        <v>593</v>
       </c>
       <c r="AM6" s="6">
         <v>46171</v>
@@ -17081,69 +16747,69 @@
         <v>565</v>
       </c>
       <c r="AO6" s="5" t="s">
-        <v>586</v>
+        <v>594</v>
       </c>
     </row>
     <row r="7" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
-        <v>94</v>
+        <v>129</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>587</v>
+        <v>595</v>
       </c>
       <c r="C7" s="3">
-        <v>46177</v>
+        <v>46185</v>
       </c>
       <c r="D7" s="4">
-        <v>560713422</v>
+        <v>560032270</v>
       </c>
       <c r="E7" s="5" t="s">
-        <v>588</v>
+        <v>596</v>
       </c>
       <c r="F7" s="6">
-        <v>46169</v>
+        <v>46147</v>
       </c>
       <c r="G7" s="5" t="s">
-        <v>394</v>
+        <v>119</v>
       </c>
       <c r="H7" s="5" t="s">
-        <v>394</v>
+        <v>119</v>
       </c>
       <c r="I7" s="5" t="s">
         <v>45</v>
       </c>
       <c r="J7" s="5" t="s">
-        <v>589</v>
+        <v>579</v>
       </c>
       <c r="K7" s="3">
-        <v>46251</v>
+        <v>46252</v>
       </c>
       <c r="L7" s="12">
-        <f t="shared" ca="1" si="0"/>
-        <v>-23</v>
+        <f ca="1">IF($O7="","",$O7-TODAY())</f>
+        <v>-15</v>
       </c>
       <c r="M7" s="12">
-        <f ca="1">IF($F7="","",$F7+90-TODAY())</f>
-        <v>-23</v>
+        <f ca="1">IF($C7="","",$C7+180-TODAY())</f>
+        <v>83</v>
       </c>
       <c r="N7" s="12">
         <f ca="1">IF($C7="","",$C7+180-TODAY())</f>
-        <v>75</v>
+        <v>83</v>
       </c>
       <c r="O7" s="6">
-        <v>46259</v>
+        <v>46267</v>
       </c>
       <c r="P7" s="5" t="s">
-        <v>47</v>
+        <v>115</v>
       </c>
       <c r="Q7" s="5" t="s">
-        <v>396</v>
+        <v>121</v>
       </c>
       <c r="R7" s="5" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="S7" s="5" t="s">
-        <v>234</v>
+        <v>50</v>
       </c>
       <c r="T7" s="5" t="s">
         <v>49</v>
@@ -17158,7 +16824,7 @@
         <v>52</v>
       </c>
       <c r="Z7" s="7">
-        <v>2173.29</v>
+        <v>1294.23</v>
       </c>
       <c r="AA7" s="7">
         <v>0</v>
@@ -17167,91 +16833,85 @@
         <v>0</v>
       </c>
       <c r="AC7" s="6">
-        <v>46177</v>
+        <v>46185</v>
       </c>
       <c r="AD7" s="7">
-        <v>2173.29</v>
+        <v>1294.23</v>
       </c>
       <c r="AE7" s="4">
-        <v>73</v>
+        <v>95</v>
       </c>
       <c r="AF7" s="5" t="s">
-        <v>590</v>
-      </c>
-      <c r="AG7" s="5" t="s">
-        <v>591</v>
-      </c>
-      <c r="AH7" s="5" t="s">
-        <v>257</v>
-      </c>
-      <c r="AI7" s="5" t="s">
-        <v>592</v>
-      </c>
+        <v>597</v>
+      </c>
+      <c r="AG7" s="5"/>
+      <c r="AH7" s="5"/>
+      <c r="AI7" s="5"/>
       <c r="AJ7" s="4"/>
       <c r="AK7" s="5" t="s">
-        <v>164</v>
+        <v>105</v>
       </c>
       <c r="AL7" s="5" t="s">
-        <v>593</v>
+        <v>92</v>
       </c>
       <c r="AM7" s="6">
-        <v>46171</v>
+        <v>46164</v>
       </c>
       <c r="AN7" s="5" t="s">
         <v>565</v>
       </c>
       <c r="AO7" s="5" t="s">
-        <v>594</v>
+        <v>598</v>
       </c>
     </row>
     <row r="8" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
-        <v>129</v>
+        <v>94</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>595</v>
+        <v>599</v>
       </c>
       <c r="C8" s="3">
-        <v>46185</v>
+        <v>46182</v>
       </c>
       <c r="D8" s="4">
-        <v>560032270</v>
+        <v>560058820</v>
       </c>
       <c r="E8" s="5" t="s">
-        <v>596</v>
+        <v>600</v>
       </c>
       <c r="F8" s="6">
-        <v>46147</v>
+        <v>46149</v>
       </c>
       <c r="G8" s="5" t="s">
-        <v>119</v>
+        <v>498</v>
       </c>
       <c r="H8" s="5" t="s">
-        <v>119</v>
+        <v>498</v>
       </c>
       <c r="I8" s="5" t="s">
         <v>45</v>
       </c>
       <c r="J8" s="5" t="s">
-        <v>579</v>
+        <v>562</v>
       </c>
       <c r="K8" s="3">
         <v>46252</v>
       </c>
       <c r="L8" s="12">
-        <f t="shared" ca="1" si="0"/>
-        <v>-15</v>
+        <f ca="1">IF($O8="","",$O8-TODAY())</f>
+        <v>-13</v>
       </c>
       <c r="M8" s="12">
         <f ca="1">IF($C8="","",$C8+180-TODAY())</f>
-        <v>83</v>
+        <v>80</v>
       </c>
       <c r="N8" s="12">
         <f ca="1">IF($C8="","",$C8+180-TODAY())</f>
-        <v>83</v>
+        <v>80</v>
       </c>
       <c r="O8" s="6">
-        <v>46267</v>
+        <v>46269</v>
       </c>
       <c r="P8" s="5" t="s">
         <v>115</v>
@@ -17278,7 +16938,7 @@
         <v>52</v>
       </c>
       <c r="Z8" s="7">
-        <v>1294.23</v>
+        <v>2528.2600000000002</v>
       </c>
       <c r="AA8" s="7">
         <v>0</v>
@@ -17286,27 +16946,29 @@
       <c r="AB8" s="7">
         <v>0</v>
       </c>
-      <c r="AC8" s="6">
-        <v>46185</v>
-      </c>
+      <c r="AC8" s="6"/>
       <c r="AD8" s="7">
-        <v>1294.23</v>
+        <v>2528.2600000000002</v>
       </c>
       <c r="AE8" s="4">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="AF8" s="5" t="s">
-        <v>597</v>
-      </c>
-      <c r="AG8" s="5"/>
-      <c r="AH8" s="5"/>
+        <v>257</v>
+      </c>
+      <c r="AG8" s="5" t="s">
+        <v>584</v>
+      </c>
+      <c r="AH8" s="5" t="s">
+        <v>563</v>
+      </c>
       <c r="AI8" s="5"/>
       <c r="AJ8" s="4"/>
       <c r="AK8" s="5" t="s">
-        <v>105</v>
+        <v>86</v>
       </c>
       <c r="AL8" s="5" t="s">
-        <v>92</v>
+        <v>564</v>
       </c>
       <c r="AM8" s="6">
         <v>46164</v>
@@ -17315,7 +16977,7 @@
         <v>565</v>
       </c>
       <c r="AO8" s="5" t="s">
-        <v>598</v>
+        <v>601</v>
       </c>
     </row>
     <row r="9" spans="1:41" x14ac:dyDescent="0.25">
@@ -17323,64 +16985,64 @@
         <v>94</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>599</v>
+        <v>602</v>
       </c>
       <c r="C9" s="3">
-        <v>46182</v>
+        <v>46171</v>
       </c>
       <c r="D9" s="4">
-        <v>560058820</v>
+        <v>560035724</v>
       </c>
       <c r="E9" s="5" t="s">
-        <v>600</v>
+        <v>603</v>
       </c>
       <c r="F9" s="6">
-        <v>46149</v>
+        <v>46147</v>
       </c>
       <c r="G9" s="5" t="s">
-        <v>498</v>
+        <v>134</v>
       </c>
       <c r="H9" s="5" t="s">
-        <v>498</v>
+        <v>134</v>
       </c>
       <c r="I9" s="5" t="s">
-        <v>45</v>
+        <v>330</v>
       </c>
       <c r="J9" s="5" t="s">
-        <v>562</v>
+        <v>604</v>
       </c>
       <c r="K9" s="3">
-        <v>46252</v>
+        <v>46257</v>
       </c>
       <c r="L9" s="12">
-        <f t="shared" ca="1" si="0"/>
-        <v>-13</v>
+        <f ca="1">IF($O9="","",$O9-TODAY())</f>
+        <v>230</v>
       </c>
       <c r="M9" s="12">
-        <f ca="1">IF($C9="","",$C9+180-TODAY())</f>
-        <v>80</v>
+        <f ca="1">IF($C9="","",$C9+365-TODAY())</f>
+        <v>254</v>
       </c>
       <c r="N9" s="12">
-        <f ca="1">IF($C9="","",$C9+180-TODAY())</f>
-        <v>80</v>
+        <f ca="1">IF($C9="","",$C9+120-TODAY())</f>
+        <v>9</v>
       </c>
       <c r="O9" s="6">
-        <v>46269</v>
+        <v>46512</v>
       </c>
       <c r="P9" s="5" t="s">
-        <v>115</v>
+        <v>51</v>
       </c>
       <c r="Q9" s="5" t="s">
-        <v>121</v>
+        <v>137</v>
       </c>
       <c r="R9" s="5" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="S9" s="5" t="s">
         <v>50</v>
       </c>
       <c r="T9" s="5" t="s">
-        <v>49</v>
+        <v>115</v>
       </c>
       <c r="U9" s="5" t="s">
         <v>50</v>
@@ -17392,7 +17054,7 @@
         <v>52</v>
       </c>
       <c r="Z9" s="7">
-        <v>2528.2600000000002</v>
+        <v>3822.49</v>
       </c>
       <c r="AA9" s="7">
         <v>0</v>
@@ -17400,29 +17062,31 @@
       <c r="AB9" s="7">
         <v>0</v>
       </c>
-      <c r="AC9" s="6"/>
+      <c r="AC9" s="6">
+        <v>46171</v>
+      </c>
       <c r="AD9" s="7">
-        <v>2528.2600000000002</v>
+        <v>3822.49</v>
       </c>
       <c r="AE9" s="4">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="AF9" s="5" t="s">
-        <v>257</v>
+        <v>575</v>
       </c>
       <c r="AG9" s="5" t="s">
         <v>584</v>
       </c>
       <c r="AH9" s="5" t="s">
-        <v>563</v>
+        <v>585</v>
       </c>
       <c r="AI9" s="5"/>
       <c r="AJ9" s="4"/>
       <c r="AK9" s="5" t="s">
-        <v>86</v>
+        <v>105</v>
       </c>
       <c r="AL9" s="5" t="s">
-        <v>564</v>
+        <v>92</v>
       </c>
       <c r="AM9" s="6">
         <v>46164</v>
@@ -17431,7 +17095,7 @@
         <v>565</v>
       </c>
       <c r="AO9" s="5" t="s">
-        <v>601</v>
+        <v>605</v>
       </c>
     </row>
     <row r="10" spans="1:41" x14ac:dyDescent="0.25">
@@ -17439,19 +17103,19 @@
         <v>94</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>602</v>
+        <v>606</v>
       </c>
       <c r="C10" s="3">
-        <v>46171</v>
+        <v>46203</v>
       </c>
       <c r="D10" s="4">
-        <v>560035724</v>
+        <v>560069379</v>
       </c>
       <c r="E10" s="5" t="s">
-        <v>603</v>
+        <v>607</v>
       </c>
       <c r="F10" s="6">
-        <v>46147</v>
+        <v>46154</v>
       </c>
       <c r="G10" s="5" t="s">
         <v>134</v>
@@ -17460,28 +17124,28 @@
         <v>134</v>
       </c>
       <c r="I10" s="5" t="s">
-        <v>330</v>
+        <v>66</v>
       </c>
       <c r="J10" s="5" t="s">
-        <v>604</v>
+        <v>608</v>
       </c>
       <c r="K10" s="3">
-        <v>46257</v>
+        <v>46259</v>
       </c>
       <c r="L10" s="12">
-        <f t="shared" ca="1" si="0"/>
-        <v>230</v>
+        <f ca="1">IF($O10="","",$O10-TODAY())</f>
+        <v>237</v>
       </c>
       <c r="M10" s="12">
-        <f t="shared" ref="M10:M15" ca="1" si="1">IF($C10="","",$C10+365-TODAY())</f>
-        <v>254</v>
+        <f ca="1">IF($C10="","",$C10+365-TODAY())</f>
+        <v>286</v>
       </c>
       <c r="N10" s="12">
         <f ca="1">IF($C10="","",$C10+120-TODAY())</f>
-        <v>9</v>
+        <v>41</v>
       </c>
       <c r="O10" s="6">
-        <v>46512</v>
+        <v>46519</v>
       </c>
       <c r="P10" s="5" t="s">
         <v>51</v>
@@ -17508,32 +17172,28 @@
         <v>52</v>
       </c>
       <c r="Z10" s="7">
-        <v>3822.49</v>
+        <v>879.06</v>
       </c>
       <c r="AA10" s="7">
         <v>0</v>
       </c>
       <c r="AB10" s="7">
-        <v>0</v>
+        <v>17.420000000000002</v>
       </c>
       <c r="AC10" s="6">
-        <v>46171</v>
+        <v>46203</v>
       </c>
       <c r="AD10" s="7">
-        <v>3822.49</v>
+        <v>879.06</v>
       </c>
       <c r="AE10" s="4">
-        <v>95</v>
+        <v>88</v>
       </c>
       <c r="AF10" s="5" t="s">
-        <v>575</v>
-      </c>
-      <c r="AG10" s="5" t="s">
-        <v>584</v>
-      </c>
-      <c r="AH10" s="5" t="s">
-        <v>585</v>
-      </c>
+        <v>609</v>
+      </c>
+      <c r="AG10" s="5"/>
+      <c r="AH10" s="5"/>
       <c r="AI10" s="5"/>
       <c r="AJ10" s="4"/>
       <c r="AK10" s="5" t="s">
@@ -17549,57 +17209,57 @@
         <v>565</v>
       </c>
       <c r="AO10" s="5" t="s">
-        <v>605</v>
+        <v>610</v>
       </c>
     </row>
     <row r="11" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A11" s="2" t="s">
-        <v>94</v>
-      </c>
-      <c r="B11" s="2" t="s">
-        <v>606</v>
+        <v>129</v>
+      </c>
+      <c r="B11" s="15" t="s">
+        <v>675</v>
       </c>
       <c r="C11" s="3">
-        <v>46203</v>
+        <v>46245</v>
       </c>
       <c r="D11" s="4">
-        <v>560069379</v>
+        <v>560072534</v>
       </c>
       <c r="E11" s="5" t="s">
-        <v>607</v>
+        <v>439</v>
       </c>
       <c r="F11" s="6">
-        <v>46154</v>
+        <v>46155</v>
       </c>
       <c r="G11" s="5" t="s">
-        <v>134</v>
+        <v>119</v>
       </c>
       <c r="H11" s="5" t="s">
         <v>134</v>
       </c>
       <c r="I11" s="5" t="s">
-        <v>66</v>
+        <v>119</v>
       </c>
       <c r="J11" s="5" t="s">
-        <v>608</v>
+        <v>604</v>
       </c>
       <c r="K11" s="3">
-        <v>46259</v>
+        <v>46258</v>
       </c>
       <c r="L11" s="12">
-        <f t="shared" ca="1" si="0"/>
-        <v>237</v>
+        <f ca="1">IF($O11="","",$O11-TODAY())</f>
+        <v>238</v>
       </c>
       <c r="M11" s="12">
-        <f t="shared" ca="1" si="1"/>
-        <v>286</v>
+        <f ca="1">IF($C11="","",$C11+365-TODAY())</f>
+        <v>328</v>
       </c>
       <c r="N11" s="12">
         <f ca="1">IF($C11="","",$C11+120-TODAY())</f>
-        <v>41</v>
+        <v>83</v>
       </c>
       <c r="O11" s="6">
-        <v>46519</v>
+        <v>46520</v>
       </c>
       <c r="P11" s="5" t="s">
         <v>51</v>
@@ -17626,35 +17286,37 @@
         <v>52</v>
       </c>
       <c r="Z11" s="7">
-        <v>879.06</v>
+        <v>3822.49</v>
       </c>
       <c r="AA11" s="7">
-        <v>0</v>
+        <v>3379.94</v>
       </c>
       <c r="AB11" s="7">
-        <v>17.420000000000002</v>
+        <v>347.58</v>
       </c>
       <c r="AC11" s="6">
-        <v>46203</v>
+        <v>46181</v>
       </c>
       <c r="AD11" s="7">
-        <v>879.06</v>
+        <v>94.97</v>
       </c>
       <c r="AE11" s="4">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="AF11" s="5" t="s">
-        <v>609</v>
+        <v>597</v>
       </c>
       <c r="AG11" s="5"/>
       <c r="AH11" s="5"/>
       <c r="AI11" s="5"/>
-      <c r="AJ11" s="4"/>
+      <c r="AJ11" s="4">
+        <v>563214016</v>
+      </c>
       <c r="AK11" s="5" t="s">
-        <v>105</v>
+        <v>164</v>
       </c>
       <c r="AL11" s="5" t="s">
-        <v>92</v>
+        <v>593</v>
       </c>
       <c r="AM11" s="6">
         <v>46164</v>
@@ -17663,57 +17325,57 @@
         <v>565</v>
       </c>
       <c r="AO11" s="5" t="s">
-        <v>610</v>
+        <v>611</v>
       </c>
     </row>
     <row r="12" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A12" s="2" t="s">
-        <v>129</v>
-      </c>
-      <c r="B12" s="15" t="s">
-        <v>675</v>
+        <v>94</v>
+      </c>
+      <c r="B12" s="2" t="s">
+        <v>602</v>
       </c>
       <c r="C12" s="3">
-        <v>46245</v>
+        <v>46178</v>
       </c>
       <c r="D12" s="4">
-        <v>560072534</v>
+        <v>560703801</v>
       </c>
       <c r="E12" s="5" t="s">
-        <v>439</v>
+        <v>612</v>
       </c>
       <c r="F12" s="6">
-        <v>46155</v>
+        <v>46161</v>
       </c>
       <c r="G12" s="5" t="s">
-        <v>119</v>
+        <v>134</v>
       </c>
       <c r="H12" s="5" t="s">
         <v>134</v>
       </c>
       <c r="I12" s="5" t="s">
-        <v>119</v>
+        <v>613</v>
       </c>
       <c r="J12" s="5" t="s">
-        <v>604</v>
+        <v>614</v>
       </c>
       <c r="K12" s="3">
-        <v>46258</v>
+        <v>46257</v>
       </c>
       <c r="L12" s="12">
-        <f t="shared" ca="1" si="0"/>
-        <v>238</v>
+        <f ca="1">IF($O12="","",$O12-TODAY())</f>
+        <v>244</v>
       </c>
       <c r="M12" s="12">
-        <f t="shared" ca="1" si="1"/>
-        <v>328</v>
+        <f ca="1">IF($C12="","",$C12+365-TODAY())</f>
+        <v>261</v>
       </c>
       <c r="N12" s="12">
         <f ca="1">IF($C12="","",$C12+120-TODAY())</f>
-        <v>83</v>
+        <v>16</v>
       </c>
       <c r="O12" s="6">
-        <v>46520</v>
+        <v>46526</v>
       </c>
       <c r="P12" s="5" t="s">
         <v>51</v>
@@ -17743,43 +17405,45 @@
         <v>3822.49</v>
       </c>
       <c r="AA12" s="7">
-        <v>3379.94</v>
+        <v>0</v>
       </c>
       <c r="AB12" s="7">
-        <v>347.58</v>
+        <v>0</v>
       </c>
       <c r="AC12" s="6">
-        <v>46181</v>
+        <v>46178</v>
       </c>
       <c r="AD12" s="7">
-        <v>94.97</v>
+        <v>3822.49</v>
       </c>
       <c r="AE12" s="4">
-        <v>87</v>
+        <v>81</v>
       </c>
       <c r="AF12" s="5" t="s">
-        <v>597</v>
-      </c>
-      <c r="AG12" s="5"/>
-      <c r="AH12" s="5"/>
+        <v>215</v>
+      </c>
+      <c r="AG12" s="5" t="s">
+        <v>585</v>
+      </c>
+      <c r="AH12" s="5" t="s">
+        <v>584</v>
+      </c>
       <c r="AI12" s="5"/>
-      <c r="AJ12" s="4">
-        <v>563214016</v>
-      </c>
+      <c r="AJ12" s="4"/>
       <c r="AK12" s="5" t="s">
-        <v>164</v>
+        <v>105</v>
       </c>
       <c r="AL12" s="5" t="s">
-        <v>593</v>
+        <v>92</v>
       </c>
       <c r="AM12" s="6">
-        <v>46164</v>
+        <v>46171</v>
       </c>
       <c r="AN12" s="5" t="s">
         <v>565</v>
       </c>
       <c r="AO12" s="5" t="s">
-        <v>611</v>
+        <v>615</v>
       </c>
     </row>
     <row r="13" spans="1:41" x14ac:dyDescent="0.25">
@@ -17787,19 +17451,19 @@
         <v>94</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>602</v>
+        <v>616</v>
       </c>
       <c r="C13" s="3">
         <v>46178</v>
       </c>
       <c r="D13" s="4">
-        <v>560703801</v>
+        <v>560707683</v>
       </c>
       <c r="E13" s="5" t="s">
-        <v>612</v>
+        <v>617</v>
       </c>
       <c r="F13" s="6">
-        <v>46161</v>
+        <v>46162</v>
       </c>
       <c r="G13" s="5" t="s">
         <v>134</v>
@@ -17808,20 +17472,20 @@
         <v>134</v>
       </c>
       <c r="I13" s="5" t="s">
-        <v>613</v>
+        <v>45</v>
       </c>
       <c r="J13" s="5" t="s">
-        <v>614</v>
+        <v>618</v>
       </c>
       <c r="K13" s="3">
         <v>46257</v>
       </c>
       <c r="L13" s="12">
-        <f t="shared" ca="1" si="0"/>
-        <v>244</v>
+        <f ca="1">IF($O13="","",$O13-TODAY())</f>
+        <v>245</v>
       </c>
       <c r="M13" s="12">
-        <f t="shared" ca="1" si="1"/>
+        <f ca="1">IF($C13="","",$C13+365-TODAY())</f>
         <v>261</v>
       </c>
       <c r="N13" s="12">
@@ -17829,7 +17493,7 @@
         <v>16</v>
       </c>
       <c r="O13" s="6">
-        <v>46526</v>
+        <v>46527</v>
       </c>
       <c r="P13" s="5" t="s">
         <v>51</v>
@@ -17856,7 +17520,7 @@
         <v>52</v>
       </c>
       <c r="Z13" s="7">
-        <v>3822.49</v>
+        <v>1649.2</v>
       </c>
       <c r="AA13" s="7">
         <v>0</v>
@@ -17868,27 +17532,23 @@
         <v>46178</v>
       </c>
       <c r="AD13" s="7">
-        <v>3822.49</v>
+        <v>1649.2</v>
       </c>
       <c r="AE13" s="4">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="AF13" s="5" t="s">
-        <v>215</v>
-      </c>
-      <c r="AG13" s="5" t="s">
-        <v>585</v>
-      </c>
-      <c r="AH13" s="5" t="s">
-        <v>584</v>
-      </c>
+        <v>575</v>
+      </c>
+      <c r="AG13" s="5"/>
+      <c r="AH13" s="5"/>
       <c r="AI13" s="5"/>
       <c r="AJ13" s="4"/>
       <c r="AK13" s="5" t="s">
-        <v>105</v>
+        <v>164</v>
       </c>
       <c r="AL13" s="5" t="s">
-        <v>92</v>
+        <v>593</v>
       </c>
       <c r="AM13" s="6">
         <v>46171</v>
@@ -17897,72 +17557,72 @@
         <v>565</v>
       </c>
       <c r="AO13" s="5" t="s">
-        <v>615</v>
+        <v>619</v>
       </c>
     </row>
     <row r="14" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A14" s="2" t="s">
-        <v>94</v>
+        <v>130</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>616</v>
+        <v>624</v>
       </c>
       <c r="C14" s="3">
-        <v>46178</v>
+        <v>46248</v>
       </c>
       <c r="D14" s="4">
-        <v>560707683</v>
+        <v>567453889</v>
       </c>
       <c r="E14" s="5" t="s">
-        <v>617</v>
+        <v>625</v>
       </c>
       <c r="F14" s="6">
-        <v>46162</v>
+        <v>46154</v>
       </c>
       <c r="G14" s="5" t="s">
-        <v>134</v>
+        <v>394</v>
       </c>
       <c r="H14" s="5" t="s">
-        <v>134</v>
+        <v>394</v>
       </c>
       <c r="I14" s="5" t="s">
         <v>45</v>
       </c>
       <c r="J14" s="5" t="s">
-        <v>618</v>
+        <v>562</v>
       </c>
       <c r="K14" s="3">
-        <v>46257</v>
+        <v>46237</v>
       </c>
       <c r="L14" s="12">
-        <f t="shared" ca="1" si="0"/>
-        <v>245</v>
+        <f ca="1">IF($O14="","",$O14-TODAY())</f>
+        <v>-38</v>
       </c>
       <c r="M14" s="12">
-        <f t="shared" ca="1" si="1"/>
-        <v>261</v>
+        <f ca="1">IF($F14="","",$F14+90-TODAY())</f>
+        <v>-38</v>
       </c>
       <c r="N14" s="12">
-        <f ca="1">IF($C14="","",$C14+120-TODAY())</f>
-        <v>16</v>
+        <f ca="1">IF($C14="","",$C14+180-TODAY())</f>
+        <v>146</v>
       </c>
       <c r="O14" s="6">
-        <v>46527</v>
+        <v>46244</v>
       </c>
       <c r="P14" s="5" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="Q14" s="5" t="s">
-        <v>137</v>
+        <v>396</v>
       </c>
       <c r="R14" s="5" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="S14" s="5" t="s">
-        <v>50</v>
+        <v>234</v>
       </c>
       <c r="T14" s="5" t="s">
-        <v>115</v>
+        <v>49</v>
       </c>
       <c r="U14" s="5" t="s">
         <v>50</v>
@@ -17974,7 +17634,7 @@
         <v>52</v>
       </c>
       <c r="Z14" s="7">
-        <v>1649.2</v>
+        <v>2528.2600000000002</v>
       </c>
       <c r="AA14" s="7">
         <v>0</v>
@@ -17983,94 +17643,96 @@
         <v>0</v>
       </c>
       <c r="AC14" s="6">
-        <v>46178</v>
+        <v>46170</v>
       </c>
       <c r="AD14" s="7">
-        <v>1649.2</v>
+        <v>2528.2600000000002</v>
       </c>
       <c r="AE14" s="4">
-        <v>80</v>
+        <v>88</v>
       </c>
       <c r="AF14" s="5" t="s">
-        <v>575</v>
-      </c>
-      <c r="AG14" s="5"/>
+        <v>626</v>
+      </c>
+      <c r="AG14" s="5" t="s">
+        <v>574</v>
+      </c>
       <c r="AH14" s="5"/>
       <c r="AI14" s="5"/>
       <c r="AJ14" s="4"/>
       <c r="AK14" s="5" t="s">
-        <v>164</v>
+        <v>105</v>
       </c>
       <c r="AL14" s="5" t="s">
-        <v>593</v>
+        <v>92</v>
       </c>
       <c r="AM14" s="6">
-        <v>46171</v>
+        <v>46164</v>
       </c>
       <c r="AN14" s="5" t="s">
         <v>565</v>
       </c>
       <c r="AO14" s="5" t="s">
-        <v>619</v>
+        <v>627</v>
       </c>
     </row>
     <row r="15" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A15" s="2" t="s">
-        <v>129</v>
+        <v>94</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>130</v>
+        <v>628</v>
       </c>
       <c r="C15" s="3">
-        <v>46232</v>
+        <v>46170</v>
       </c>
       <c r="D15" s="4">
-        <v>560072930</v>
+        <v>560081393</v>
       </c>
       <c r="E15" s="5" t="s">
-        <v>173</v>
+        <v>629</v>
       </c>
       <c r="F15" s="6">
         <v>46155</v>
       </c>
       <c r="G15" s="5" t="s">
-        <v>174</v>
+        <v>44</v>
       </c>
       <c r="H15" s="5" t="s">
-        <v>174</v>
+        <v>44</v>
       </c>
       <c r="I15" s="5" t="s">
         <v>45</v>
       </c>
       <c r="J15" s="5" t="s">
-        <v>569</v>
+        <v>614</v>
       </c>
       <c r="K15" s="3">
-        <v>46251</v>
+        <v>46245</v>
       </c>
       <c r="L15" s="12">
-        <f t="shared" ca="1" si="0"/>
-        <v>-67</v>
+        <f ca="1">IF($O15="","",$O15-TODAY())</f>
+        <v>-37</v>
       </c>
       <c r="M15" s="12">
-        <f t="shared" ca="1" si="1"/>
-        <v>315</v>
+        <f ca="1">IF($C15="","",$C15+180-TODAY())</f>
+        <v>68</v>
       </c>
       <c r="N15" s="12">
         <f ca="1">IF($C15="","",$C15+365-TODAY())</f>
-        <v>315</v>
+        <v>253</v>
       </c>
       <c r="O15" s="6">
-        <v>46215</v>
+        <v>46245</v>
       </c>
       <c r="P15" s="5" t="s">
-        <v>169</v>
+        <v>47</v>
       </c>
       <c r="Q15" s="5" t="s">
-        <v>175</v>
+        <v>48</v>
       </c>
       <c r="R15" s="5" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="S15" s="5" t="s">
         <v>50</v>
@@ -18096,7 +17758,9 @@
       <c r="AB15" s="7">
         <v>0</v>
       </c>
-      <c r="AC15" s="6"/>
+      <c r="AC15" s="6">
+        <v>46175</v>
+      </c>
       <c r="AD15" s="7">
         <v>3822.49</v>
       </c>
@@ -18104,12 +17768,14 @@
         <v>87</v>
       </c>
       <c r="AF15" s="5" t="s">
-        <v>620</v>
+        <v>575</v>
       </c>
       <c r="AG15" s="5" t="s">
-        <v>575</v>
-      </c>
-      <c r="AH15" s="5"/>
+        <v>585</v>
+      </c>
+      <c r="AH15" s="5" t="s">
+        <v>584</v>
+      </c>
       <c r="AI15" s="5"/>
       <c r="AJ15" s="4"/>
       <c r="AK15" s="5" t="s">
@@ -18125,63 +17791,59 @@
         <v>565</v>
       </c>
       <c r="AO15" s="5" t="s">
-        <v>621</v>
+        <v>630</v>
       </c>
     </row>
     <row r="16" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A16" s="2" t="s">
-        <v>129</v>
+        <v>94</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>130</v>
+        <v>631</v>
       </c>
       <c r="C16" s="3">
-        <v>46232</v>
+        <v>46236</v>
       </c>
       <c r="D16" s="4">
-        <v>565419142</v>
+        <v>564984009</v>
       </c>
       <c r="E16" s="5" t="s">
-        <v>622</v>
+        <v>632</v>
       </c>
       <c r="F16" s="6">
-        <v>46147</v>
+        <v>46149</v>
       </c>
       <c r="G16" s="5" t="s">
-        <v>75</v>
+        <v>168</v>
       </c>
       <c r="H16" s="5" t="s">
-        <v>75</v>
+        <v>168</v>
       </c>
       <c r="I16" s="5" t="s">
-        <v>45</v>
+        <v>633</v>
       </c>
       <c r="J16" s="5" t="s">
-        <v>604</v>
+        <v>634</v>
       </c>
       <c r="K16" s="3">
-        <v>46245</v>
-      </c>
-      <c r="L16" s="12">
-        <f t="shared" ca="1" si="0"/>
-        <v>-45</v>
+        <v>46259</v>
+      </c>
+      <c r="L16" s="12" t="str">
+        <f ca="1">IF($O16="","",$O16-TODAY())</f>
+        <v/>
       </c>
       <c r="M16" s="12">
         <f ca="1">IF($C16="","",$C16+180-TODAY())</f>
-        <v>130</v>
+        <v>134</v>
       </c>
       <c r="N16" s="12">
         <f ca="1">IF($C16="","",$C16+365-TODAY())</f>
-        <v>315</v>
-      </c>
-      <c r="O16" s="6">
-        <v>46237</v>
-      </c>
-      <c r="P16" s="5" t="s">
-        <v>47</v>
-      </c>
+        <v>319</v>
+      </c>
+      <c r="O16" s="6"/>
+      <c r="P16" s="5"/>
       <c r="Q16" s="5" t="s">
-        <v>77</v>
+        <v>170</v>
       </c>
       <c r="R16" s="5" t="s">
         <v>49</v>
@@ -18210,27 +17872,31 @@
       <c r="AB16" s="7">
         <v>0</v>
       </c>
-      <c r="AC16" s="6">
-        <v>46174</v>
-      </c>
+      <c r="AC16" s="6"/>
       <c r="AD16" s="7">
         <v>3822.49</v>
       </c>
       <c r="AE16" s="4">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="AF16" s="5" t="s">
-        <v>609</v>
-      </c>
-      <c r="AG16" s="5"/>
-      <c r="AH16" s="5"/>
-      <c r="AI16" s="5"/>
+        <v>635</v>
+      </c>
+      <c r="AG16" s="5" t="s">
+        <v>636</v>
+      </c>
+      <c r="AH16" s="5" t="s">
+        <v>637</v>
+      </c>
+      <c r="AI16" s="5" t="s">
+        <v>638</v>
+      </c>
       <c r="AJ16" s="4"/>
       <c r="AK16" s="5" t="s">
-        <v>105</v>
+        <v>86</v>
       </c>
       <c r="AL16" s="5" t="s">
-        <v>92</v>
+        <v>564</v>
       </c>
       <c r="AM16" s="6">
         <v>46164</v>
@@ -18239,360 +17905,12 @@
         <v>565</v>
       </c>
       <c r="AO16" s="5" t="s">
-        <v>623</v>
-      </c>
-    </row>
-    <row r="17" spans="1:41" x14ac:dyDescent="0.25">
-      <c r="A17" s="2" t="s">
-        <v>130</v>
-      </c>
-      <c r="B17" s="2" t="s">
-        <v>624</v>
-      </c>
-      <c r="C17" s="3">
-        <v>46248</v>
-      </c>
-      <c r="D17" s="4">
-        <v>567453889</v>
-      </c>
-      <c r="E17" s="5" t="s">
-        <v>625</v>
-      </c>
-      <c r="F17" s="6">
-        <v>46154</v>
-      </c>
-      <c r="G17" s="5" t="s">
-        <v>394</v>
-      </c>
-      <c r="H17" s="5" t="s">
-        <v>394</v>
-      </c>
-      <c r="I17" s="5" t="s">
-        <v>45</v>
-      </c>
-      <c r="J17" s="5" t="s">
-        <v>562</v>
-      </c>
-      <c r="K17" s="3">
-        <v>46237</v>
-      </c>
-      <c r="L17" s="12">
-        <f t="shared" ca="1" si="0"/>
-        <v>-38</v>
-      </c>
-      <c r="M17" s="12">
-        <f ca="1">IF($F17="","",$F17+90-TODAY())</f>
-        <v>-38</v>
-      </c>
-      <c r="N17" s="12">
-        <f ca="1">IF($C17="","",$C17+180-TODAY())</f>
-        <v>146</v>
-      </c>
-      <c r="O17" s="6">
-        <v>46244</v>
-      </c>
-      <c r="P17" s="5" t="s">
-        <v>47</v>
-      </c>
-      <c r="Q17" s="5" t="s">
-        <v>396</v>
-      </c>
-      <c r="R17" s="5" t="s">
-        <v>47</v>
-      </c>
-      <c r="S17" s="5" t="s">
-        <v>234</v>
-      </c>
-      <c r="T17" s="5" t="s">
-        <v>49</v>
-      </c>
-      <c r="U17" s="5" t="s">
-        <v>50</v>
-      </c>
-      <c r="V17" s="5"/>
-      <c r="W17" s="5"/>
-      <c r="X17" s="5"/>
-      <c r="Y17" s="5" t="s">
-        <v>52</v>
-      </c>
-      <c r="Z17" s="7">
-        <v>2528.2600000000002</v>
-      </c>
-      <c r="AA17" s="7">
-        <v>0</v>
-      </c>
-      <c r="AB17" s="7">
-        <v>0</v>
-      </c>
-      <c r="AC17" s="6">
-        <v>46170</v>
-      </c>
-      <c r="AD17" s="7">
-        <v>2528.2600000000002</v>
-      </c>
-      <c r="AE17" s="4">
-        <v>88</v>
-      </c>
-      <c r="AF17" s="5" t="s">
-        <v>626</v>
-      </c>
-      <c r="AG17" s="5" t="s">
-        <v>574</v>
-      </c>
-      <c r="AH17" s="5"/>
-      <c r="AI17" s="5"/>
-      <c r="AJ17" s="4"/>
-      <c r="AK17" s="5" t="s">
-        <v>105</v>
-      </c>
-      <c r="AL17" s="5" t="s">
-        <v>92</v>
-      </c>
-      <c r="AM17" s="6">
-        <v>46164</v>
-      </c>
-      <c r="AN17" s="5" t="s">
-        <v>565</v>
-      </c>
-      <c r="AO17" s="5" t="s">
-        <v>627</v>
-      </c>
-    </row>
-    <row r="18" spans="1:41" x14ac:dyDescent="0.25">
-      <c r="A18" s="2" t="s">
-        <v>94</v>
-      </c>
-      <c r="B18" s="2" t="s">
-        <v>628</v>
-      </c>
-      <c r="C18" s="3">
-        <v>46170</v>
-      </c>
-      <c r="D18" s="4">
-        <v>560081393</v>
-      </c>
-      <c r="E18" s="5" t="s">
-        <v>629</v>
-      </c>
-      <c r="F18" s="6">
-        <v>46155</v>
-      </c>
-      <c r="G18" s="5" t="s">
-        <v>44</v>
-      </c>
-      <c r="H18" s="5" t="s">
-        <v>44</v>
-      </c>
-      <c r="I18" s="5" t="s">
-        <v>45</v>
-      </c>
-      <c r="J18" s="5" t="s">
-        <v>614</v>
-      </c>
-      <c r="K18" s="3">
-        <v>46245</v>
-      </c>
-      <c r="L18" s="12">
-        <f t="shared" ca="1" si="0"/>
-        <v>-37</v>
-      </c>
-      <c r="M18" s="12">
-        <f ca="1">IF($C18="","",$C18+180-TODAY())</f>
-        <v>68</v>
-      </c>
-      <c r="N18" s="12">
-        <f ca="1">IF($C18="","",$C18+365-TODAY())</f>
-        <v>253</v>
-      </c>
-      <c r="O18" s="6">
-        <v>46245</v>
-      </c>
-      <c r="P18" s="5" t="s">
-        <v>47</v>
-      </c>
-      <c r="Q18" s="5" t="s">
-        <v>48</v>
-      </c>
-      <c r="R18" s="5" t="s">
-        <v>49</v>
-      </c>
-      <c r="S18" s="5" t="s">
-        <v>50</v>
-      </c>
-      <c r="T18" s="5" t="s">
-        <v>51</v>
-      </c>
-      <c r="U18" s="5" t="s">
-        <v>50</v>
-      </c>
-      <c r="V18" s="5"/>
-      <c r="W18" s="5"/>
-      <c r="X18" s="5"/>
-      <c r="Y18" s="5" t="s">
-        <v>52</v>
-      </c>
-      <c r="Z18" s="7">
-        <v>3822.49</v>
-      </c>
-      <c r="AA18" s="7">
-        <v>0</v>
-      </c>
-      <c r="AB18" s="7">
-        <v>0</v>
-      </c>
-      <c r="AC18" s="6">
-        <v>46175</v>
-      </c>
-      <c r="AD18" s="7">
-        <v>3822.49</v>
-      </c>
-      <c r="AE18" s="4">
-        <v>87</v>
-      </c>
-      <c r="AF18" s="5" t="s">
-        <v>575</v>
-      </c>
-      <c r="AG18" s="5" t="s">
-        <v>585</v>
-      </c>
-      <c r="AH18" s="5" t="s">
-        <v>584</v>
-      </c>
-      <c r="AI18" s="5"/>
-      <c r="AJ18" s="4"/>
-      <c r="AK18" s="5" t="s">
-        <v>164</v>
-      </c>
-      <c r="AL18" s="5" t="s">
-        <v>593</v>
-      </c>
-      <c r="AM18" s="6">
-        <v>46164</v>
-      </c>
-      <c r="AN18" s="5" t="s">
-        <v>565</v>
-      </c>
-      <c r="AO18" s="5" t="s">
-        <v>630</v>
-      </c>
-    </row>
-    <row r="19" spans="1:41" x14ac:dyDescent="0.25">
-      <c r="A19" s="2" t="s">
-        <v>94</v>
-      </c>
-      <c r="B19" s="2" t="s">
-        <v>631</v>
-      </c>
-      <c r="C19" s="3">
-        <v>46236</v>
-      </c>
-      <c r="D19" s="4">
-        <v>564984009</v>
-      </c>
-      <c r="E19" s="5" t="s">
-        <v>632</v>
-      </c>
-      <c r="F19" s="6">
-        <v>46149</v>
-      </c>
-      <c r="G19" s="5" t="s">
-        <v>168</v>
-      </c>
-      <c r="H19" s="5" t="s">
-        <v>168</v>
-      </c>
-      <c r="I19" s="5" t="s">
-        <v>633</v>
-      </c>
-      <c r="J19" s="5" t="s">
-        <v>634</v>
-      </c>
-      <c r="K19" s="3">
-        <v>46259</v>
-      </c>
-      <c r="L19" s="12" t="str">
-        <f t="shared" ca="1" si="0"/>
-        <v/>
-      </c>
-      <c r="M19" s="12">
-        <f ca="1">IF($C19="","",$C19+180-TODAY())</f>
-        <v>134</v>
-      </c>
-      <c r="N19" s="12">
-        <f ca="1">IF($C19="","",$C19+365-TODAY())</f>
-        <v>319</v>
-      </c>
-      <c r="O19" s="6"/>
-      <c r="P19" s="5"/>
-      <c r="Q19" s="5" t="s">
-        <v>170</v>
-      </c>
-      <c r="R19" s="5" t="s">
-        <v>49</v>
-      </c>
-      <c r="S19" s="5" t="s">
-        <v>50</v>
-      </c>
-      <c r="T19" s="5" t="s">
-        <v>51</v>
-      </c>
-      <c r="U19" s="5" t="s">
-        <v>50</v>
-      </c>
-      <c r="V19" s="5"/>
-      <c r="W19" s="5"/>
-      <c r="X19" s="5"/>
-      <c r="Y19" s="5" t="s">
-        <v>52</v>
-      </c>
-      <c r="Z19" s="7">
-        <v>3822.49</v>
-      </c>
-      <c r="AA19" s="7">
-        <v>0</v>
-      </c>
-      <c r="AB19" s="7">
-        <v>0</v>
-      </c>
-      <c r="AC19" s="6"/>
-      <c r="AD19" s="7">
-        <v>3822.49</v>
-      </c>
-      <c r="AE19" s="4">
-        <v>93</v>
-      </c>
-      <c r="AF19" s="5" t="s">
-        <v>635</v>
-      </c>
-      <c r="AG19" s="5" t="s">
-        <v>636</v>
-      </c>
-      <c r="AH19" s="5" t="s">
-        <v>637</v>
-      </c>
-      <c r="AI19" s="5" t="s">
-        <v>638</v>
-      </c>
-      <c r="AJ19" s="4"/>
-      <c r="AK19" s="5" t="s">
-        <v>86</v>
-      </c>
-      <c r="AL19" s="5" t="s">
-        <v>564</v>
-      </c>
-      <c r="AM19" s="6">
-        <v>46164</v>
-      </c>
-      <c r="AN19" s="5" t="s">
-        <v>565</v>
-      </c>
-      <c r="AO19" s="5" t="s">
         <v>639</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AO19" xr:uid="{00000000-0009-0000-0000-000004000000}"/>
-  <conditionalFormatting sqref="L2:L19">
+  <autoFilter ref="A1:AO16" xr:uid="{00000000-0009-0000-0000-000004000000}"/>
+  <conditionalFormatting sqref="L2:L16">
     <cfRule type="expression" dxfId="19" priority="1">
       <formula>AND($L2&lt;&gt;"", $L2&gt;=0, $L2&lt;=5)</formula>
     </cfRule>
@@ -18609,7 +17927,7 @@
       <formula>$L2=""</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="M2:M19">
+  <conditionalFormatting sqref="M2:M16">
     <cfRule type="expression" dxfId="14" priority="6">
       <formula>AND($M2&lt;&gt;"", $M2&gt;=0, $M2&lt;=5)</formula>
     </cfRule>
@@ -18626,7 +17944,7 @@
       <formula>$M2=""</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="N2:N19">
+  <conditionalFormatting sqref="N2:N16">
     <cfRule type="expression" dxfId="9" priority="11">
       <formula>AND($N2&lt;&gt;"", $N2&gt;=0, $N2&lt;=5)</formula>
     </cfRule>
@@ -18643,7 +17961,7 @@
       <formula>$N2=""</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="O2:U19">
+  <conditionalFormatting sqref="O2:U16">
     <cfRule type="expression" dxfId="4" priority="16">
       <formula>AND($L2&lt;&gt;"", $L2&gt;=0, $L2&lt;=5)</formula>
     </cfRule>
@@ -18661,7 +17979,7 @@
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" promptTitle="Claim Status" prompt="Pick a status, or type a new one." sqref="A2:A19" xr:uid="{00000000-0002-0000-0400-000000000000}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" promptTitle="Claim Status" prompt="Pick a status, or type a new one." sqref="A2:A16" xr:uid="{00000000-0002-0000-0400-000000000000}">
       <formula1>"Denied,Finalized,PAID,Pending,Received,Rejected"</formula1>
     </dataValidation>
   </dataValidations>

--- a/Specialty Claims 2026-S1/2026-05 May - Specialty Claims.xlsx
+++ b/Specialty Claims 2026-S1/2026-05 May - Specialty Claims.xlsx
@@ -1078,7 +1078,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2490" uniqueCount="676">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2509" uniqueCount="685">
   <si>
     <t>Claim Status</t>
   </si>
@@ -3106,6 +3106,33 @@
   </si>
   <si>
     <t>Secondary - PAID</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Under Review</t>
+  </si>
+  <si>
+    <t xml:space="preserve">I need to call PT - Aetna termed date March 31, 2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Waiting for account to get activated again</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MUE issue - CALL INS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Still processing - ins received claim on 07/20/2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Call PT for COB update needed by ins - Rep said the patient will need to update their Coordination of Benefits (COB) information with their insurance carrier. Once the COB has been updated, the claim can be reprocessed for review and adjudication. On yearly basis patient needs to update the COB.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Call ins - Bundled - but we have an auth for this one </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Expecting ins reply - DND as medical necessity - Jess sent MR </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Statuses currently in use: Denied, Finalized, PAID, Pending, Received, Rejected, Under Review.</t>
   </si>
 </sst>
 </file>
@@ -5708,10 +5735,10 @@
     </row>
     <row r="11" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A11" s="2" t="s">
-        <v>94</v>
+        <v>676</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>112</v>
+        <v>677</v>
       </c>
       <c r="C11" s="3">
         <v>46195</v>
@@ -7404,10 +7431,10 @@
     </row>
     <row r="26" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A26" s="2" t="s">
-        <v>190</v>
+        <v>676</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>191</v>
+        <v>678</v>
       </c>
       <c r="C26" s="3"/>
       <c r="D26" s="4">
@@ -7878,10 +7905,10 @@
     </row>
     <row r="31" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A31" s="2" t="s">
-        <v>190</v>
+        <v>676</v>
       </c>
       <c r="B31" s="2" t="s">
-        <v>191</v>
+        <v>678</v>
       </c>
       <c r="C31" s="3"/>
       <c r="D31" s="4">
@@ -8021,7 +8048,7 @@
   </conditionalFormatting>
   <dataValidations count="1">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" promptTitle="Claim Status" prompt="Pick a status, or type a new one." sqref="A2:A31" xr:uid="{00000000-0002-0000-0000-000000000000}">
-      <formula1>"Denied,Finalized,PAID,Pending,Received,Rejected"</formula1>
+      <formula1>"Denied,Finalized,PAID,Pending,Received,Rejected,Under Review"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -9374,10 +9401,10 @@
     </row>
     <row r="12" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A12" s="2" t="s">
-        <v>94</v>
+        <v>676</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>287</v>
+        <v>679</v>
       </c>
       <c r="C12" s="3">
         <v>46190</v>
@@ -11140,10 +11167,10 @@
     </row>
     <row r="27" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A27" s="2" t="s">
-        <v>41</v>
+        <v>676</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>380</v>
+        <v>680</v>
       </c>
       <c r="C27" s="3"/>
       <c r="D27" s="4">
@@ -11844,10 +11871,10 @@
     </row>
     <row r="33" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A33" s="2" t="s">
-        <v>94</v>
+        <v>676</v>
       </c>
       <c r="B33" s="2" t="s">
-        <v>410</v>
+        <v>681</v>
       </c>
       <c r="C33" s="3">
         <v>46203</v>
@@ -12238,7 +12265,7 @@
   </conditionalFormatting>
   <dataValidations disablePrompts="1" count="1">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" promptTitle="Claim Status" prompt="Pick a status, or type a new one." sqref="A2:A35" xr:uid="{00000000-0002-0000-0100-000000000000}">
-      <formula1>"Denied,Finalized,PAID,Pending,Received,Rejected"</formula1>
+      <formula1>"Denied,Finalized,PAID,Pending,Received,Rejected,Under Review"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -13032,10 +13059,10 @@
     </row>
     <row r="7" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
-        <v>190</v>
+        <v>676</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>191</v>
+        <v>678</v>
       </c>
       <c r="C7" s="3"/>
       <c r="D7" s="4">
@@ -13202,7 +13229,7 @@
   </conditionalFormatting>
   <dataValidations count="1">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" promptTitle="Claim Status" prompt="Pick a status, or type a new one." sqref="A2:A7" xr:uid="{00000000-0002-0000-0200-000000000000}">
-      <formula1>"Denied,Finalized,PAID,Pending,Received,Rejected"</formula1>
+      <formula1>"Denied,Finalized,PAID,Pending,Received,Rejected,Under Review"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -15366,10 +15393,10 @@
     </row>
     <row r="19" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A19" s="2" t="s">
-        <v>94</v>
+        <v>676</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>537</v>
+        <v>682</v>
       </c>
       <c r="C19" s="3">
         <v>46162</v>
@@ -15594,10 +15621,10 @@
     </row>
     <row r="21" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A21" s="2" t="s">
-        <v>94</v>
+        <v>676</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>549</v>
+        <v>683</v>
       </c>
       <c r="C21" s="3">
         <v>46197</v>
@@ -15994,7 +16021,7 @@
   </conditionalFormatting>
   <dataValidations count="1">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" promptTitle="Claim Status" prompt="Pick a status, or type a new one." sqref="A2:A23" xr:uid="{00000000-0002-0000-0300-000000000000}">
-      <formula1>"Denied,Finalized,PAID,Pending,Received,Rejected"</formula1>
+      <formula1>"Denied,Finalized,PAID,Pending,Received,Rejected,Under Review"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -17980,7 +18007,7 @@
   </conditionalFormatting>
   <dataValidations count="1">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" promptTitle="Claim Status" prompt="Pick a status, or type a new one." sqref="A2:A16" xr:uid="{00000000-0002-0000-0400-000000000000}">
-      <formula1>"Denied,Finalized,PAID,Pending,Received,Rejected"</formula1>
+      <formula1>"Denied,Finalized,PAID,Pending,Received,Rejected,Under Review"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -18093,7 +18120,7 @@
     </row>
     <row r="21" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A21" s="9" t="s">
-        <v>656</v>
+        <v>684</v>
       </c>
     </row>
     <row r="22" spans="1:1" ht="30" x14ac:dyDescent="0.25">

--- a/Specialty Claims 2026-S1/2026-05 May - Specialty Claims.xlsx
+++ b/Specialty Claims 2026-S1/2026-05 May - Specialty Claims.xlsx
@@ -1078,7 +1078,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2509" uniqueCount="685">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2511" uniqueCount="686">
   <si>
     <t>Claim Status</t>
   </si>
@@ -3133,6 +3133,9 @@
   </si>
   <si>
     <t xml:space="preserve">Statuses currently in use: Denied, Finalized, PAID, Pending, Received, Rejected, Under Review.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Statuses currently in use: Denied, Finalized, Not found, PAID, Pending, Received, Rejected, Under Review.</t>
   </si>
 </sst>
 </file>
@@ -8048,7 +8051,7 @@
   </conditionalFormatting>
   <dataValidations count="1">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" promptTitle="Claim Status" prompt="Pick a status, or type a new one." sqref="A2:A31" xr:uid="{00000000-0002-0000-0000-000000000000}">
-      <formula1>"Denied,Finalized,PAID,Pending,Received,Rejected,Under Review"</formula1>
+      <formula1>"Denied,Finalized,Not found,PAID,Pending,Received,Rejected,Under Review"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -12265,7 +12268,7 @@
   </conditionalFormatting>
   <dataValidations disablePrompts="1" count="1">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" promptTitle="Claim Status" prompt="Pick a status, or type a new one." sqref="A2:A35" xr:uid="{00000000-0002-0000-0100-000000000000}">
-      <formula1>"Denied,Finalized,PAID,Pending,Received,Rejected,Under Review"</formula1>
+      <formula1>"Denied,Finalized,Not found,PAID,Pending,Received,Rejected,Under Review"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -13229,7 +13232,7 @@
   </conditionalFormatting>
   <dataValidations count="1">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" promptTitle="Claim Status" prompt="Pick a status, or type a new one." sqref="A2:A7" xr:uid="{00000000-0002-0000-0200-000000000000}">
-      <formula1>"Denied,Finalized,PAID,Pending,Received,Rejected,Under Review"</formula1>
+      <formula1>"Denied,Finalized,Not found,PAID,Pending,Received,Rejected,Under Review"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -15275,7 +15278,7 @@
     </row>
     <row r="18" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A18" s="2" t="s">
-        <v>532</v>
+        <v>41</v>
       </c>
       <c r="B18" s="2" t="s">
         <v>533</v>
@@ -16021,7 +16024,7 @@
   </conditionalFormatting>
   <dataValidations count="1">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" promptTitle="Claim Status" prompt="Pick a status, or type a new one." sqref="A2:A23" xr:uid="{00000000-0002-0000-0300-000000000000}">
-      <formula1>"Denied,Finalized,PAID,Pending,Received,Rejected,Under Review"</formula1>
+      <formula1>"Denied,Finalized,Not found,PAID,Pending,Received,Rejected,Under Review"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -18007,7 +18010,7 @@
   </conditionalFormatting>
   <dataValidations count="1">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" promptTitle="Claim Status" prompt="Pick a status, or type a new one." sqref="A2:A16" xr:uid="{00000000-0002-0000-0400-000000000000}">
-      <formula1>"Denied,Finalized,PAID,Pending,Received,Rejected,Under Review"</formula1>
+      <formula1>"Denied,Finalized,Not found,PAID,Pending,Received,Rejected,Under Review"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -18120,7 +18123,7 @@
     </row>
     <row r="21" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A21" s="9" t="s">
-        <v>684</v>
+        <v>685</v>
       </c>
     </row>
     <row r="22" spans="1:1" ht="30" x14ac:dyDescent="0.25">

--- a/Specialty Claims 2026-S1/2026-05 May - Specialty Claims.xlsx
+++ b/Specialty Claims 2026-S1/2026-05 May - Specialty Claims.xlsx
@@ -1078,7 +1078,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2511" uniqueCount="686">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2525" uniqueCount="687">
   <si>
     <t>Claim Status</t>
   </si>
@@ -3136,6 +3136,9 @@
   </si>
   <si>
     <t xml:space="preserve">Statuses currently in use: Denied, Finalized, Not found, PAID, Pending, Received, Rejected, Under Review.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">540 days</t>
   </si>
 </sst>
 </file>
@@ -7038,21 +7041,27 @@
       </c>
       <c r="L22" s="12">
         <f ca="1">IF($O22="","",$O22-TODAY())</f>
-        <v>-73</v>
-      </c>
-      <c r="M22" s="12"/>
-      <c r="N22" s="12"/>
+        <v>-44</v>
+      </c>
+      <c r="M22" s="12" t="str">
+        <f ca="1">IF($C22="","",$C22+365-TODAY())</f>
+        <v/>
+      </c>
+      <c r="N22" s="12" t="str">
+        <f ca="1">IF($C22="","",$C22+365-TODAY())</f>
+        <v/>
+      </c>
       <c r="O22" s="6">
-        <v>46209</v>
+        <v>46239</v>
       </c>
       <c r="P22" s="5" t="s">
-        <v>169</v>
+        <v>47</v>
       </c>
       <c r="Q22" s="5" t="s">
         <v>170</v>
       </c>
       <c r="R22" s="5" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="S22" s="5" t="s">
         <v>50</v>
@@ -7261,12 +7270,12 @@
         <v>-38</v>
       </c>
       <c r="M24" s="12">
-        <f ca="1">IF($C24="","",$C24+365-TODAY())</f>
-        <v>299</v>
+        <f ca="1">IF($F24="","",$F24+90-TODAY())</f>
+        <v>-39</v>
       </c>
       <c r="N24" s="12">
         <f ca="1">IF($C24="","",$C24+365-TODAY())</f>
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="O24" s="6">
         <v>46244</v>
@@ -7278,10 +7287,10 @@
         <v>182</v>
       </c>
       <c r="R24" s="5" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="S24" s="5" t="s">
-        <v>50</v>
+        <v>234</v>
       </c>
       <c r="T24" s="5" t="s">
         <v>51</v>
@@ -8260,7 +8269,7 @@
         <v>46244</v>
       </c>
       <c r="L2" s="12">
-        <f t="shared" ref="L2:L35" ca="1" si="0">IF($O2="","",$O2-TODAY())</f>
+        <f ca="1">IF($O2="","",$O2-TODAY())</f>
         <v>-35</v>
       </c>
       <c r="M2" s="12" t="str">
@@ -8380,7 +8389,7 @@
         <v>46245</v>
       </c>
       <c r="L3" s="12">
-        <f t="shared" ca="1" si="0"/>
+        <f ca="1">IF($O3="","",$O3-TODAY())</f>
         <v>-32</v>
       </c>
       <c r="M3" s="12">
@@ -8496,16 +8505,16 @@
         <v>46245</v>
       </c>
       <c r="L4" s="12">
-        <f t="shared" ca="1" si="0"/>
+        <f ca="1">IF($O4="","",$O4-TODAY())</f>
         <v>-32</v>
       </c>
       <c r="M4" s="12">
         <f ca="1">IF($F4="","",$F4+90-TODAY())</f>
-        <v>-32</v>
+        <v>-33</v>
       </c>
       <c r="N4" s="12">
-        <f ca="1">IF($C4="","",$C4+60-TODAY())</f>
-        <v>-37</v>
+        <f ca="1">IF($C4="","",$C4+540-TODAY())</f>
+        <v>442</v>
       </c>
       <c r="O4" s="6">
         <v>46250</v>
@@ -8523,7 +8532,7 @@
         <v>234</v>
       </c>
       <c r="T4" s="5" t="s">
-        <v>169</v>
+        <v>686</v>
       </c>
       <c r="U4" s="5" t="s">
         <v>50</v>
@@ -8614,7 +8623,7 @@
         <v>46245</v>
       </c>
       <c r="L5" s="12">
-        <f t="shared" ca="1" si="0"/>
+        <f ca="1">IF($O5="","",$O5-TODAY())</f>
         <v>-29</v>
       </c>
       <c r="M5" s="12">
@@ -8732,7 +8741,7 @@
         <v>46245</v>
       </c>
       <c r="L6" s="12">
-        <f t="shared" ca="1" si="0"/>
+        <f ca="1">IF($O6="","",$O6-TODAY())</f>
         <v>-28</v>
       </c>
       <c r="M6" s="12">
@@ -8850,7 +8859,7 @@
         <v>46248</v>
       </c>
       <c r="L7" s="12">
-        <f t="shared" ca="1" si="0"/>
+        <f ca="1">IF($O7="","",$O7-TODAY())</f>
         <v>-24</v>
       </c>
       <c r="M7" s="12">
@@ -8970,7 +8979,7 @@
         <v>46248</v>
       </c>
       <c r="L8" s="12">
-        <f t="shared" ca="1" si="0"/>
+        <f ca="1">IF($O8="","",$O8-TODAY())</f>
         <v>-16</v>
       </c>
       <c r="M8" s="12"/>
@@ -9079,7 +9088,7 @@
         <v>46252</v>
       </c>
       <c r="L9" s="12">
-        <f t="shared" ca="1" si="0"/>
+        <f ca="1">IF($O9="","",$O9-TODAY())</f>
         <v>-1</v>
       </c>
       <c r="M9" s="12">
@@ -9197,7 +9206,7 @@
         <v>46253</v>
       </c>
       <c r="L10" s="12">
-        <f t="shared" ca="1" si="0"/>
+        <f ca="1">IF($O10="","",$O10-TODAY())</f>
         <v>6</v>
       </c>
       <c r="M10" s="12">
@@ -9319,7 +9328,7 @@
         <v>46254</v>
       </c>
       <c r="L11" s="12">
-        <f t="shared" ca="1" si="0"/>
+        <f ca="1">IF($O11="","",$O11-TODAY())</f>
         <v>44</v>
       </c>
       <c r="M11" s="12">
@@ -9435,7 +9444,7 @@
       </c>
       <c r="K12" s="3"/>
       <c r="L12" s="12">
-        <f t="shared" ca="1" si="0"/>
+        <f ca="1">IF($O12="","",$O12-TODAY())</f>
         <v>58</v>
       </c>
       <c r="M12" s="12">
@@ -9553,7 +9562,7 @@
         <v>46254</v>
       </c>
       <c r="L13" s="12">
-        <f t="shared" ca="1" si="0"/>
+        <f ca="1">IF($O13="","",$O13-TODAY())</f>
         <v>68</v>
       </c>
       <c r="M13" s="12">
@@ -9673,15 +9682,15 @@
         <v>46254</v>
       </c>
       <c r="L14" s="12">
-        <f t="shared" ca="1" si="0"/>
+        <f ca="1">IF($O14="","",$O14-TODAY())</f>
         <v>230</v>
       </c>
       <c r="M14" s="12">
-        <f t="shared" ref="M14:M27" ca="1" si="1">IF($C14="","",$C14+365-TODAY())</f>
+        <f ca="1">IF($C14="","",$C14+365-TODAY())</f>
         <v>239</v>
       </c>
       <c r="N14" s="12">
-        <f t="shared" ref="N14:N25" ca="1" si="2">IF($C14="","",$C14+120-TODAY())</f>
+        <f ca="1">IF($C14="","",$C14+120-TODAY())</f>
         <v>-6</v>
       </c>
       <c r="O14" s="6">
@@ -9787,15 +9796,15 @@
       </c>
       <c r="K15" s="3"/>
       <c r="L15" s="12">
-        <f t="shared" ca="1" si="0"/>
+        <f ca="1">IF($O15="","",$O15-TODAY())</f>
         <v>230</v>
       </c>
       <c r="M15" s="12">
-        <f t="shared" ca="1" si="1"/>
+        <f ca="1">IF($C15="","",$C15+365-TODAY())</f>
         <v>332</v>
       </c>
       <c r="N15" s="12">
-        <f t="shared" ca="1" si="2"/>
+        <f ca="1">IF($C15="","",$C15+120-TODAY())</f>
         <v>87</v>
       </c>
       <c r="O15" s="6">
@@ -9903,15 +9912,15 @@
       </c>
       <c r="K16" s="3"/>
       <c r="L16" s="12">
-        <f t="shared" ca="1" si="0"/>
+        <f ca="1">IF($O16="","",$O16-TODAY())</f>
         <v>233</v>
       </c>
       <c r="M16" s="12">
-        <f t="shared" ca="1" si="1"/>
+        <f ca="1">IF($C16="","",$C16+365-TODAY())</f>
         <v>285</v>
       </c>
       <c r="N16" s="12">
-        <f t="shared" ca="1" si="2"/>
+        <f ca="1">IF($C16="","",$C16+120-TODAY())</f>
         <v>40</v>
       </c>
       <c r="O16" s="6">
@@ -10023,15 +10032,15 @@
         <v>46254</v>
       </c>
       <c r="L17" s="12">
-        <f t="shared" ca="1" si="0"/>
+        <f ca="1">IF($O17="","",$O17-TODAY())</f>
         <v>233</v>
       </c>
       <c r="M17" s="12">
-        <f t="shared" ca="1" si="1"/>
+        <f ca="1">IF($C17="","",$C17+365-TODAY())</f>
         <v>268</v>
       </c>
       <c r="N17" s="12">
-        <f t="shared" ca="1" si="2"/>
+        <f ca="1">IF($C17="","",$C17+120-TODAY())</f>
         <v>23</v>
       </c>
       <c r="O17" s="6">
@@ -10143,15 +10152,15 @@
         <v>46254</v>
       </c>
       <c r="L18" s="12">
-        <f t="shared" ca="1" si="0"/>
+        <f ca="1">IF($O18="","",$O18-TODAY())</f>
         <v>239</v>
       </c>
       <c r="M18" s="12">
-        <f t="shared" ca="1" si="1"/>
+        <f ca="1">IF($C18="","",$C18+365-TODAY())</f>
         <v>294</v>
       </c>
       <c r="N18" s="12">
-        <f t="shared" ca="1" si="2"/>
+        <f ca="1">IF($C18="","",$C18+120-TODAY())</f>
         <v>49</v>
       </c>
       <c r="O18" s="6">
@@ -10263,15 +10272,15 @@
         <v>46254</v>
       </c>
       <c r="L19" s="12">
-        <f t="shared" ca="1" si="0"/>
+        <f ca="1">IF($O19="","",$O19-TODAY())</f>
         <v>239</v>
       </c>
       <c r="M19" s="12">
-        <f t="shared" ca="1" si="1"/>
+        <f ca="1">IF($C19="","",$C19+365-TODAY())</f>
         <v>330</v>
       </c>
       <c r="N19" s="12">
-        <f t="shared" ca="1" si="2"/>
+        <f ca="1">IF($C19="","",$C19+120-TODAY())</f>
         <v>85</v>
       </c>
       <c r="O19" s="6">
@@ -10381,15 +10390,15 @@
         <v>46255</v>
       </c>
       <c r="L20" s="12">
-        <f t="shared" ca="1" si="0"/>
+        <f ca="1">IF($O20="","",$O20-TODAY())</f>
         <v>243</v>
       </c>
       <c r="M20" s="12">
-        <f t="shared" ca="1" si="1"/>
+        <f ca="1">IF($C20="","",$C20+365-TODAY())</f>
         <v>302</v>
       </c>
       <c r="N20" s="12">
-        <f t="shared" ca="1" si="2"/>
+        <f ca="1">IF($C20="","",$C20+120-TODAY())</f>
         <v>57</v>
       </c>
       <c r="O20" s="6">
@@ -10497,15 +10506,15 @@
         <v>46255</v>
       </c>
       <c r="L21" s="12">
-        <f t="shared" ca="1" si="0"/>
+        <f ca="1">IF($O21="","",$O21-TODAY())</f>
         <v>244</v>
       </c>
       <c r="M21" s="12">
-        <f t="shared" ca="1" si="1"/>
+        <f ca="1">IF($C21="","",$C21+365-TODAY())</f>
         <v>329</v>
       </c>
       <c r="N21" s="12">
-        <f t="shared" ca="1" si="2"/>
+        <f ca="1">IF($C21="","",$C21+120-TODAY())</f>
         <v>84</v>
       </c>
       <c r="O21" s="6">
@@ -10613,15 +10622,15 @@
       </c>
       <c r="K22" s="3"/>
       <c r="L22" s="12">
-        <f t="shared" ca="1" si="0"/>
+        <f ca="1">IF($O22="","",$O22-TODAY())</f>
         <v>251</v>
       </c>
       <c r="M22" s="12">
-        <f t="shared" ca="1" si="1"/>
+        <f ca="1">IF($C22="","",$C22+365-TODAY())</f>
         <v>292</v>
       </c>
       <c r="N22" s="12">
-        <f t="shared" ca="1" si="2"/>
+        <f ca="1">IF($C22="","",$C22+120-TODAY())</f>
         <v>47</v>
       </c>
       <c r="O22" s="6">
@@ -10729,15 +10738,15 @@
       </c>
       <c r="K23" s="3"/>
       <c r="L23" s="12">
-        <f t="shared" ca="1" si="0"/>
+        <f ca="1">IF($O23="","",$O23-TODAY())</f>
         <v>251</v>
       </c>
       <c r="M23" s="12">
-        <f t="shared" ca="1" si="1"/>
+        <f ca="1">IF($C23="","",$C23+365-TODAY())</f>
         <v>332</v>
       </c>
       <c r="N23" s="12">
-        <f t="shared" ca="1" si="2"/>
+        <f ca="1">IF($C23="","",$C23+120-TODAY())</f>
         <v>87</v>
       </c>
       <c r="O23" s="6">
@@ -10845,15 +10854,15 @@
         <v>46255</v>
       </c>
       <c r="L24" s="12">
-        <f t="shared" ca="1" si="0"/>
+        <f ca="1">IF($O24="","",$O24-TODAY())</f>
         <v>253</v>
       </c>
       <c r="M24" s="12">
-        <f t="shared" ca="1" si="1"/>
+        <f ca="1">IF($C24="","",$C24+365-TODAY())</f>
         <v>287</v>
       </c>
       <c r="N24" s="12">
-        <f t="shared" ca="1" si="2"/>
+        <f ca="1">IF($C24="","",$C24+120-TODAY())</f>
         <v>42</v>
       </c>
       <c r="O24" s="6">
@@ -10967,15 +10976,15 @@
         <v>46276</v>
       </c>
       <c r="L25" s="12">
-        <f t="shared" ca="1" si="0"/>
+        <f ca="1">IF($O25="","",$O25-TODAY())</f>
         <v>254</v>
       </c>
       <c r="M25" s="12">
-        <f t="shared" ca="1" si="1"/>
+        <f ca="1">IF($C25="","",$C25+365-TODAY())</f>
         <v>351</v>
       </c>
       <c r="N25" s="12">
-        <f t="shared" ca="1" si="2"/>
+        <f ca="1">IF($C25="","",$C25+120-TODAY())</f>
         <v>106</v>
       </c>
       <c r="O25" s="6">
@@ -11087,11 +11096,11 @@
         <v>46255</v>
       </c>
       <c r="L26" s="12">
-        <f t="shared" ca="1" si="0"/>
+        <f ca="1">IF($O26="","",$O26-TODAY())</f>
         <v>-69</v>
       </c>
       <c r="M26" s="12">
-        <f t="shared" ca="1" si="1"/>
+        <f ca="1">IF($C26="","",$C26+365-TODAY())</f>
         <v>245</v>
       </c>
       <c r="N26" s="12">
@@ -11199,11 +11208,11 @@
       </c>
       <c r="K27" s="3"/>
       <c r="L27" s="12">
-        <f t="shared" ca="1" si="0"/>
+        <f ca="1">IF($O27="","",$O27-TODAY())</f>
         <v>-49</v>
       </c>
       <c r="M27" s="12" t="str">
-        <f t="shared" ca="1" si="1"/>
+        <f ca="1">IF($C27="","",$C27+365-TODAY())</f>
         <v/>
       </c>
       <c r="N27" s="12" t="str">
@@ -11315,7 +11324,7 @@
         <v>46253</v>
       </c>
       <c r="L28" s="12">
-        <f t="shared" ca="1" si="0"/>
+        <f ca="1">IF($O28="","",$O28-TODAY())</f>
         <v>-49</v>
       </c>
       <c r="M28" s="12">
@@ -11431,16 +11440,16 @@
         <v>46253</v>
       </c>
       <c r="L29" s="12">
-        <f t="shared" ca="1" si="0"/>
+        <f ca="1">IF($O29="","",$O29-TODAY())</f>
         <v>-46</v>
       </c>
       <c r="M29" s="12">
-        <f ca="1">IF($C29="","",$C29+365-TODAY())</f>
-        <v>267</v>
+        <f ca="1">IF($F29="","",$F29+90-TODAY())</f>
+        <v>-47</v>
       </c>
       <c r="N29" s="12">
         <f ca="1">IF($C29="","",$C29+365-TODAY())</f>
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="O29" s="6">
         <v>46236</v>
@@ -11452,10 +11461,10 @@
         <v>182</v>
       </c>
       <c r="R29" s="5" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="S29" s="5" t="s">
-        <v>50</v>
+        <v>234</v>
       </c>
       <c r="T29" s="5" t="s">
         <v>51</v>
@@ -11549,7 +11558,7 @@
         <v>46253</v>
       </c>
       <c r="L30" s="12">
-        <f t="shared" ca="1" si="0"/>
+        <f ca="1">IF($O30="","",$O30-TODAY())</f>
         <v>-42</v>
       </c>
       <c r="M30" s="12">
@@ -11667,7 +11676,7 @@
         <v>46253</v>
       </c>
       <c r="L31" s="12">
-        <f t="shared" ca="1" si="0"/>
+        <f ca="1">IF($O31="","",$O31-TODAY())</f>
         <v>-42</v>
       </c>
       <c r="M31" s="12">
@@ -11789,7 +11798,7 @@
         <v>46253</v>
       </c>
       <c r="L32" s="12">
-        <f t="shared" ca="1" si="0"/>
+        <f ca="1">IF($O32="","",$O32-TODAY())</f>
         <v>-39</v>
       </c>
       <c r="M32" s="12">
@@ -11907,16 +11916,16 @@
         <v>46255</v>
       </c>
       <c r="L33" s="12">
-        <f t="shared" ca="1" si="0"/>
+        <f ca="1">IF($O33="","",$O33-TODAY())</f>
         <v>-39</v>
       </c>
       <c r="M33" s="12">
-        <f ca="1">IF($C33="","",$C33+365-TODAY())</f>
-        <v>286</v>
+        <f ca="1">IF($F33="","",$F33+90-TODAY())</f>
+        <v>-40</v>
       </c>
       <c r="N33" s="12">
         <f ca="1">IF($C33="","",$C33+365-TODAY())</f>
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="O33" s="6">
         <v>46243</v>
@@ -11928,10 +11937,10 @@
         <v>182</v>
       </c>
       <c r="R33" s="5" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="S33" s="5" t="s">
-        <v>50</v>
+        <v>234</v>
       </c>
       <c r="T33" s="5" t="s">
         <v>51</v>
@@ -12027,7 +12036,7 @@
         <v>46244</v>
       </c>
       <c r="L34" s="12" t="str">
-        <f t="shared" ca="1" si="0"/>
+        <f ca="1">IF($O34="","",$O34-TODAY())</f>
         <v/>
       </c>
       <c r="M34" s="12"/>
@@ -12123,7 +12132,7 @@
         <v>46244</v>
       </c>
       <c r="L35" s="12" t="str">
-        <f t="shared" ca="1" si="0"/>
+        <f ca="1">IF($O35="","",$O35-TODAY())</f>
         <v/>
       </c>
       <c r="M35" s="12"/>
@@ -12479,7 +12488,7 @@
         <v>46248</v>
       </c>
       <c r="L2" s="12">
-        <f t="shared" ref="L2:L7" ca="1" si="0">IF($O2="","",$O2-TODAY())</f>
+        <f ca="1">IF($O2="","",$O2-TODAY())</f>
         <v>-16</v>
       </c>
       <c r="M2" s="12">
@@ -12599,7 +12608,7 @@
         <v>46255</v>
       </c>
       <c r="L3" s="12">
-        <f t="shared" ca="1" si="0"/>
+        <f ca="1">IF($O3="","",$O3-TODAY())</f>
         <v>236</v>
       </c>
       <c r="M3" s="12">
@@ -12723,7 +12732,7 @@
         <v>46224</v>
       </c>
       <c r="L4" s="12">
-        <f t="shared" ca="1" si="0"/>
+        <f ca="1">IF($O4="","",$O4-TODAY())</f>
         <v>243</v>
       </c>
       <c r="M4" s="12">
@@ -12849,7 +12858,7 @@
         <v>46255</v>
       </c>
       <c r="L5" s="12">
-        <f t="shared" ca="1" si="0"/>
+        <f ca="1">IF($O5="","",$O5-TODAY())</f>
         <v>-39</v>
       </c>
       <c r="M5" s="12">
@@ -12971,16 +12980,16 @@
         <v>46256</v>
       </c>
       <c r="L6" s="12">
-        <f t="shared" ca="1" si="0"/>
+        <f ca="1">IF($O6="","",$O6-TODAY())</f>
         <v>-39</v>
       </c>
       <c r="M6" s="12">
         <f ca="1">IF($F6="","",$F6+90-TODAY())</f>
-        <v>-39</v>
+        <v>-40</v>
       </c>
       <c r="N6" s="12">
-        <f ca="1">IF($C6="","",$C6+60-TODAY())</f>
-        <v>-26</v>
+        <f ca="1">IF($C6="","",$C6+540-TODAY())</f>
+        <v>453</v>
       </c>
       <c r="O6" s="6">
         <v>46243</v>
@@ -12998,7 +13007,7 @@
         <v>234</v>
       </c>
       <c r="T6" s="5" t="s">
-        <v>169</v>
+        <v>686</v>
       </c>
       <c r="U6" s="5" t="s">
         <v>50</v>
@@ -13091,7 +13100,7 @@
       </c>
       <c r="K7" s="3"/>
       <c r="L7" s="12" t="str">
-        <f t="shared" ca="1" si="0"/>
+        <f ca="1">IF($O7="","",$O7-TODAY())</f>
         <v/>
       </c>
       <c r="M7" s="12"/>
@@ -15661,12 +15670,12 @@
         <v>-44</v>
       </c>
       <c r="M21" s="12">
-        <f ca="1">IF($C21="","",$C21+365-TODAY())</f>
-        <v>280</v>
+        <f ca="1">IF($F21="","",$F21+90-TODAY())</f>
+        <v>-45</v>
       </c>
       <c r="N21" s="12">
         <f ca="1">IF($C21="","",$C21+365-TODAY())</f>
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="O21" s="6">
         <v>46238</v>
@@ -15678,10 +15687,10 @@
         <v>182</v>
       </c>
       <c r="R21" s="5" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="S21" s="5" t="s">
-        <v>50</v>
+        <v>234</v>
       </c>
       <c r="T21" s="5" t="s">
         <v>51</v>
@@ -17858,25 +17867,29 @@
       <c r="K16" s="3">
         <v>46259</v>
       </c>
-      <c r="L16" s="12" t="str">
+      <c r="L16" s="12">
         <f ca="1">IF($O16="","",$O16-TODAY())</f>
-        <v/>
+        <v>-44</v>
       </c>
       <c r="M16" s="12">
-        <f ca="1">IF($C16="","",$C16+180-TODAY())</f>
-        <v>134</v>
+        <f ca="1">IF($C16="","",$C16+365-TODAY())</f>
+        <v>318</v>
       </c>
       <c r="N16" s="12">
         <f ca="1">IF($C16="","",$C16+365-TODAY())</f>
-        <v>319</v>
-      </c>
-      <c r="O16" s="6"/>
-      <c r="P16" s="5"/>
+        <v>318</v>
+      </c>
+      <c r="O16" s="6">
+        <v>46239</v>
+      </c>
+      <c r="P16" s="5" t="s">
+        <v>47</v>
+      </c>
       <c r="Q16" s="5" t="s">
         <v>170</v>
       </c>
       <c r="R16" s="5" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="S16" s="5" t="s">
         <v>50</v>

--- a/Specialty Claims 2026-S1/2026-05 May - Specialty Claims.xlsx
+++ b/Specialty Claims 2026-S1/2026-05 May - Specialty Claims.xlsx
@@ -235,20 +235,6 @@
         </r>
       </text>
     </comment>
-    <comment ref="AO1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-00000E000000}">
-      <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color theme="1"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-            <scheme val="minor"/>
-          </rPr>
-          <t>The rows of the original 'Merged' sheet that were combined into this claim, so every claim traces back to the source. Informational only.</t>
-        </r>
-      </text>
-    </comment>
   </commentList>
 </comments>
 </file>
@@ -438,20 +424,6 @@
             <scheme val="minor"/>
           </rPr>
           <t>Whether the carrier counts the appeal window from the date of service or from the processed date.</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="AO1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0100-00000E000000}">
-      <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color theme="1"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-            <scheme val="minor"/>
-          </rPr>
-          <t>The rows of the original 'Merged' sheet that were combined into this claim, so every claim traces back to the source. Informational only.</t>
         </r>
       </text>
     </comment>
@@ -647,20 +619,6 @@
         </r>
       </text>
     </comment>
-    <comment ref="AO1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0200-00000E000000}">
-      <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color theme="1"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-            <scheme val="minor"/>
-          </rPr>
-          <t>The rows of the original 'Merged' sheet that were combined into this claim, so every claim traces back to the source. Informational only.</t>
-        </r>
-      </text>
-    </comment>
   </commentList>
 </comments>
 </file>
@@ -853,20 +811,6 @@
         </r>
       </text>
     </comment>
-    <comment ref="AO1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0300-00000E000000}">
-      <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color theme="1"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-            <scheme val="minor"/>
-          </rPr>
-          <t>The rows of the original 'Merged' sheet that were combined into this claim, so every claim traces back to the source. Informational only.</t>
-        </r>
-      </text>
-    </comment>
   </commentList>
 </comments>
 </file>
@@ -1056,20 +1000,6 @@
             <scheme val="minor"/>
           </rPr>
           <t>Whether the carrier counts the appeal window from the date of service or from the processed date.</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="AO1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0400-00000E000000}">
-      <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color theme="1"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-            <scheme val="minor"/>
-          </rPr>
-          <t>The rows of the original 'Merged' sheet that were combined into this claim, so every claim traces back to the source. Informational only.</t>
         </r>
       </text>
     </comment>
@@ -4561,7 +4491,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:AO31"/>
+  <dimension ref="A1:AN31"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="14" customWidth="1"/>
@@ -4599,10 +4529,9 @@
     <col min="38" max="38" width="24" customWidth="1"/>
     <col min="39" max="39" width="14" customWidth="1"/>
     <col min="40" max="40" width="11" customWidth="1"/>
-    <col min="41" max="41" width="14" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:41" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:40" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="11" t="s">
         <v>0</v>
       </c>
@@ -4723,11 +4652,8 @@
       <c r="AN1" s="11" t="s">
         <v>39</v>
       </c>
-      <c r="AO1" s="11" t="s">
-        <v>40</v>
-      </c>
     </row>
-    <row r="2" spans="1:41" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
         <v>41</v>
       </c>
@@ -4833,11 +4759,8 @@
       <c r="AN2" s="5" t="s">
         <v>56</v>
       </c>
-      <c r="AO2" s="5" t="s">
-        <v>57</v>
-      </c>
     </row>
-    <row r="3" spans="1:41" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
         <v>41</v>
       </c>
@@ -4943,11 +4866,8 @@
       <c r="AN3" s="5" t="s">
         <v>56</v>
       </c>
-      <c r="AO3" s="5" t="s">
-        <v>62</v>
-      </c>
     </row>
-    <row r="4" spans="1:41" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
         <v>41</v>
       </c>
@@ -5053,11 +4973,8 @@
       <c r="AN4" s="5" t="s">
         <v>56</v>
       </c>
-      <c r="AO4" s="5" t="s">
-        <v>72</v>
-      </c>
     </row>
-    <row r="5" spans="1:41" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
         <v>41</v>
       </c>
@@ -5169,11 +5086,8 @@
       <c r="AN5" s="5" t="s">
         <v>56</v>
       </c>
-      <c r="AO5" s="5" t="s">
-        <v>81</v>
-      </c>
     </row>
-    <row r="6" spans="1:41" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
         <v>41</v>
       </c>
@@ -5285,11 +5199,8 @@
       <c r="AN6" s="5" t="s">
         <v>56</v>
       </c>
-      <c r="AO6" s="5" t="s">
-        <v>87</v>
-      </c>
     </row>
-    <row r="7" spans="1:41" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
         <v>41</v>
       </c>
@@ -5395,11 +5306,8 @@
       <c r="AN7" s="5" t="s">
         <v>56</v>
       </c>
-      <c r="AO7" s="5" t="s">
-        <v>93</v>
-      </c>
     </row>
-    <row r="8" spans="1:41" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
         <v>94</v>
       </c>
@@ -5511,11 +5419,8 @@
       <c r="AN8" s="5" t="s">
         <v>56</v>
       </c>
-      <c r="AO8" s="5" t="s">
-        <v>100</v>
-      </c>
     </row>
-    <row r="9" spans="1:41" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A9" s="2" t="s">
         <v>94</v>
       </c>
@@ -5625,11 +5530,8 @@
       <c r="AN9" s="5" t="s">
         <v>56</v>
       </c>
-      <c r="AO9" s="5" t="s">
-        <v>106</v>
-      </c>
     </row>
-    <row r="10" spans="1:41" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A10" s="2" t="s">
         <v>107</v>
       </c>
@@ -5735,11 +5637,8 @@
       <c r="AN10" s="5" t="s">
         <v>56</v>
       </c>
-      <c r="AO10" s="5" t="s">
-        <v>111</v>
-      </c>
     </row>
-    <row r="11" spans="1:41" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A11" s="2" t="s">
         <v>676</v>
       </c>
@@ -5847,11 +5746,8 @@
       <c r="AN11" s="5" t="s">
         <v>56</v>
       </c>
-      <c r="AO11" s="5" t="s">
-        <v>117</v>
-      </c>
     </row>
-    <row r="12" spans="1:41" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A12" s="2" t="s">
         <v>129</v>
       </c>
@@ -5967,11 +5863,8 @@
       <c r="AN12" s="5" t="s">
         <v>56</v>
       </c>
-      <c r="AO12" s="5" t="s">
-        <v>128</v>
-      </c>
     </row>
-    <row r="13" spans="1:41" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A13" s="2" t="s">
         <v>129</v>
       </c>
@@ -6079,11 +5972,8 @@
       <c r="AN13" s="5" t="s">
         <v>56</v>
       </c>
-      <c r="AO13" s="5" t="s">
-        <v>139</v>
-      </c>
     </row>
-    <row r="14" spans="1:41" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A14" s="2" t="s">
         <v>94</v>
       </c>
@@ -6193,11 +6083,8 @@
       <c r="AN14" s="5" t="s">
         <v>56</v>
       </c>
-      <c r="AO14" s="5" t="s">
-        <v>146</v>
-      </c>
     </row>
-    <row r="15" spans="1:41" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A15" s="2" t="s">
         <v>41</v>
       </c>
@@ -6309,11 +6196,8 @@
       <c r="AN15" s="5" t="s">
         <v>56</v>
       </c>
-      <c r="AO15" s="5" t="s">
-        <v>150</v>
-      </c>
     </row>
-    <row r="16" spans="1:41" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A16" s="2" t="s">
         <v>129</v>
       </c>
@@ -6425,11 +6309,8 @@
       <c r="AN16" s="5" t="s">
         <v>56</v>
       </c>
-      <c r="AO16" s="5" t="s">
-        <v>152</v>
-      </c>
     </row>
-    <row r="17" spans="1:41" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A17" s="2" t="s">
         <v>130</v>
       </c>
@@ -6539,11 +6420,8 @@
       <c r="AN17" s="5" t="s">
         <v>56</v>
       </c>
-      <c r="AO17" s="5" t="s">
-        <v>155</v>
-      </c>
     </row>
-    <row r="18" spans="1:41" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A18" s="2" t="s">
         <v>129</v>
       </c>
@@ -6655,11 +6533,8 @@
       <c r="AN18" s="5" t="s">
         <v>56</v>
       </c>
-      <c r="AO18" s="5" t="s">
-        <v>158</v>
-      </c>
     </row>
-    <row r="19" spans="1:41" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A19" s="2" t="s">
         <v>41</v>
       </c>
@@ -6771,11 +6646,8 @@
       <c r="AN19" s="5" t="s">
         <v>56</v>
       </c>
-      <c r="AO19" s="5" t="s">
-        <v>160</v>
-      </c>
     </row>
-    <row r="20" spans="1:41" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A20" s="2" t="s">
         <v>41</v>
       </c>
@@ -6887,11 +6759,8 @@
       <c r="AN20" s="5" t="s">
         <v>56</v>
       </c>
-      <c r="AO20" s="5" t="s">
-        <v>162</v>
-      </c>
     </row>
-    <row r="21" spans="1:41" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A21" s="2" t="s">
         <v>41</v>
       </c>
@@ -7003,11 +6872,8 @@
       <c r="AN21" s="5" t="s">
         <v>56</v>
       </c>
-      <c r="AO21" s="5" t="s">
-        <v>165</v>
-      </c>
     </row>
-    <row r="22" spans="1:41" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A22" s="2" t="s">
         <v>41</v>
       </c>
@@ -7113,11 +6979,8 @@
       <c r="AN22" s="5" t="s">
         <v>56</v>
       </c>
-      <c r="AO22" s="5" t="s">
-        <v>171</v>
-      </c>
     </row>
-    <row r="23" spans="1:41" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A23" s="2" t="s">
         <v>41</v>
       </c>
@@ -7227,11 +7090,8 @@
       <c r="AN23" s="5" t="s">
         <v>56</v>
       </c>
-      <c r="AO23" s="5" t="s">
-        <v>176</v>
-      </c>
     </row>
-    <row r="24" spans="1:41" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A24" s="2" t="s">
         <v>129</v>
       </c>
@@ -7341,11 +7201,8 @@
       <c r="AN24" s="5" t="s">
         <v>56</v>
       </c>
-      <c r="AO24" s="5" t="s">
-        <v>183</v>
-      </c>
     </row>
-    <row r="25" spans="1:41" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A25" s="2" t="s">
         <v>94</v>
       </c>
@@ -7437,11 +7294,8 @@
       <c r="AN25" s="5" t="s">
         <v>56</v>
       </c>
-      <c r="AO25" s="5" t="s">
-        <v>189</v>
-      </c>
     </row>
-    <row r="26" spans="1:41" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A26" s="2" t="s">
         <v>676</v>
       </c>
@@ -7527,11 +7381,8 @@
       <c r="AN26" s="5" t="s">
         <v>56</v>
       </c>
-      <c r="AO26" s="5" t="s">
-        <v>195</v>
-      </c>
     </row>
-    <row r="27" spans="1:41" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A27" s="2" t="s">
         <v>94</v>
       </c>
@@ -7623,11 +7474,8 @@
       <c r="AN27" s="5" t="s">
         <v>56</v>
       </c>
-      <c r="AO27" s="5" t="s">
-        <v>198</v>
-      </c>
     </row>
-    <row r="28" spans="1:41" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A28" s="2" t="s">
         <v>94</v>
       </c>
@@ -7721,11 +7569,8 @@
       <c r="AN28" s="5" t="s">
         <v>56</v>
       </c>
-      <c r="AO28" s="5" t="s">
-        <v>200</v>
-      </c>
     </row>
-    <row r="29" spans="1:41" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A29" s="2" t="s">
         <v>94</v>
       </c>
@@ -7817,11 +7662,8 @@
       <c r="AN29" s="5" t="s">
         <v>56</v>
       </c>
-      <c r="AO29" s="5" t="s">
-        <v>202</v>
-      </c>
     </row>
-    <row r="30" spans="1:41" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A30" s="2" t="s">
         <v>129</v>
       </c>
@@ -7911,11 +7753,8 @@
       <c r="AN30" s="5" t="s">
         <v>56</v>
       </c>
-      <c r="AO30" s="5" t="s">
-        <v>205</v>
-      </c>
     </row>
-    <row r="31" spans="1:41" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A31" s="2" t="s">
         <v>676</v>
       </c>
@@ -8001,12 +7840,9 @@
       <c r="AN31" s="5" t="s">
         <v>56</v>
       </c>
-      <c r="AO31" s="5" t="s">
-        <v>207</v>
-      </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AO31" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
+  <autoFilter ref="A1:AN31" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
   <conditionalFormatting sqref="L2:L31 O2:U31">
     <cfRule type="expression" dxfId="94" priority="1">
       <formula>AND($L2&lt;&gt;"", $L2&gt;=0, $L2&lt;=5)</formula>
@@ -8070,7 +7906,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:AO48"/>
+  <dimension ref="A1:AN48"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="14" customWidth="1"/>
@@ -8108,10 +7944,9 @@
     <col min="38" max="38" width="24" customWidth="1"/>
     <col min="39" max="39" width="14" customWidth="1"/>
     <col min="40" max="40" width="11" customWidth="1"/>
-    <col min="41" max="41" width="14" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:41" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:40" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="11" t="s">
         <v>0</v>
       </c>
@@ -8232,11 +8067,8 @@
       <c r="AN1" s="11" t="s">
         <v>39</v>
       </c>
-      <c r="AO1" s="11" t="s">
-        <v>40</v>
-      </c>
     </row>
-    <row r="2" spans="1:41" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
         <v>107</v>
       </c>
@@ -8350,11 +8182,8 @@
       <c r="AN2" s="5" t="s">
         <v>220</v>
       </c>
-      <c r="AO2" s="5" t="s">
-        <v>221</v>
-      </c>
     </row>
-    <row r="3" spans="1:41" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
         <v>94</v>
       </c>
@@ -8466,11 +8295,8 @@
       <c r="AN3" s="5" t="s">
         <v>220</v>
       </c>
-      <c r="AO3" s="5" t="s">
-        <v>228</v>
-      </c>
     </row>
-    <row r="4" spans="1:41" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
         <v>94</v>
       </c>
@@ -8584,11 +8410,8 @@
       <c r="AN4" s="5" t="s">
         <v>220</v>
       </c>
-      <c r="AO4" s="5" t="s">
-        <v>238</v>
-      </c>
     </row>
-    <row r="5" spans="1:41" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
         <v>129</v>
       </c>
@@ -8702,11 +8525,8 @@
       <c r="AN5" s="5" t="s">
         <v>220</v>
       </c>
-      <c r="AO5" s="5" t="s">
-        <v>247</v>
-      </c>
     </row>
-    <row r="6" spans="1:41" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
         <v>129</v>
       </c>
@@ -8820,11 +8640,8 @@
       <c r="AN6" s="5" t="s">
         <v>220</v>
       </c>
-      <c r="AO6" s="5" t="s">
-        <v>253</v>
-      </c>
     </row>
-    <row r="7" spans="1:41" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
         <v>129</v>
       </c>
@@ -8940,11 +8757,8 @@
       <c r="AN7" s="5" t="s">
         <v>220</v>
       </c>
-      <c r="AO7" s="5" t="s">
-        <v>260</v>
-      </c>
     </row>
-    <row r="8" spans="1:41" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
         <v>129</v>
       </c>
@@ -9049,11 +8863,8 @@
       <c r="AN8" s="5" t="s">
         <v>220</v>
       </c>
-      <c r="AO8" s="5" t="s">
-        <v>266</v>
-      </c>
     </row>
-    <row r="9" spans="1:41" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A9" s="2" t="s">
         <v>267</v>
       </c>
@@ -9167,11 +8978,8 @@
       <c r="AN9" s="5" t="s">
         <v>220</v>
       </c>
-      <c r="AO9" s="5" t="s">
-        <v>275</v>
-      </c>
     </row>
-    <row r="10" spans="1:41" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A10" s="2" t="s">
         <v>94</v>
       </c>
@@ -9289,11 +9097,8 @@
       <c r="AN10" s="5" t="s">
         <v>220</v>
       </c>
-      <c r="AO10" s="5" t="s">
-        <v>281</v>
-      </c>
     </row>
-    <row r="11" spans="1:41" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A11" s="2" t="s">
         <v>94</v>
       </c>
@@ -9407,11 +9212,8 @@
       <c r="AN11" s="5" t="s">
         <v>220</v>
       </c>
-      <c r="AO11" s="5" t="s">
-        <v>286</v>
-      </c>
     </row>
-    <row r="12" spans="1:41" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A12" s="2" t="s">
         <v>676</v>
       </c>
@@ -9523,11 +9325,8 @@
       <c r="AN12" s="5" t="s">
         <v>220</v>
       </c>
-      <c r="AO12" s="5" t="s">
-        <v>291</v>
-      </c>
     </row>
-    <row r="13" spans="1:41" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A13" s="2" t="s">
         <v>94</v>
       </c>
@@ -9643,11 +9442,8 @@
       <c r="AN13" s="5" t="s">
         <v>220</v>
       </c>
-      <c r="AO13" s="5" t="s">
-        <v>297</v>
-      </c>
     </row>
-    <row r="14" spans="1:41" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A14" s="2" t="s">
         <v>94</v>
       </c>
@@ -9759,11 +9555,8 @@
       <c r="AN14" s="5" t="s">
         <v>220</v>
       </c>
-      <c r="AO14" s="5" t="s">
-        <v>306</v>
-      </c>
     </row>
-    <row r="15" spans="1:41" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A15" s="2" t="s">
         <v>130</v>
       </c>
@@ -9875,11 +9668,8 @@
       <c r="AN15" s="5" t="s">
         <v>220</v>
       </c>
-      <c r="AO15" s="5" t="s">
-        <v>312</v>
-      </c>
     </row>
-    <row r="16" spans="1:41" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A16" s="2" t="s">
         <v>130</v>
       </c>
@@ -9993,11 +9783,8 @@
       <c r="AN16" s="5" t="s">
         <v>220</v>
       </c>
-      <c r="AO16" s="5" t="s">
-        <v>321</v>
-      </c>
     </row>
-    <row r="17" spans="1:41" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A17" s="2" t="s">
         <v>94</v>
       </c>
@@ -10113,11 +9900,8 @@
       <c r="AN17" s="5" t="s">
         <v>220</v>
       </c>
-      <c r="AO17" s="5" t="s">
-        <v>327</v>
-      </c>
     </row>
-    <row r="18" spans="1:41" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A18" s="2" t="s">
         <v>41</v>
       </c>
@@ -10233,11 +10017,8 @@
       <c r="AN18" s="5" t="s">
         <v>220</v>
       </c>
-      <c r="AO18" s="5" t="s">
-        <v>331</v>
-      </c>
     </row>
-    <row r="19" spans="1:41" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A19" s="2" t="s">
         <v>129</v>
       </c>
@@ -10351,11 +10132,8 @@
       <c r="AN19" s="5" t="s">
         <v>220</v>
       </c>
-      <c r="AO19" s="5" t="s">
-        <v>339</v>
-      </c>
     </row>
-    <row r="20" spans="1:41" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A20" s="2" t="s">
         <v>129</v>
       </c>
@@ -10467,11 +10245,8 @@
       <c r="AN20" s="5" t="s">
         <v>220</v>
       </c>
-      <c r="AO20" s="5" t="s">
-        <v>345</v>
-      </c>
     </row>
-    <row r="21" spans="1:41" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A21" s="2" t="s">
         <v>129</v>
       </c>
@@ -10585,11 +10360,8 @@
       <c r="AN21" s="5" t="s">
         <v>220</v>
       </c>
-      <c r="AO21" s="5" t="s">
-        <v>353</v>
-      </c>
     </row>
-    <row r="22" spans="1:41" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A22" s="2" t="s">
         <v>130</v>
       </c>
@@ -10701,11 +10473,8 @@
       <c r="AN22" s="5" t="s">
         <v>220</v>
       </c>
-      <c r="AO22" s="5" t="s">
-        <v>359</v>
-      </c>
     </row>
-    <row r="23" spans="1:41" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A23" s="2" t="s">
         <v>130</v>
       </c>
@@ -10815,11 +10584,8 @@
       <c r="AN23" s="5" t="s">
         <v>220</v>
       </c>
-      <c r="AO23" s="5" t="s">
-        <v>361</v>
-      </c>
     </row>
-    <row r="24" spans="1:41" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A24" s="2" t="s">
         <v>94</v>
       </c>
@@ -10937,11 +10703,8 @@
       <c r="AN24" s="5" t="s">
         <v>220</v>
       </c>
-      <c r="AO24" s="5" t="s">
-        <v>370</v>
-      </c>
     </row>
-    <row r="25" spans="1:41" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A25" s="2" t="s">
         <v>129</v>
       </c>
@@ -11057,11 +10820,8 @@
       <c r="AN25" s="5" t="s">
         <v>220</v>
       </c>
-      <c r="AO25" s="5" t="s">
-        <v>373</v>
-      </c>
     </row>
-    <row r="26" spans="1:41" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A26" s="2" t="s">
         <v>94</v>
       </c>
@@ -11173,11 +10933,8 @@
       <c r="AN26" s="5" t="s">
         <v>220</v>
       </c>
-      <c r="AO26" s="5" t="s">
-        <v>379</v>
-      </c>
     </row>
-    <row r="27" spans="1:41" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A27" s="2" t="s">
         <v>676</v>
       </c>
@@ -11285,11 +11042,8 @@
       <c r="AN27" s="5" t="s">
         <v>220</v>
       </c>
-      <c r="AO27" s="5" t="s">
-        <v>382</v>
-      </c>
     </row>
-    <row r="28" spans="1:41" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A28" s="2" t="s">
         <v>129</v>
       </c>
@@ -11401,11 +11155,8 @@
       <c r="AN28" s="5" t="s">
         <v>220</v>
       </c>
-      <c r="AO28" s="5" t="s">
-        <v>385</v>
-      </c>
     </row>
-    <row r="29" spans="1:41" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A29" s="2" t="s">
         <v>94</v>
       </c>
@@ -11519,11 +11270,8 @@
       <c r="AN29" s="5" t="s">
         <v>220</v>
       </c>
-      <c r="AO29" s="5" t="s">
-        <v>391</v>
-      </c>
     </row>
-    <row r="30" spans="1:41" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A30" s="2" t="s">
         <v>94</v>
       </c>
@@ -11637,11 +11385,8 @@
       <c r="AN30" s="5" t="s">
         <v>220</v>
       </c>
-      <c r="AO30" s="5" t="s">
-        <v>398</v>
-      </c>
     </row>
-    <row r="31" spans="1:41" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A31" s="2" t="s">
         <v>129</v>
       </c>
@@ -11759,11 +11504,8 @@
       <c r="AN31" s="5" t="s">
         <v>220</v>
       </c>
-      <c r="AO31" s="5" t="s">
-        <v>405</v>
-      </c>
     </row>
-    <row r="32" spans="1:41" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A32" s="2" t="s">
         <v>129</v>
       </c>
@@ -11877,11 +11619,8 @@
       <c r="AN32" s="5" t="s">
         <v>220</v>
       </c>
-      <c r="AO32" s="5" t="s">
-        <v>409</v>
-      </c>
     </row>
-    <row r="33" spans="1:41" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A33" s="2" t="s">
         <v>676</v>
       </c>
@@ -11997,11 +11736,8 @@
       <c r="AN33" s="5" t="s">
         <v>220</v>
       </c>
-      <c r="AO33" s="5" t="s">
-        <v>412</v>
-      </c>
     </row>
-    <row r="34" spans="1:41" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A34" s="2" t="s">
         <v>94</v>
       </c>
@@ -12093,11 +11829,8 @@
       <c r="AN34" s="5" t="s">
         <v>220</v>
       </c>
-      <c r="AO34" s="5" t="s">
-        <v>415</v>
-      </c>
     </row>
-    <row r="35" spans="1:41" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A35" s="2" t="s">
         <v>94</v>
       </c>
@@ -12193,20 +11926,17 @@
       <c r="AN35" s="5" t="s">
         <v>220</v>
       </c>
-      <c r="AO35" s="5" t="s">
-        <v>418</v>
-      </c>
     </row>
-    <row r="47" spans="1:41" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:40" x14ac:dyDescent="0.25">
       <c r="F47" s="13"/>
     </row>
-    <row r="48" spans="1:41" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:40" x14ac:dyDescent="0.25">
       <c r="G48" s="13"/>
       <c r="H48" s="13"/>
       <c r="J48" s="14"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AO35" xr:uid="{00000000-0009-0000-0000-000001000000}"/>
+  <autoFilter ref="A1:AN35" xr:uid="{00000000-0009-0000-0000-000001000000}"/>
   <conditionalFormatting sqref="L2:L35">
     <cfRule type="expression" dxfId="79" priority="1">
       <formula>AND($L2&lt;&gt;"", $L2&gt;=0, $L2&lt;=5)</formula>
@@ -12287,7 +12017,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
-  <dimension ref="A1:AO7"/>
+  <dimension ref="A1:AN7"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="14" customWidth="1"/>
@@ -12325,10 +12055,9 @@
     <col min="38" max="38" width="24" customWidth="1"/>
     <col min="39" max="39" width="14" customWidth="1"/>
     <col min="40" max="40" width="11" customWidth="1"/>
-    <col min="41" max="41" width="14" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:41" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:40" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="11" t="s">
         <v>0</v>
       </c>
@@ -12449,11 +12178,8 @@
       <c r="AN1" s="11" t="s">
         <v>39</v>
       </c>
-      <c r="AO1" s="11" t="s">
-        <v>40</v>
-      </c>
     </row>
-    <row r="2" spans="1:41" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
         <v>129</v>
       </c>
@@ -12569,11 +12295,8 @@
       <c r="AN2" s="5" t="s">
         <v>428</v>
       </c>
-      <c r="AO2" s="5" t="s">
-        <v>429</v>
-      </c>
     </row>
-    <row r="3" spans="1:41" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
         <v>94</v>
       </c>
@@ -12693,11 +12416,8 @@
       <c r="AN3" s="5" t="s">
         <v>428</v>
       </c>
-      <c r="AO3" s="5" t="s">
-        <v>437</v>
-      </c>
     </row>
-    <row r="4" spans="1:41" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
         <v>130</v>
       </c>
@@ -12819,11 +12539,8 @@
       <c r="AN4" s="5" t="s">
         <v>428</v>
       </c>
-      <c r="AO4" s="5" t="s">
-        <v>444</v>
-      </c>
     </row>
-    <row r="5" spans="1:41" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
         <v>129</v>
       </c>
@@ -12941,11 +12658,8 @@
       <c r="AN5" s="5" t="s">
         <v>428</v>
       </c>
-      <c r="AO5" s="5" t="s">
-        <v>451</v>
-      </c>
     </row>
-    <row r="6" spans="1:41" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
         <v>94</v>
       </c>
@@ -13065,11 +12779,8 @@
       <c r="AN6" s="5" t="s">
         <v>428</v>
       </c>
-      <c r="AO6" s="5" t="s">
-        <v>457</v>
-      </c>
     </row>
-    <row r="7" spans="1:41" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
         <v>676</v>
       </c>
@@ -13165,12 +12876,9 @@
       <c r="AN7" s="5" t="s">
         <v>428</v>
       </c>
-      <c r="AO7" s="5" t="s">
-        <v>462</v>
-      </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AO7" xr:uid="{00000000-0009-0000-0000-000002000000}"/>
+  <autoFilter ref="A1:AN7" xr:uid="{00000000-0009-0000-0000-000002000000}"/>
   <conditionalFormatting sqref="L2:L7">
     <cfRule type="expression" dxfId="59" priority="1">
       <formula>AND($L2&lt;&gt;"", $L2&gt;=0, $L2&lt;=5)</formula>
@@ -13251,7 +12959,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
-  <dimension ref="A1:AO23"/>
+  <dimension ref="A1:AN23"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="14" customWidth="1"/>
@@ -13289,10 +12997,9 @@
     <col min="38" max="38" width="24" customWidth="1"/>
     <col min="39" max="39" width="14" customWidth="1"/>
     <col min="40" max="40" width="11" customWidth="1"/>
-    <col min="41" max="41" width="14" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:41" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:40" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="11" t="s">
         <v>0</v>
       </c>
@@ -13413,11 +13120,8 @@
       <c r="AN1" s="11" t="s">
         <v>39</v>
       </c>
-      <c r="AO1" s="11" t="s">
-        <v>40</v>
-      </c>
     </row>
-    <row r="2" spans="1:41" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
         <v>94</v>
       </c>
@@ -13527,11 +13231,8 @@
       <c r="AN2" s="5" t="s">
         <v>466</v>
       </c>
-      <c r="AO2" s="5" t="s">
-        <v>467</v>
-      </c>
     </row>
-    <row r="3" spans="1:41" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
         <v>94</v>
       </c>
@@ -13643,11 +13344,8 @@
       <c r="AN3" s="5" t="s">
         <v>466</v>
       </c>
-      <c r="AO3" s="5" t="s">
-        <v>473</v>
-      </c>
     </row>
-    <row r="4" spans="1:41" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
         <v>129</v>
       </c>
@@ -13761,11 +13459,8 @@
       <c r="AN4" s="5" t="s">
         <v>466</v>
       </c>
-      <c r="AO4" s="5" t="s">
-        <v>477</v>
-      </c>
     </row>
-    <row r="5" spans="1:41" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
         <v>94</v>
       </c>
@@ -13881,11 +13576,8 @@
       <c r="AN5" s="5" t="s">
         <v>466</v>
       </c>
-      <c r="AO5" s="5" t="s">
-        <v>483</v>
-      </c>
     </row>
-    <row r="6" spans="1:41" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
         <v>129</v>
       </c>
@@ -13995,11 +13687,8 @@
       <c r="AN6" s="5" t="s">
         <v>466</v>
       </c>
-      <c r="AO6" s="5" t="s">
-        <v>488</v>
-      </c>
     </row>
-    <row r="7" spans="1:41" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
         <v>94</v>
       </c>
@@ -14115,11 +13804,8 @@
       <c r="AN7" s="5" t="s">
         <v>466</v>
       </c>
-      <c r="AO7" s="5" t="s">
-        <v>495</v>
-      </c>
     </row>
-    <row r="8" spans="1:41" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
         <v>94</v>
       </c>
@@ -14231,11 +13917,8 @@
       <c r="AN8" s="5" t="s">
         <v>466</v>
       </c>
-      <c r="AO8" s="5" t="s">
-        <v>500</v>
-      </c>
     </row>
-    <row r="9" spans="1:41" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A9" s="2" t="s">
         <v>129</v>
       </c>
@@ -14353,11 +14036,8 @@
       <c r="AN9" s="5" t="s">
         <v>466</v>
       </c>
-      <c r="AO9" s="5" t="s">
-        <v>506</v>
-      </c>
     </row>
-    <row r="10" spans="1:41" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A10" s="2" t="s">
         <v>41</v>
       </c>
@@ -14469,11 +14149,8 @@
       <c r="AN10" s="5" t="s">
         <v>466</v>
       </c>
-      <c r="AO10" s="5" t="s">
-        <v>509</v>
-      </c>
     </row>
-    <row r="11" spans="1:41" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A11" s="2" t="s">
         <v>129</v>
       </c>
@@ -14583,11 +14260,8 @@
       <c r="AN11" s="5" t="s">
         <v>466</v>
       </c>
-      <c r="AO11" s="5" t="s">
-        <v>512</v>
-      </c>
     </row>
-    <row r="12" spans="1:41" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A12" s="2" t="s">
         <v>129</v>
       </c>
@@ -14697,11 +14371,8 @@
       <c r="AN12" s="5" t="s">
         <v>466</v>
       </c>
-      <c r="AO12" s="5" t="s">
-        <v>514</v>
-      </c>
     </row>
-    <row r="13" spans="1:41" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A13" s="2" t="s">
         <v>94</v>
       </c>
@@ -14813,11 +14484,8 @@
       <c r="AN13" s="5" t="s">
         <v>466</v>
       </c>
-      <c r="AO13" s="5" t="s">
-        <v>518</v>
-      </c>
     </row>
-    <row r="14" spans="1:41" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A14" s="2" t="s">
         <v>94</v>
       </c>
@@ -14933,11 +14601,8 @@
       <c r="AN14" s="5" t="s">
         <v>466</v>
       </c>
-      <c r="AO14" s="5" t="s">
-        <v>522</v>
-      </c>
     </row>
-    <row r="15" spans="1:41" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A15" s="2" t="s">
         <v>94</v>
       </c>
@@ -15047,11 +14712,8 @@
       <c r="AN15" s="5" t="s">
         <v>466</v>
       </c>
-      <c r="AO15" s="5" t="s">
-        <v>525</v>
-      </c>
     </row>
-    <row r="16" spans="1:41" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A16" s="2" t="s">
         <v>94</v>
       </c>
@@ -15163,11 +14825,8 @@
       <c r="AN16" s="5" t="s">
         <v>466</v>
       </c>
-      <c r="AO16" s="5" t="s">
-        <v>529</v>
-      </c>
     </row>
-    <row r="17" spans="1:41" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A17" s="2" t="s">
         <v>94</v>
       </c>
@@ -15281,11 +14940,8 @@
       <c r="AN17" s="5" t="s">
         <v>466</v>
       </c>
-      <c r="AO17" s="5" t="s">
-        <v>531</v>
-      </c>
     </row>
-    <row r="18" spans="1:41" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A18" s="2" t="s">
         <v>41</v>
       </c>
@@ -15399,11 +15055,8 @@
       <c r="AN18" s="5" t="s">
         <v>466</v>
       </c>
-      <c r="AO18" s="5" t="s">
-        <v>536</v>
-      </c>
     </row>
-    <row r="19" spans="1:41" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A19" s="2" t="s">
         <v>676</v>
       </c>
@@ -15513,11 +15166,8 @@
       <c r="AN19" s="5" t="s">
         <v>466</v>
       </c>
-      <c r="AO19" s="5" t="s">
-        <v>538</v>
-      </c>
     </row>
-    <row r="20" spans="1:41" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A20" s="2" t="s">
         <v>94</v>
       </c>
@@ -15627,11 +15277,8 @@
       <c r="AN20" s="5" t="s">
         <v>466</v>
       </c>
-      <c r="AO20" s="5" t="s">
-        <v>543</v>
-      </c>
     </row>
-    <row r="21" spans="1:41" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A21" s="2" t="s">
         <v>676</v>
       </c>
@@ -15743,11 +15390,8 @@
       <c r="AN21" s="5" t="s">
         <v>466</v>
       </c>
-      <c r="AO21" s="5" t="s">
-        <v>550</v>
-      </c>
     </row>
-    <row r="22" spans="1:41" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A22" s="2" t="s">
         <v>94</v>
       </c>
@@ -15863,11 +15507,8 @@
       <c r="AN22" s="5" t="s">
         <v>466</v>
       </c>
-      <c r="AO22" s="5" t="s">
-        <v>557</v>
-      </c>
     </row>
-    <row r="23" spans="1:41" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A23" s="2" t="s">
         <v>130</v>
       </c>
@@ -15957,12 +15598,9 @@
       <c r="AN23" s="5" t="s">
         <v>466</v>
       </c>
-      <c r="AO23" s="5" t="s">
-        <v>559</v>
-      </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AO23" xr:uid="{00000000-0009-0000-0000-000003000000}"/>
+  <autoFilter ref="A1:AN23" xr:uid="{00000000-0009-0000-0000-000003000000}"/>
   <conditionalFormatting sqref="L2:L23">
     <cfRule type="expression" dxfId="39" priority="1">
       <formula>AND($L2&lt;&gt;"", $L2&gt;=0, $L2&lt;=5)</formula>
@@ -16043,7 +15681,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
-  <dimension ref="A1:AO16"/>
+  <dimension ref="A1:AN16"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="14" customWidth="1"/>
@@ -16081,10 +15719,9 @@
     <col min="38" max="38" width="24" customWidth="1"/>
     <col min="39" max="39" width="14" customWidth="1"/>
     <col min="40" max="40" width="11" customWidth="1"/>
-    <col min="41" max="41" width="14" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:41" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:40" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="11" t="s">
         <v>0</v>
       </c>
@@ -16205,11 +15842,8 @@
       <c r="AN1" s="11" t="s">
         <v>39</v>
       </c>
-      <c r="AO1" s="11" t="s">
-        <v>40</v>
-      </c>
     </row>
-    <row r="2" spans="1:41" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
         <v>129</v>
       </c>
@@ -16319,11 +15953,8 @@
       <c r="AN2" s="5" t="s">
         <v>565</v>
       </c>
-      <c r="AO2" s="5" t="s">
-        <v>566</v>
-      </c>
     </row>
-    <row r="3" spans="1:41" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
         <v>94</v>
       </c>
@@ -16431,11 +16062,8 @@
       <c r="AN3" s="5" t="s">
         <v>565</v>
       </c>
-      <c r="AO3" s="5" t="s">
-        <v>571</v>
-      </c>
     </row>
-    <row r="4" spans="1:41" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
         <v>129</v>
       </c>
@@ -16547,11 +16175,8 @@
       <c r="AN4" s="5" t="s">
         <v>565</v>
       </c>
-      <c r="AO4" s="5" t="s">
-        <v>581</v>
-      </c>
     </row>
-    <row r="5" spans="1:41" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
         <v>94</v>
       </c>
@@ -16665,11 +16290,8 @@
       <c r="AN5" s="5" t="s">
         <v>565</v>
       </c>
-      <c r="AO5" s="5" t="s">
-        <v>586</v>
-      </c>
     </row>
-    <row r="6" spans="1:41" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
         <v>94</v>
       </c>
@@ -16785,11 +16407,8 @@
       <c r="AN6" s="5" t="s">
         <v>565</v>
       </c>
-      <c r="AO6" s="5" t="s">
-        <v>594</v>
-      </c>
     </row>
-    <row r="7" spans="1:41" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
         <v>129</v>
       </c>
@@ -16899,11 +16518,8 @@
       <c r="AN7" s="5" t="s">
         <v>565</v>
       </c>
-      <c r="AO7" s="5" t="s">
-        <v>598</v>
-      </c>
     </row>
-    <row r="8" spans="1:41" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
         <v>94</v>
       </c>
@@ -17015,11 +16631,8 @@
       <c r="AN8" s="5" t="s">
         <v>565</v>
       </c>
-      <c r="AO8" s="5" t="s">
-        <v>601</v>
-      </c>
     </row>
-    <row r="9" spans="1:41" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A9" s="2" t="s">
         <v>94</v>
       </c>
@@ -17133,11 +16746,8 @@
       <c r="AN9" s="5" t="s">
         <v>565</v>
       </c>
-      <c r="AO9" s="5" t="s">
-        <v>605</v>
-      </c>
     </row>
-    <row r="10" spans="1:41" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A10" s="2" t="s">
         <v>94</v>
       </c>
@@ -17247,11 +16857,8 @@
       <c r="AN10" s="5" t="s">
         <v>565</v>
       </c>
-      <c r="AO10" s="5" t="s">
-        <v>610</v>
-      </c>
     </row>
-    <row r="11" spans="1:41" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A11" s="2" t="s">
         <v>129</v>
       </c>
@@ -17363,11 +16970,8 @@
       <c r="AN11" s="5" t="s">
         <v>565</v>
       </c>
-      <c r="AO11" s="5" t="s">
-        <v>611</v>
-      </c>
     </row>
-    <row r="12" spans="1:41" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A12" s="2" t="s">
         <v>94</v>
       </c>
@@ -17481,11 +17085,8 @@
       <c r="AN12" s="5" t="s">
         <v>565</v>
       </c>
-      <c r="AO12" s="5" t="s">
-        <v>615</v>
-      </c>
     </row>
-    <row r="13" spans="1:41" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A13" s="2" t="s">
         <v>94</v>
       </c>
@@ -17595,11 +17196,8 @@
       <c r="AN13" s="5" t="s">
         <v>565</v>
       </c>
-      <c r="AO13" s="5" t="s">
-        <v>619</v>
-      </c>
     </row>
-    <row r="14" spans="1:41" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A14" s="2" t="s">
         <v>130</v>
       </c>
@@ -17711,11 +17309,8 @@
       <c r="AN14" s="5" t="s">
         <v>565</v>
       </c>
-      <c r="AO14" s="5" t="s">
-        <v>627</v>
-      </c>
     </row>
-    <row r="15" spans="1:41" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A15" s="2" t="s">
         <v>94</v>
       </c>
@@ -17829,11 +17424,8 @@
       <c r="AN15" s="5" t="s">
         <v>565</v>
       </c>
-      <c r="AO15" s="5" t="s">
-        <v>630</v>
-      </c>
     </row>
-    <row r="16" spans="1:41" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A16" s="2" t="s">
         <v>94</v>
       </c>
@@ -17947,12 +17539,9 @@
       <c r="AN16" s="5" t="s">
         <v>565</v>
       </c>
-      <c r="AO16" s="5" t="s">
-        <v>639</v>
-      </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AO16" xr:uid="{00000000-0009-0000-0000-000004000000}"/>
+  <autoFilter ref="A1:AN16" xr:uid="{00000000-0009-0000-0000-000004000000}"/>
   <conditionalFormatting sqref="L2:L16">
     <cfRule type="expression" dxfId="19" priority="1">
       <formula>AND($L2&lt;&gt;"", $L2&gt;=0, $L2&lt;=5)</formula>

--- a/Specialty Claims 2026-S1/2026-05 May - Specialty Claims.xlsx
+++ b/Specialty Claims 2026-S1/2026-05 May - Specialty Claims.xlsx
@@ -1008,7 +1008,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2525" uniqueCount="687">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2534" uniqueCount="696">
   <si>
     <t>Claim Status</t>
   </si>
@@ -3069,6 +3069,33 @@
   </si>
   <si>
     <t xml:space="preserve">540 days</t>
+  </si>
+  <si>
+    <t xml:space="preserve">107 claims with a date of service in 2026-05 May, split into one sheet per specialty: BH, DME, GAE, ORTHO, US.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Every specialty sheet is sorted by how close the claim is to its primary payer's timely filing deadline. Days Until Deadline (column L) carries the count: claims with five days or less left sit at the top of each sheet in red, a negative number means the filing window has already closed, and a blank means no limit is on file for that payer.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Order down the sheet, with the colour band each row gets, counted on 19 September 2026:</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    1 - Due in 5 days or less: 0</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    2 - Due in 6-30 days: 4</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    3 - Due in 31+ days: 38</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    4 - Past deadline: 54</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    5 - No limit on file: 11</t>
+  </si>
+  <si>
+    <t xml:space="preserve">'ALL Claims 2026-S1 - Master.xlsx' (same folder) holds all 482 claims for 2026 S1. Its Claim Status and Notes columns are formulas that read this file, so anything you type in columns A and B here shows up there. Keep both files in the same folder, keep the file name unchanged, and save this file before opening the master.</t>
   </si>
 </sst>
 </file>
@@ -17641,7 +17668,7 @@
     </row>
     <row r="3" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A3" s="9" t="s">
-        <v>641</v>
+        <v>687</v>
       </c>
     </row>
     <row r="4" spans="1:1" x14ac:dyDescent="0.25">
@@ -17654,37 +17681,37 @@
     </row>
     <row r="6" spans="1:1" ht="45" x14ac:dyDescent="0.25">
       <c r="A6" s="9" t="s">
-        <v>643</v>
+        <v>688</v>
       </c>
     </row>
     <row r="7" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A7" s="9" t="s">
-        <v>644</v>
+        <v>689</v>
       </c>
     </row>
     <row r="8" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A8" s="9" t="s">
-        <v>645</v>
+        <v>690</v>
       </c>
     </row>
     <row r="9" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A9" s="9" t="s">
-        <v>646</v>
+        <v>691</v>
       </c>
     </row>
     <row r="10" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A10" s="9" t="s">
-        <v>647</v>
+        <v>692</v>
       </c>
     </row>
     <row r="11" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A11" s="9" t="s">
-        <v>648</v>
+        <v>693</v>
       </c>
     </row>
     <row r="12" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A12" s="9" t="s">
-        <v>649</v>
+        <v>694</v>
       </c>
     </row>
     <row r="13" spans="1:1" x14ac:dyDescent="0.25">
@@ -17784,7 +17811,7 @@
     </row>
     <row r="34" spans="1:1" ht="45" x14ac:dyDescent="0.25">
       <c r="A34" s="9" t="s">
-        <v>666</v>
+        <v>695</v>
       </c>
     </row>
     <row r="35" spans="1:1" ht="30" x14ac:dyDescent="0.25">

--- a/Specialty Claims 2026-S1/2026-05 May - Specialty Claims.xlsx
+++ b/Specialty Claims 2026-S1/2026-05 May - Specialty Claims.xlsx
@@ -1346,7 +1346,7 @@
     <t>851, 852</t>
   </si>
   <si>
-    <t>***I need to call PT - Aetna termed date March 31, 2026</t>
+    <t>I need to call PT - Aetna termed date March 31, 2026</t>
   </si>
   <si>
     <t>HF539945835</t>
@@ -1583,7 +1583,7 @@
     <t>Received</t>
   </si>
   <si>
-    <t>***Waiting for account to get activated again</t>
+    <t>Waiting for account to get activated again</t>
   </si>
   <si>
     <t>HF509754338</t>
@@ -1871,7 +1871,7 @@
     <t>285</t>
   </si>
   <si>
-    <t>***MUE issue - CALL INS</t>
+    <t>MUE issue - CALL INS</t>
   </si>
   <si>
     <t>HF551547091</t>
@@ -2150,7 +2150,7 @@
     <t>798</t>
   </si>
   <si>
-    <t>***Still processing - ins received claim on 07/20/2026</t>
+    <t>Still processing - ins received claim on 07/20/2026</t>
   </si>
   <si>
     <t>HF436451045</t>
@@ -2240,7 +2240,7 @@
     <t>901</t>
   </si>
   <si>
-    <t>***Call PT for COB update needed by ins - Rep said the patient will need to update their Coordination of Benefits (COB) information with their insurance carrier. Once the COB has been updated, the claim can be reprocessed for review and adjudication. On yearly basis patient needs to update the COB.</t>
+    <t>Call PT for COB update needed by ins - Rep said the patient will need to update their Coordination of Benefits (COB) information with their insurance carrier. Once the COB has been updated, the claim can be reprocessed for review and adjudication. On yearly basis patient needs to update the COB.</t>
   </si>
   <si>
     <t>HF331630717</t>
@@ -2621,7 +2621,7 @@
     <t>234</t>
   </si>
   <si>
-    <t xml:space="preserve">***Call ins - Bundled - but we have an auth for this one </t>
+    <t xml:space="preserve">Call ins - Bundled - but we have an auth for this one </t>
   </si>
   <si>
     <t>805</t>
@@ -2657,7 +2657,7 @@
     <t>619</t>
   </si>
   <si>
-    <t xml:space="preserve">***Expecting ins reply - DND as medical necessity - Jess sent MR </t>
+    <t xml:space="preserve">Expecting ins reply - DND as medical necessity - Jess sent MR </t>
   </si>
   <si>
     <t>853</t>

--- a/Specialty Claims 2026-S1/2026-05 May - Specialty Claims.xlsx
+++ b/Specialty Claims 2026-S1/2026-05 May - Specialty Claims.xlsx
@@ -3080,16 +3080,16 @@
     <t xml:space="preserve">Order down the sheet, with the colour band each row gets, counted on 19 September 2026:</t>
   </si>
   <si>
-    <t xml:space="preserve">    1 - Due in 5 days or less: 0</t>
-  </si>
-  <si>
-    <t xml:space="preserve">    2 - Due in 6-30 days: 4</t>
+    <t xml:space="preserve">    1 - Due in 5 days or less: 3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    2 - Due in 6-30 days: 0</t>
   </si>
   <si>
     <t xml:space="preserve">    3 - Due in 31+ days: 38</t>
   </si>
   <si>
-    <t xml:space="preserve">    4 - Past deadline: 54</t>
+    <t xml:space="preserve">    4 - Past deadline: 55</t>
   </si>
   <si>
     <t xml:space="preserve">    5 - No limit on file: 11</t>
@@ -5592,7 +5592,7 @@
       </c>
       <c r="L10" s="12">
         <f ca="1">IF($O10="","",$O10-TODAY())</f>
-        <v>6</v>
+        <v>-51</v>
       </c>
       <c r="M10" s="12" t="str">
         <f ca="1">IF($C10="","",$C10+180-TODAY())</f>
@@ -5603,7 +5603,7 @@
         <v/>
       </c>
       <c r="O10" s="6">
-        <v>46288</v>
+        <v>46233</v>
       </c>
       <c r="P10" s="5" t="s">
         <v>47</v>

--- a/Specialty Claims 2026-S1/2026-05 May - Specialty Claims.xlsx
+++ b/Specialty Claims 2026-S1/2026-05 May - Specialty Claims.xlsx
@@ -5573,7 +5573,7 @@
         <v>109</v>
       </c>
       <c r="F10" s="6">
-        <v>46198</v>
+        <v>46143</v>
       </c>
       <c r="G10" s="5" t="s">
         <v>75</v>
